--- a/certificates data.xlsx
+++ b/certificates data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="2370">
   <si>
-    <t>Timestamp</t>
+    <t xml:space="preserve">Program Name</t>
   </si>
   <si>
     <t xml:space="preserve">Name to be Printed on Certificate</t>
@@ -22207,7 +22207,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="16.140625"/>
-    <col bestFit="1" min="7" max="7" width="15.33203125"/>
+    <col bestFit="1" min="7" max="7" width="17.36328125"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">

--- a/certificates data.xlsx
+++ b/certificates data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,6 +11,7 @@
     <sheet name="3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="NVScriptsProperties" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet name="DO NOT DELETE - AutoCrat Job Se" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="4" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2855" uniqueCount="2855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="2912">
   <si>
     <t xml:space="preserve">Program Name</t>
   </si>
@@ -6791,13 +6792,1483 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 12:48 AM</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Priyanka S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Kajal Senghani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kriya Sharir (Human Physiology) Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0449</t>
+  </si>
+  <si>
+    <t>1O_W-dYQB4ARQxPm--iqQ4nvixQt14MLB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1O_W-dYQB4ARQxPm--iqQ4nvixQt14MLB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:10 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Adishree B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Ajith Krishnan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agad Tantra evam Vidhi Vaidyaka part A</t>
+  </si>
+  <si>
+    <t>2526ECD0450</t>
+  </si>
+  <si>
+    <t>1at1Z8bs2ct0Kk_OeGzaGcjQCuc3Rbx9u</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1at1Z8bs2ct0Kk_OeGzaGcjQCuc3Rbx9u/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:11 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sambu Surendran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sahil Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shalya Tantra Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0455</t>
+  </si>
+  <si>
+    <t>1932qQ9e91it8wqRW1XB9cY_eKbmgu3Ct</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1932qQ9e91it8wqRW1XB9cY_eKbmgu3Ct/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:12 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Anoop K S </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nikita V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaumarabhritya Part B</t>
+  </si>
+  <si>
+    <t>2526ECD0458</t>
+  </si>
+  <si>
+    <t>1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Rahul Jadhav</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Vivek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Methodology and Medical-statistics</t>
+  </si>
+  <si>
+    <t>2526ECD0459</t>
+  </si>
+  <si>
+    <t>1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPER ( Pharmacy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vivek Joshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Seena Sunil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human Anatomy and Physiology</t>
+  </si>
+  <si>
+    <t>2526ECD0465</t>
+  </si>
+  <si>
+    <t>1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:56 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Devshree Parmar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Yash Janve</t>
+  </si>
+  <si>
+    <t>Pharmacology–Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0466</t>
+  </si>
+  <si>
+    <t>1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Vrundaben Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Jenish Bhagat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community Pharmacy &amp; Management – Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0467</t>
+  </si>
+  <si>
+    <t>177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Rasana Yadav </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Soniya Yadav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmacotherapeutics – Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0468</t>
+  </si>
+  <si>
+    <t>14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Srushti Shah </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Vishva Patel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital &amp; Clinical Pharmacy – Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0469</t>
+  </si>
+  <si>
+    <t>1wcLOrmkHORoFVytxRv78yqDEh1-IRszk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wcLOrmkHORoFVytxRv78yqDEh1-IRszk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIA AYurveda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Narendra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Tanjila</t>
+  </si>
+  <si>
+    <t>2526ECD0483</t>
+  </si>
+  <si>
+    <t>1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:51 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aswini Patil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Veena</t>
+  </si>
+  <si>
+    <t>12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:52 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Mahadevi B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Parth Akhani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dravyaguna Vigyan paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0486</t>
+  </si>
+  <si>
+    <t>1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. POONAM BHOJAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. HARISANKAR K T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agad Tantra evam Vidhi Vaidyaka part B</t>
+  </si>
+  <si>
+    <t>2526ECD0488</t>
+  </si>
+  <si>
+    <t>12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Mrunal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Akshatha K </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roga Nidan evam Vikriti Vigyan Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0489</t>
+  </si>
+  <si>
+    <t>1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:53 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Vasuprada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. MAULI VAISHNAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prasuti Tantra evam Stree Roga Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0494</t>
+  </si>
+  <si>
+    <t>1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name to be Printed on certificate 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc ID - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc URL - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link to merged Doc - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document Merge Status - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialization - Cyber Security and Forensics - I</t>
+  </si>
+  <si>
+    <t>2526ECD0164</t>
+  </si>
+  <si>
+    <t>1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 3:44 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Renuka Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Gaurav Kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Priya Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialization - Full Stack Web Development - I</t>
+  </si>
+  <si>
+    <t>2526ECD0165</t>
+  </si>
+  <si>
+    <t>1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Satish Chauhan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Meet Soni </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Shubhrajyoti Kundu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical and Electronics Engineering</t>
+  </si>
+  <si>
+    <t>2526ECD0166</t>
+  </si>
+  <si>
+    <t>1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 4:33 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Kartik Pandya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Mahit Jain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Electrical Engineering</t>
+  </si>
+  <si>
+    <t>2526ECD0167</t>
+  </si>
+  <si>
+    <t>1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ankitsinh Zala</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Divya Garg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Niti Shah</t>
+  </si>
+  <si>
+    <t>CVPDE</t>
+  </si>
+  <si>
+    <t>2526ECD0168</t>
+  </si>
+  <si>
+    <t>1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Purvesh Valanad</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr.  Mujahid Mirchiwala</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Gaurav Sahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC-1 (D.C Circuit)</t>
+  </si>
+  <si>
+    <t>2526ECD0205</t>
+  </si>
+  <si>
+    <t>1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:15 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Mayank Vyas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.  Ankit Patel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.  Nishant Hadiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction to Electrical Safety &amp; Management</t>
+  </si>
+  <si>
+    <t>2526ECD0206</t>
+  </si>
+  <si>
+    <t>1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:16 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Hetal Prajapati</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Pavez Vasovala </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamental of Electrical Engineering</t>
+  </si>
+  <si>
+    <t>2526ECD0207</t>
+  </si>
+  <si>
+    <t>1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Krunal Kayasth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.Jayesh Mahant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.Manthan Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Graphics </t>
+  </si>
+  <si>
+    <t>2526ECD0208</t>
+  </si>
+  <si>
+    <t>1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bhumi Bhoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Piyush Mali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Shreen Gazala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Of Things</t>
+  </si>
+  <si>
+    <t>2526ECD0209</t>
+  </si>
+  <si>
+    <t>19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ashish Pandey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Prachi Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ravi Bhardwaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Security</t>
+  </si>
+  <si>
+    <t>2526ECD0210</t>
+  </si>
+  <si>
+    <t>1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Kausal kalariya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bipasha Mandal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Hemali Nimavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operating system </t>
+  </si>
+  <si>
+    <t>2526ECD0211</t>
+  </si>
+  <si>
+    <t>1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Mansi Rana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Kavita Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Bankim Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object Oriented Programming with C++</t>
+  </si>
+  <si>
+    <t>2526ECD0212</t>
+  </si>
+  <si>
+    <t>1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:17 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. DEVANSHI THAKKAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. AMITA TAILOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. SHILPA KHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web Design and Development</t>
+  </si>
+  <si>
+    <t>2526ECD0346</t>
+  </si>
+  <si>
+    <t>1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:47 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. VAIBHAVI PANDYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. RIYA DESAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.HARDIK KUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Structure </t>
+  </si>
+  <si>
+    <t>2526ECD0347</t>
+  </si>
+  <si>
+    <t>1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. BHAVYA GAJIWALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. KAVYA PRAJAPATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. POONAM FALDU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Network</t>
+  </si>
+  <si>
+    <t>2526ECD0348</t>
+  </si>
+  <si>
+    <t>1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:48 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. KALPANA PRAJAPATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. DEVIKA KSHTRIYA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. VIJAY VASAIYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.Net Programming with C# </t>
+  </si>
+  <si>
+    <t>2526ECD0349</t>
+  </si>
+  <si>
+    <t>159BT_GO9SchY3qO-sK9fZg4H87gfmKd8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/159BT_GO9SchY3qO-sK9fZg4H87gfmKd8/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Vrunda patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ankit Padariya, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Suraj singh</t>
+  </si>
+  <si>
+    <t>2526ECD0350</t>
+  </si>
+  <si>
+    <t>1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Radhika Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BK Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bhavya shah</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>2526ECD0351</t>
+  </si>
+  <si>
+    <t>1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Shivani Shelke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Shivani Gupta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Suraj Singh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Communication Network</t>
+  </si>
+  <si>
+    <t>2526ECD0352</t>
+  </si>
+  <si>
+    <t>1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Hiral Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Rachana S. Kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Harshrajsinh Rana</t>
+  </si>
+  <si>
+    <t>Pharmaceutics</t>
+  </si>
+  <si>
+    <t>2526ECD0353</t>
+  </si>
+  <si>
+    <t>16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 3:20 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Tora Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bhargavi Mistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Krutika Agarwal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmaceutics –Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0354</t>
+  </si>
+  <si>
+    <t>1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ashish Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vikash Verma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ishan Desai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power System - I </t>
+  </si>
+  <si>
+    <t>2526ECD0386</t>
+  </si>
+  <si>
+    <t>1wOuYeHtarx_tKiscCvISOnpheAA3LoXB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wOuYeHtarx_tKiscCvISOnpheAA3LoXB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 4:49 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mrs. Priyanka Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Priyank Makwana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Krishna Gohil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematics - I</t>
+  </si>
+  <si>
+    <t>2526ECD405</t>
+  </si>
+  <si>
+    <t>1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 28 2026 5:51 AM</t>
+  </si>
+  <si>
+    <t>Physiotheraphy</t>
+  </si>
+  <si>
+    <t>Dr.Pooja</t>
+  </si>
+  <si>
+    <t>Dr.Vrunda</t>
+  </si>
+  <si>
+    <t>Dr.Siddharth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomechanics and Kinesiology-I</t>
+  </si>
+  <si>
+    <t>2526ECD426</t>
+  </si>
+  <si>
+    <t>1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Pooja-Dr.Vrunda-Dr.Siddharth-Biomechanics and Kinesiology-I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:49 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Bhavik Thacker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Sonal Poojara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Vaishali Nathwani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied physics</t>
+  </si>
+  <si>
+    <t>1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Bhavik Thacker-Ms. Sonal Poojara-Ms. Vaishali Nathwani-Applied physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 2:16 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Ravi Joshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Amarjeet Kaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Mital Kanani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachana Sharir (Human Anatomy) Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0460</t>
+  </si>
+  <si>
+    <t>1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Ravi Joshi-Dr.Amarjeet Kaur-Dr.Mital Kanani-Rachana Sharir (Human Anatomy) Paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:09 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nikita P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Kruti P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Smita Rai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dravyaguna Vigyan paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0461</t>
+  </si>
+  <si>
+    <t>1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nikita P-Dr. Kruti P-Dr.Smita Rai-Dravyaguna Vigyan paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Palak C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Jignesha P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Milind C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rasashastra evam Bhaishajyakalpana paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0462</t>
+  </si>
+  <si>
+    <t>1fZiljGMmRqmPperHUIzG1NAFD138oohm</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fZiljGMmRqmPperHUIzG1NAFD138oohm/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Palak C-Dr. Jignesha P-Dr. Milind C-Rasashastra evam Bhaishajyakalpana paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Reshma Shaji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Vivek M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Archana Panchaksharimath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swasthavritta evam Yoga Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0463</t>
+  </si>
+  <si>
+    <t>1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Reshma Shaji-Dr. Vivek M-Dr. Archana Panchaksharimath-Swasthavritta evam Yoga Paper 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Sathish Mittapalli </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Rahul Barot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Janavi Raut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmaceutical Organic Chemistry</t>
+  </si>
+  <si>
+    <t>2526ECD0464</t>
+  </si>
+  <si>
+    <t>15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Sathish Mittapalli - Mr. Rahul Barot -Ms. Janavi Raut-Pharmaceutical Organic Chemistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:54 AM</t>
+  </si>
+  <si>
+    <t>JNHMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Uma Sahoo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Upma Raval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Vinit Tapas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physiology and Biochemistry</t>
+  </si>
+  <si>
+    <t>2526ECD0476</t>
+  </si>
+  <si>
+    <t>1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Uma Sahoo-Dr Upma Raval-Dr Vinit Tapas-Physiology and Biochemistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:18 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Naresh Bhusara </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Nayana Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Neelima Sharan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homoeopathic Pharmacy</t>
+  </si>
+  <si>
+    <t>2526ECD0477</t>
+  </si>
+  <si>
+    <t>11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Naresh Bhusara -Dr Nayana Patel-Dr Neelima Sharan-Homoeopathic Pharmacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Vani Oza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Archana Tegwal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Preeti Mulani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homoeopathic Materia Medica</t>
+  </si>
+  <si>
+    <t>2526ECD0478</t>
+  </si>
+  <si>
+    <t>1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Vani Oza-Dr Archana Tegwal-Dr Preeti Mulani-Homoeopathic Materia Medica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Pragya Srivastva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Preeti Pathak </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Amar Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pathology and Microbiology</t>
+  </si>
+  <si>
+    <t>2526ECD0479</t>
+  </si>
+  <si>
+    <t>1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Pragya Srivastva-Dr Preeti Pathak -Dr Amar Thakkar-Pathology and Microbiology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Smit Dad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Astha Rawal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Dhwani Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice of Medicine</t>
+  </si>
+  <si>
+    <t>2526ECD0480</t>
+  </si>
+  <si>
+    <t>1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Smit Dad-Dr Astha Rawal-Dr Dhwani Thakkar-Practice of Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aparna Bagul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Rajalekshmi R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Hari Sankar M S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swasthavritta evam Yoga Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0481</t>
+  </si>
+  <si>
+    <t>1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aparna Bagul-Dr Rajalekshmi R-Dr Hari Sankar M S-Swasthavritta evam Yoga Paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:58 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Jaiminikumari Mahendrasinh Rathod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nishant Nareshbhai Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
+  </si>
+  <si>
+    <t>2526ECD0482</t>
+  </si>
+  <si>
+    <t>1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE-Dr. Jaiminikumari Mahendrasinh Rathod-Dr. Nishant Nareshbhai Patel-Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. PARIKSHIT RAMAKANT SHIRODE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. PRAJAPATI HARSHADKUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shalya Tantra Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0491</t>
+  </si>
+  <si>
+    <t>1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari-Dr. PARIKSHIT RAMAKANT SHIRODE -Dr. PRAJAPATI HARSHADKUMAR-Shalya Tantra Paper 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 5:07 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Jalpa Zalawadia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sumit Das Lala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krishnamraju Putta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop and Manufacturing Practice</t>
+  </si>
+  <si>
+    <t>1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Jalpa Zalawadia-Dr. Sumit Das Lala-Krishnamraju Putta-Workshop and Manufacturing Practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:24 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vishal Jain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Nishant Rajput</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Omprakash Bharti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elements of Thermal and Fluid Sciences</t>
+  </si>
+  <si>
+    <t>1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vishal Jain-Mr. Nishant Rajput-Dr. Omprakash Bharti-Elements of Thermal and Fluid Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:26 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Manan Shah </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Akash Shukla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Hitesh Dave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Graphics and Design</t>
+  </si>
+  <si>
+    <t>1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Manan Shah -Mr. Akash Shukla-Mr. Hitesh Dave-Engineering Graphics and Design</t>
+  </si>
+  <si>
+    <t>autocratn</t>
+  </si>
+  <si>
+    <t>autocratp</t>
+  </si>
+  <si>
+    <t>dataSheetName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Form Responses 1"</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>"5.1"</t>
+  </si>
+  <si>
+    <t>dataSheetId</t>
+  </si>
+  <si>
+    <t>"6.50628832E8"</t>
+  </si>
+  <si>
+    <t>updateTime</t>
+  </si>
+  <si>
+    <t>"1.777270430007E12"</t>
+  </si>
+  <si>
+    <t>vp</t>
+  </si>
+  <si>
+    <t>ssId</t>
+  </si>
+  <si>
+    <t>"1XAffx2osIAaU40eNPfh9ozyEJ0Jv8Cac9e2lgVmJ_5Y"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Sheet ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Data Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share As</t>
+  </si>
+  <si>
+    <t>Folders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic Folder Reference</t>
+  </si>
+  <si>
+    <t>Conditionals</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Append Breaks</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run On Time Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Trigger Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run On Form Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send Email And Share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email BCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Reply To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email No Reply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevent Resharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Trigger Timestamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form Trigger Timestamp</t>
+  </si>
+  <si>
+    <t>_1777010583975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) E content certificate</t>
+  </si>
+  <si>
+    <t>1hyfm2hOwN-su9PZzJQCcmUAJfsTj_Tuv6JRyBkz19SU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;&lt;Name to be Printed on Certificate&gt;&gt;-&lt;&lt;Subject&gt;&gt;</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>["1APY_TOVAsRdET2TZ1CeJ3l6lXbibUj-U"]</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>MULTIPLE_OUTPUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Sr No"},"tag":"Sr No"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Date"},"tag":"Date"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Subject"},"tag":"Subject"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Name to be Printed on Certificate"},"tag":"Name"}]</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name to be Printed on Certificate 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name to be Printed on Certificate 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc ID - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc URL - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link to merged Doc - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document Merge Status - 2 Econtent Certificate</t>
+  </si>
+  <si>
     <t>PHYSIOTHERAPHY</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr.Rinkal, Dr.Prachi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Asha, Dr.Dhaval</t>
+    <t>Dr.Rinkal</t>
+  </si>
+  <si>
+    <t>Dr.Asha</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr.Prachi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr.Dhaval</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentals of ET-1</t>
@@ -6812,10 +8283,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:51 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">DR.RUSHIKESH JOSHI, DR.POOJA SONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.TANVI PATEL, DR.NIDHI MANGROLIA</t>
+    <t xml:space="preserve">DR.RUSHIKESH JOSHI, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.TANVI PATEL, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.POOJA SONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.NIDHI MANGROLIA</t>
   </si>
   <si>
     <t xml:space="preserve">Biomedical Physics</t>
@@ -6827,10 +8304,16 @@
     <t>https://drive.google.com/file/d/1RomXGXq4D02P0f3OIuBCfx5HuIEalA7w/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr.Meghavi, Dr.Sonal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Heli, Dr.Mansi</t>
+    <t>Dr.Meghavi,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Heli, </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr.Sonal</t>
+  </si>
+  <si>
+    <t>Dr.Mansi</t>
   </si>
   <si>
     <t>Electrotherapy-I</t>
@@ -6845,10 +8328,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:52 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Priyanka, Dr. Madhavi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Simrah, Dr. Didhiti</t>
+    <t xml:space="preserve">Dr. Priyanka,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Simrah, </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Madhavi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Didhiti</t>
   </si>
   <si>
     <t xml:space="preserve">Therapeutics of Exercise Therapy-I</t>
@@ -6860,10 +8349,16 @@
     <t>https://drive.google.com/file/d/1H2hyQG6O2w0pM_3K6xpCqWfDUAdyVq2u/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr.Jigisha, Dr. Joyal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Advita, Dr. Nilesh</t>
+    <t xml:space="preserve">Dr.Jigisha, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Advita, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Joyal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nilesh</t>
   </si>
   <si>
     <t xml:space="preserve">Therapeutics of Exercise Therapy-II</t>
@@ -6875,10 +8370,16 @@
     <t>https://drive.google.com/file/d/1nOYQgrmFO5MQqh5kDUnf05OxlJc20Y8P/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Dhwani, Dr. Chaitali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Dwija, Dr. Dharmang</t>
+    <t xml:space="preserve">Dr. Dhwani, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Dwija, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Chaitali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Dharmang</t>
   </si>
   <si>
     <t xml:space="preserve">Biomechanics and Kinesiology-II</t>
@@ -6890,10 +8391,16 @@
     <t>https://drive.google.com/file/d/1PbxtA94A1_2lqEzrLOgMEK0CWlhdnE6C/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">DR.SANDIP PAREKH, DR.GOPI PANCHMATIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.PRAKRUTI PARIKH, DR.DARPAN VANAVI</t>
+    <t xml:space="preserve">DR.SANDIP PAREKH, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.PRAKRUTI PARIKH, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.GOPI PANCHMATIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.DARPAN VANAVI</t>
   </si>
   <si>
     <t>Electrotherapy-II</t>
@@ -6905,10 +8412,16 @@
     <t>https://drive.google.com/file/d/1Rv1Qt1YcCGA4StmAj7SMbnIu_Twmdzpq/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">DR.MONALI SONI, DR.HETA DOSHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.PAYAL BHARDVA, DR.PARTH PRAJAPATI</t>
+    <t xml:space="preserve">DR.MONALI SONI, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.PAYAL BHARDVA, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.HETA DOSHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.PARTH PRAJAPATI</t>
   </si>
   <si>
     <t xml:space="preserve">EXERCISE THERAPY 2</t>
@@ -6920,10 +8433,13 @@
     <t>https://drive.google.com/file/d/1tRu8QJeYFsCjglalcbcD1UIuRU4EbLAt/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Mr. Vikash Verma, Mr. Ashish Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vinay Yadav, Ishan Desai</t>
+    <t xml:space="preserve">Mr. Vikash Verma, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vinay Yadav, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ishan Desai</t>
   </si>
   <si>
     <t xml:space="preserve">Power System - I</t>
@@ -6938,52 +8454,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 2:00 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Priyanka S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Kajal Senghani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kriya Sharir (Human Physiology) Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0449</t>
-  </si>
-  <si>
-    <t>1O_W-dYQB4ARQxPm--iqQ4nvixQt14MLB</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1O_W-dYQB4ARQxPm--iqQ4nvixQt14MLB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:10 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Adishree B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Ajith Krishnan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agad Tantra evam Vidhi Vaidyaka part A</t>
-  </si>
-  <si>
-    <t>2526ECD0450</t>
-  </si>
-  <si>
-    <t>1at1Z8bs2ct0Kk_OeGzaGcjQCuc3Rbx9u</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1at1Z8bs2ct0Kk_OeGzaGcjQCuc3Rbx9u/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:11 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Manjusha P, Dr. Parvathy S </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Hrishita Dahilekar, Dr Prashant Patil</t>
+    <t xml:space="preserve">Dr. Manjusha P, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Hrishita Dahilekar, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Parvathy S </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Prashant Patil</t>
   </si>
   <si>
     <t xml:space="preserve">Roga Nidan evam Vikriti Vigyan Paper 2</t>
@@ -6998,10 +8478,16 @@
     <t>https://drive.google.com/file/d/1UmjUvnHaxt6BeT3jjrEykDQbcSa6V4yV/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Tarangna G, Dr. Malavika B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Prachi V, Dr.Shivangi </t>
+    <t xml:space="preserve">Dr. Tarangna G, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Prachi V, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Malavika B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Shivangi </t>
   </si>
   <si>
     <t xml:space="preserve">Kayachikitsa including Manasa Roga, Rasayana and Vajikarana Paper 2 </t>
@@ -7016,10 +8502,13 @@
     <t>https://drive.google.com/file/d/1LHlKr3Bk47mOWsvJ_R1tUp5uHJ1oHHHM/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr.Shivangi, Dr. Malavika B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Tarangna G, Dr. Prachi V </t>
+    <t xml:space="preserve">Dr.Shivangi, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Tarangna G,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Prachi V </t>
   </si>
   <si>
     <t xml:space="preserve">Kayachikitsa including Vyadhi Vishesha Chikitsa Evam Rasayana, Vajikarana Paper 3</t>
@@ -7034,10 +8523,16 @@
     <t>https://drive.google.com/file/d/1AsNyuchpBCQQl4kEASbZE-IIO5FdzPCK/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Nisha R, Dr. Abhilesh V S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Mahesh Dodiya, Dr. Jignesha Charel </t>
+    <t xml:space="preserve">Dr. Nisha R, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Mahesh Dodiya, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Abhilesh V S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Jignesha Charel </t>
   </si>
   <si>
     <t xml:space="preserve">Panchakarma &amp; Upakarma Part B</t>
@@ -7052,31 +8547,16 @@
     <t>https://drive.google.com/file/d/1WVFGwQ0m49_KQuLaHRMhFdKq10TR_E7U/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Sambu Surendran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Sahil Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shalya Tantra Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0455</t>
-  </si>
-  <si>
-    <t>1932qQ9e91it8wqRW1XB9cY_eKbmgu3Ct</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1932qQ9e91it8wqRW1XB9cY_eKbmgu3Ct/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:12 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Krunal P, Dr. Jasna C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Ganesh T, Dr Sreelakshmy</t>
+    <t xml:space="preserve">Dr. Krunal P, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Ganesh T,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Jasna C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr Sreelakshmy</t>
   </si>
   <si>
     <t xml:space="preserve"> Shalakya Tantra-Ophthalmology, Oto-Rhino- Laryngology &amp; Oro-Dentistry Paper 1</t>
@@ -7091,10 +8571,16 @@
     <t>https://drive.google.com/file/d/1koI4RPd-nOHo_lb2iOgHTjr6mKzBoQ8c/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Chithra G, Dr. Gauri S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Prashant Fawde, Dr Shradha</t>
+    <t xml:space="preserve">Dr. Chithra G,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Prashant Fawde, </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Gauri S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Shradha</t>
   </si>
   <si>
     <t xml:space="preserve">Prasuti Tantra evam Stree Roga Paper 1</t>
@@ -7109,145 +8595,16 @@
     <t>https://drive.google.com/file/d/1FBCNbuS3_lEecm604qOtLsP7BPtDVV5A/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Anoop K S </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nikita V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaumarabhritya Part B</t>
-  </si>
-  <si>
-    <t>2526ECD0458</t>
-  </si>
-  <si>
-    <t>1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Rahul Jadhav</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Vivek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Methodology and Medical-statistics</t>
-  </si>
-  <si>
-    <t>2526ECD0459</t>
-  </si>
-  <si>
-    <t>1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPER ( Pharmacy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vivek Joshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Seena Sunil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Anatomy and Physiology</t>
-  </si>
-  <si>
-    <t>2526ECD0465</t>
-  </si>
-  <si>
-    <t>1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:56 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ms. Devshree Parmar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Yash Janve</t>
-  </si>
-  <si>
-    <t>Pharmacology–Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0466</t>
-  </si>
-  <si>
-    <t>1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Vrundaben Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ms. Jenish Bhagat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community Pharmacy &amp; Management – Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0467</t>
-  </si>
-  <si>
-    <t>177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Rasana Yadav </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Soniya Yadav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmacotherapeutics – Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0468</t>
-  </si>
-  <si>
-    <t>14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Srushti Shah </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Vishva Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospital &amp; Clinical Pharmacy – Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0469</t>
-  </si>
-  <si>
-    <t>1wcLOrmkHORoFVytxRv78yqDEh1-IRszk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wcLOrmkHORoFVytxRv78yqDEh1-IRszk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>JNHMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Sunderlal Singh, Dr Jay K Solanki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Jash Mehta, Dr Selva Panda</t>
+    <t xml:space="preserve">Dr Sunderlal Singh, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Jash Mehta, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Jay K Solanki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Selva Panda</t>
   </si>
   <si>
     <t xml:space="preserve">Human Anatomy</t>
@@ -7265,10 +8622,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:20 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr Komal Patel, Dr Alpesh Jaiswal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Jyoti Poddar, Dr Shreya Joshi</t>
+    <t xml:space="preserve">Dr Komal Patel, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Jyoti Poddar,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Alpesh Jaiswal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr Shreya Joshi</t>
   </si>
   <si>
     <t xml:space="preserve">Organon of Medicine</t>
@@ -7283,10 +8646,16 @@
     <t>https://drive.google.com/file/d/1oGPHJH4NJfjdtR70rEzDR_rczylB9E4P/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr Falguni Patel, Dr Sameera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Jagruti Patel, Dr Janki</t>
+    <t xml:space="preserve">Dr Falguni Patel, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Jagruti Patel, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Sameera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Janki</t>
   </si>
   <si>
     <t xml:space="preserve">Forensic Medicine</t>
@@ -7301,10 +8670,16 @@
     <t>https://drive.google.com/file/d/1Yzm6m5OGbrHLeXMFo9Iqzgjvg9CxTGfk/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr Riya Jodha, Dr Indrani Halder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Parula Patel,Dr Krunal Dabhi</t>
+    <t xml:space="preserve">Dr Riya Jodha, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Parula Patel,Dr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Indrani Halder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krunal Dabhi</t>
   </si>
   <si>
     <t>Repertory</t>
@@ -7322,10 +8697,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:21 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr Priyanka Shah, Dr Surbhi Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Sujeet Lal, Dr Viren Nimbark</t>
+    <t xml:space="preserve">Dr Priyanka Shah, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Sujeet Lal, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Surbhi Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Viren Nimbark</t>
   </si>
   <si>
     <t>Surgery</t>
@@ -7340,10 +8721,16 @@
     <t>https://drive.google.com/file/d/1H4QmffVYIcXCRnjadG-E2K_FzdLgoHcB/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr Pranali Mistry, Dr Hasti Dekivadiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Zankhana Desai, Dr Mayank Yadav</t>
+    <t xml:space="preserve">Dr Pranali Mistry, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Zankhana Desai, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Hasti Dekivadiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Mayank Yadav</t>
   </si>
   <si>
     <t xml:space="preserve">Community Medicine</t>
@@ -7358,31 +8745,16 @@
     <t>https://drive.google.com/file/d/17aUuH1zh2QFm_baUArun_GgIrWADaZnP/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">PIA AYurveda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Narendra </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Tanjila</t>
-  </si>
-  <si>
-    <t>2526ECD0483</t>
-  </si>
-  <si>
-    <t>1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:51 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Nirav, Dr Sebin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Amal Thomas, Dr Shivakumar</t>
+    <t xml:space="preserve">Dr Nirav, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Amal Thomas, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Sebin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Shivakumar</t>
   </si>
   <si>
     <t xml:space="preserve">Rachana Sharir (Human Anatomy) Paper 2</t>
@@ -7394,43 +8766,16 @@
     <t>https://drive.google.com/file/d/1oTebnx5Nbn9hEZmpE20ixsE3WSBHAXIC/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:52 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Aswini Patil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Veena</t>
-  </si>
-  <si>
-    <t>12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Mahadevi B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Parth Akhani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dravyaguna Vigyan paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0486</t>
-  </si>
-  <si>
-    <t>1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Maitry Sachinwala, Dr Anjali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Ebin, Dr. ANILA R S</t>
+    <t xml:space="preserve">Dr. Maitry Sachinwala, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Ebin, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Anjali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. ANILA R S</t>
   </si>
   <si>
     <t xml:space="preserve">Rasashastra evam Bhaishajyakalpana paper 2</t>
@@ -7445,49 +8790,16 @@
     <t>https://drive.google.com/file/d/1nl9TkdO_KlxMAiyE9M4c6oYcEJvoyM-P/view?usp=drivesdk</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. POONAM BHOJAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. HARISANKAR K T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agad Tantra evam Vidhi Vaidyaka part B</t>
-  </si>
-  <si>
-    <t>2526ECD0488</t>
-  </si>
-  <si>
-    <t>12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Mrunal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Akshatha K </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roga Nidan evam Vikriti Vigyan Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0489</t>
-  </si>
-  <si>
-    <t>1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:53 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Swati Barve, Dr Rahul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. KORA RANJITH KUMAR, Dr. SREELAL</t>
+    <t xml:space="preserve">Dr. Swati Barve, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. KORA RANJITH KUMAR, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Rahul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. SREELAL</t>
   </si>
   <si>
     <t xml:space="preserve">Panchakarma &amp; Upakarma Part A</t>
@@ -7505,10 +8817,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:57 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. NIHALUDDIN , Dr. NIJIL A.V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. RADHIKA , Dr. SHALAKA MORE</t>
+    <t xml:space="preserve">Dr. NIHALUDDIN , </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. RADHIKA , </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. NIJIL A.V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. SHALAKA MORE</t>
   </si>
   <si>
     <t xml:space="preserve">Shalakya Tantra-Ophthalmology, Oto-Rhino- Laryngology &amp; Oro-Dentistry Paper 2</t>
@@ -7526,10 +8844,16 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:56 AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Kavya MohanKumar,Dr. Ishita Swami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Shailaja, Dr. Aneesh</t>
+    <t xml:space="preserve">Dr. Kavya MohanKumar,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Shailaja, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Ishita Swami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aneesh</t>
   </si>
   <si>
     <t xml:space="preserve">Kaumarabhritya Part A</t>
@@ -7545,1158 +8869,6 @@
   </si>
   <si>
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 4:00 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Vasuprada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. MAULI VAISHNAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prasuti Tantra evam Stree Roga Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0494</t>
-  </si>
-  <si>
-    <t>1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name to be Printed on certificate 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Doc ID - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Doc URL - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link to merged Doc - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document Merge Status - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialization - Cyber Security and Forensics - I</t>
-  </si>
-  <si>
-    <t>2526ECD0164</t>
-  </si>
-  <si>
-    <t>1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 3:44 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Renuka Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Gaurav Kumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Priya Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialization - Full Stack Web Development - I</t>
-  </si>
-  <si>
-    <t>2526ECD0165</t>
-  </si>
-  <si>
-    <t>1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Satish Chauhan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Meet Soni </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Shubhrajyoti Kundu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical and Electronics Engineering</t>
-  </si>
-  <si>
-    <t>2526ECD0166</t>
-  </si>
-  <si>
-    <t>1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 4:33 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Kartik Pandya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Mahit Jain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic Electrical Engineering</t>
-  </si>
-  <si>
-    <t>2526ECD0167</t>
-  </si>
-  <si>
-    <t>1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ankitsinh Zala</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ms. Divya Garg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Niti Shah</t>
-  </si>
-  <si>
-    <t>CVPDE</t>
-  </si>
-  <si>
-    <t>2526ECD0168</t>
-  </si>
-  <si>
-    <t>1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Purvesh Valanad</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr.  Mujahid Mirchiwala</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Gaurav Sahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC-1 (D.C Circuit)</t>
-  </si>
-  <si>
-    <t>2526ECD0205</t>
-  </si>
-  <si>
-    <t>1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:15 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Mayank Vyas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.  Ankit Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.  Nishant Hadiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduction to Electrical Safety &amp; Management</t>
-  </si>
-  <si>
-    <t>2526ECD0206</t>
-  </si>
-  <si>
-    <t>1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:16 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Hetal Prajapati</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Pavez Vasovala </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundamental of Electrical Engineering</t>
-  </si>
-  <si>
-    <t>2526ECD0207</t>
-  </si>
-  <si>
-    <t>1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Krunal Kayasth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.Jayesh Mahant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.Manthan Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Graphics </t>
-  </si>
-  <si>
-    <t>2526ECD0208</t>
-  </si>
-  <si>
-    <t>1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bhumi Bhoi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Piyush Mali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Shreen Gazala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Of Things</t>
-  </si>
-  <si>
-    <t>2526ECD0209</t>
-  </si>
-  <si>
-    <t>19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ashish Pandey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Prachi Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ravi Bhardwaj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Security</t>
-  </si>
-  <si>
-    <t>2526ECD0210</t>
-  </si>
-  <si>
-    <t>1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Kausal kalariya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bipasha Mandal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Hemali Nimavat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operating system </t>
-  </si>
-  <si>
-    <t>2526ECD0211</t>
-  </si>
-  <si>
-    <t>1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Mansi Rana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Kavita Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Bankim Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Object Oriented Programming with C++</t>
-  </si>
-  <si>
-    <t>2526ECD0212</t>
-  </si>
-  <si>
-    <t>1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:17 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. DEVANSHI THAKKAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. AMITA TAILOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. SHILPA KHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web Design and Development</t>
-  </si>
-  <si>
-    <t>2526ECD0346</t>
-  </si>
-  <si>
-    <t>1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:47 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. VAIBHAVI PANDYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. RIYA DESAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.HARDIK KUMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Structure </t>
-  </si>
-  <si>
-    <t>2526ECD0347</t>
-  </si>
-  <si>
-    <t>1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. BHAVYA GAJIWALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. KAVYA PRAJAPATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. POONAM FALDU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Network</t>
-  </si>
-  <si>
-    <t>2526ECD0348</t>
-  </si>
-  <si>
-    <t>1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:48 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. KALPANA PRAJAPATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. DEVIKA KSHTRIYA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. VIJAY VASAIYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.Net Programming with C# </t>
-  </si>
-  <si>
-    <t>2526ECD0349</t>
-  </si>
-  <si>
-    <t>159BT_GO9SchY3qO-sK9fZg4H87gfmKd8</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/159BT_GO9SchY3qO-sK9fZg4H87gfmKd8/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Vrunda patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ankit Padariya, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Suraj singh</t>
-  </si>
-  <si>
-    <t>2526ECD0350</t>
-  </si>
-  <si>
-    <t>1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Radhika Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BK Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bhavya shah</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>2526ECD0351</t>
-  </si>
-  <si>
-    <t>1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Shivani Shelke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Shivani Gupta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Suraj Singh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Communication Network</t>
-  </si>
-  <si>
-    <t>2526ECD0352</t>
-  </si>
-  <si>
-    <t>1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Hiral Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Rachana S. Kumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Harshrajsinh Rana</t>
-  </si>
-  <si>
-    <t>Pharmaceutics</t>
-  </si>
-  <si>
-    <t>2526ECD0353</t>
-  </si>
-  <si>
-    <t>16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 3:20 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Tora Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bhargavi Mistry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Krutika Agarwal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmaceutics –Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0354</t>
-  </si>
-  <si>
-    <t>1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ashish Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vikash Verma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ishan Desai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power System - I </t>
-  </si>
-  <si>
-    <t>2526ECD0386</t>
-  </si>
-  <si>
-    <t>1wOuYeHtarx_tKiscCvISOnpheAA3LoXB</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wOuYeHtarx_tKiscCvISOnpheAA3LoXB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 4:49 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mrs. Priyanka Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Priyank Makwana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Krishna Gohil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathematics - I</t>
-  </si>
-  <si>
-    <t>2526ECD405</t>
-  </si>
-  <si>
-    <t>1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 28 2026 5:51 AM</t>
-  </si>
-  <si>
-    <t>Physiotheraphy</t>
-  </si>
-  <si>
-    <t>Dr.Pooja</t>
-  </si>
-  <si>
-    <t>Dr.Vrunda</t>
-  </si>
-  <si>
-    <t>Dr.Siddharth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biomechanics and Kinesiology-I</t>
-  </si>
-  <si>
-    <t>2526ECD426</t>
-  </si>
-  <si>
-    <t>1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Pooja-Dr.Vrunda-Dr.Siddharth-Biomechanics and Kinesiology-I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:49 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Bhavik Thacker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Sonal Poojara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Vaishali Nathwani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied physics</t>
-  </si>
-  <si>
-    <t>1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Bhavik Thacker-Ms. Sonal Poojara-Ms. Vaishali Nathwani-Applied physics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 2:16 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Ravi Joshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Amarjeet Kaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Mital Kanani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachana Sharir (Human Anatomy) Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0460</t>
-  </si>
-  <si>
-    <t>1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Ravi Joshi-Dr.Amarjeet Kaur-Dr.Mital Kanani-Rachana Sharir (Human Anatomy) Paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:09 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nikita P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Kruti P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Smita Rai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dravyaguna Vigyan paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0461</t>
-  </si>
-  <si>
-    <t>1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nikita P-Dr. Kruti P-Dr.Smita Rai-Dravyaguna Vigyan paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Palak C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Jignesha P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Milind C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rasashastra evam Bhaishajyakalpana paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0462</t>
-  </si>
-  <si>
-    <t>1fZiljGMmRqmPperHUIzG1NAFD138oohm</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1fZiljGMmRqmPperHUIzG1NAFD138oohm/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Palak C-Dr. Jignesha P-Dr. Milind C-Rasashastra evam Bhaishajyakalpana paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Reshma Shaji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Vivek M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Archana Panchaksharimath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swasthavritta evam Yoga Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0463</t>
-  </si>
-  <si>
-    <t>1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Reshma Shaji-Dr. Vivek M-Dr. Archana Panchaksharimath-Swasthavritta evam Yoga Paper 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Sathish Mittapalli </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Rahul Barot </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Janavi Raut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmaceutical Organic Chemistry</t>
-  </si>
-  <si>
-    <t>2526ECD0464</t>
-  </si>
-  <si>
-    <t>15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Sathish Mittapalli - Mr. Rahul Barot -Ms. Janavi Raut-Pharmaceutical Organic Chemistry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:54 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Uma Sahoo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Upma Raval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Vinit Tapas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physiology and Biochemistry</t>
-  </si>
-  <si>
-    <t>2526ECD0476</t>
-  </si>
-  <si>
-    <t>1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Uma Sahoo-Dr Upma Raval-Dr Vinit Tapas-Physiology and Biochemistry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:18 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Naresh Bhusara </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Nayana Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Neelima Sharan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homoeopathic Pharmacy</t>
-  </si>
-  <si>
-    <t>2526ECD0477</t>
-  </si>
-  <si>
-    <t>11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Naresh Bhusara -Dr Nayana Patel-Dr Neelima Sharan-Homoeopathic Pharmacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Vani Oza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Archana Tegwal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Preeti Mulani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homoeopathic Materia Medica</t>
-  </si>
-  <si>
-    <t>2526ECD0478</t>
-  </si>
-  <si>
-    <t>1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Vani Oza-Dr Archana Tegwal-Dr Preeti Mulani-Homoeopathic Materia Medica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Pragya Srivastva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Preeti Pathak </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Amar Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pathology and Microbiology</t>
-  </si>
-  <si>
-    <t>2526ECD0479</t>
-  </si>
-  <si>
-    <t>1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Pragya Srivastva-Dr Preeti Pathak -Dr Amar Thakkar-Pathology and Microbiology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Smit Dad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Astha Rawal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Dhwani Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice of Medicine</t>
-  </si>
-  <si>
-    <t>2526ECD0480</t>
-  </si>
-  <si>
-    <t>1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Smit Dad-Dr Astha Rawal-Dr Dhwani Thakkar-Practice of Medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Aparna Bagul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Rajalekshmi R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Hari Sankar M S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swasthavritta evam Yoga Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0481</t>
-  </si>
-  <si>
-    <t>1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Aparna Bagul-Dr Rajalekshmi R-Dr Hari Sankar M S-Swasthavritta evam Yoga Paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:58 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Jaiminikumari Mahendrasinh Rathod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nishant Nareshbhai Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
-  </si>
-  <si>
-    <t>2526ECD0482</t>
-  </si>
-  <si>
-    <t>1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE-Dr. Jaiminikumari Mahendrasinh Rathod-Dr. Nishant Nareshbhai Patel-Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. PARIKSHIT RAMAKANT SHIRODE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. PRAJAPATI HARSHADKUMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shalya Tantra Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0491</t>
-  </si>
-  <si>
-    <t>1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari-Dr. PARIKSHIT RAMAKANT SHIRODE -Dr. PRAJAPATI HARSHADKUMAR-Shalya Tantra Paper 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 5:07 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Jalpa Zalawadia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Sumit Das Lala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krishnamraju Putta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop and Manufacturing Practice</t>
-  </si>
-  <si>
-    <t>1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Jalpa Zalawadia-Dr. Sumit Das Lala-Krishnamraju Putta-Workshop and Manufacturing Practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:24 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vishal Jain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Nishant Rajput</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Omprakash Bharti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elements of Thermal and Fluid Sciences</t>
-  </si>
-  <si>
-    <t>1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vishal Jain-Mr. Nishant Rajput-Dr. Omprakash Bharti-Elements of Thermal and Fluid Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:26 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Manan Shah </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Akash Shukla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Hitesh Dave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Graphics and Design</t>
-  </si>
-  <si>
-    <t>1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Manan Shah -Mr. Akash Shukla-Mr. Hitesh Dave-Engineering Graphics and Design</t>
-  </si>
-  <si>
-    <t>autocratn</t>
-  </si>
-  <si>
-    <t>autocratp</t>
-  </si>
-  <si>
-    <t>dataSheetName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Form Responses 1"</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>"5.1"</t>
-  </si>
-  <si>
-    <t>dataSheetId</t>
-  </si>
-  <si>
-    <t>"6.50628832E8"</t>
-  </si>
-  <si>
-    <t>updateTime</t>
-  </si>
-  <si>
-    <t>"1.777270430007E12"</t>
-  </si>
-  <si>
-    <t>vp</t>
-  </si>
-  <si>
-    <t>ssId</t>
-  </si>
-  <si>
-    <t>"1XAffx2osIAaU40eNPfh9ozyEJ0Jv8Cac9e2lgVmJ_5Y"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Sheet ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Data Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share As</t>
-  </si>
-  <si>
-    <t>Folders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Folder Reference</t>
-  </si>
-  <si>
-    <t>Conditionals</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Append Breaks</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run On Time Trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Trigger Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run On Form Trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Send Email And Share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email BCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Reply To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email No Reply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prevent Resharing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Trigger Timestamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form Trigger Timestamp</t>
-  </si>
-  <si>
-    <t>_1777010583975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) E content certificate</t>
-  </si>
-  <si>
-    <t>1hyfm2hOwN-su9PZzJQCcmUAJfsTj_Tuv6JRyBkz19SU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;&lt;Name to be Printed on Certificate&gt;&gt;-&lt;&lt;Subject&gt;&gt;</t>
-  </si>
-  <si>
-    <t>PDF</t>
-  </si>
-  <si>
-    <t>["1APY_TOVAsRdET2TZ1CeJ3l6lXbibUj-U"]</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>MULTIPLE_OUTPUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Sr No"},"tag":"Sr No"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Date"},"tag":"Date"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Subject"},"tag":"Subject"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Name to be Printed on Certificate"},"tag":"Name"}]</t>
   </si>
 </sst>
 </file>
@@ -8707,7 +8879,7 @@
     <numFmt numFmtId="164" formatCode="d mmmm,yyyy"/>
     <numFmt numFmtId="165" formatCode="d mmmm, yyyy"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="51">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -8958,6 +9130,28 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.000000"/>
+      <color indexed="65"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10.000000"/>
+      <color indexed="64"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="24">
     <fill>
@@ -9099,7 +9293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="71">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -9830,36 +10024,6 @@
         <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color indexed="7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="7"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
@@ -9955,11 +10119,157 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFEFEFEF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8EAED"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color indexed="7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="7"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="386">
+  <cellXfs count="404">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -10851,27 +11161,6 @@
     <xf fontId="1" fillId="15" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="35" fillId="6" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="24" fillId="6" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="6" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="35" fillId="6" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="6" borderId="55" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="35" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
@@ -10881,13 +11170,13 @@
     <xf fontId="35" fillId="6" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="6" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="6" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="34" fillId="6" borderId="56" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="34" fillId="6" borderId="54" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="6" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="6" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="33" fillId="6" borderId="51" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10902,7 +11191,7 @@
     <xf fontId="10" fillId="23" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="10" fillId="23" borderId="57" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="23" borderId="55" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf fontId="5" fillId="23" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10914,7 +11203,7 @@
     <xf fontId="1" fillId="23" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="10" fillId="23" borderId="58" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="23" borderId="56" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf fontId="44" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10987,10 +11276,10 @@
     <xf fontId="32" fillId="4" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="4" borderId="59" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="4" borderId="57" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="4" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="4" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" wrapText="1"/>
     </xf>
     <xf fontId="33" fillId="4" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10999,13 +11288,13 @@
     <xf fontId="33" fillId="15" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="34" fillId="4" borderId="60" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="34" fillId="4" borderId="58" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="4" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="4" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="4" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="4" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="33" fillId="4" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11026,15 +11315,90 @@
     <xf fontId="33" fillId="4" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="34" fillId="4" borderId="61" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="34" fillId="4" borderId="59" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="34" fillId="6" borderId="62" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="34" fillId="6" borderId="60" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf fontId="47" fillId="2" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="47" fillId="2" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="48" fillId="3" borderId="63" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="48" fillId="3" borderId="64" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="65" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" wrapText="1"/>
+    </xf>
+    <xf fontId="35" fillId="6" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="49" fillId="6" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="6" borderId="66" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="6" borderId="25" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="4" borderId="31" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="6" borderId="36" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="6" borderId="67" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="4" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="69" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="70" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="6" borderId="48" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -24538,1431 +24902,547 @@
     </row>
     <row r="81" ht="25.5" customHeight="1">
       <c r="A81" s="323" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B81" s="196" t="s">
         <v>2219</v>
       </c>
-      <c r="B81" s="324" t="s">
+      <c r="C81" s="196" t="s">
         <v>2220</v>
       </c>
-      <c r="C81" s="187" t="s">
+      <c r="D81" s="230" t="s">
         <v>2221</v>
       </c>
-      <c r="D81" s="187" t="s">
+      <c r="E81" s="194" t="s">
         <v>2222</v>
       </c>
-      <c r="E81" s="325" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F81" s="186">
+      <c r="F81" s="195">
         <v>46139</v>
       </c>
-      <c r="G81" s="187" t="s">
+      <c r="G81" s="196" t="s">
         <v>2223</v>
       </c>
-      <c r="H81" s="188" t="s">
+      <c r="H81" s="197" t="s">
         <v>2224</v>
       </c>
-      <c r="I81" s="188" t="s">
-        <v>2222</v>
-      </c>
-      <c r="J81" s="189" t="s">
+      <c r="I81" s="197" t="s">
+        <v>2221</v>
+      </c>
+      <c r="J81" s="198" t="s">
         <v>2225</v>
       </c>
       <c r="K81" s="190"/>
       <c r="L81" s="190"/>
     </row>
     <row r="82" ht="25.5" customHeight="1">
-      <c r="A82" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B82" s="196" t="s">
+      <c r="A82" s="324" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B82" s="203" t="s">
         <v>2226</v>
       </c>
-      <c r="C82" s="196" t="s">
+      <c r="C82" s="203" t="s">
         <v>2227</v>
       </c>
-      <c r="D82" s="196" t="s">
+      <c r="D82" s="212" t="s">
         <v>2228</v>
       </c>
-      <c r="E82" s="327" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F82" s="195">
+      <c r="E82" s="194" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F82" s="202">
         <v>46139</v>
       </c>
-      <c r="G82" s="196" t="s">
-        <v>2229</v>
-      </c>
-      <c r="H82" s="197" t="s">
+      <c r="G82" s="203" t="s">
         <v>2230</v>
       </c>
-      <c r="I82" s="197" t="s">
+      <c r="H82" s="204" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I82" s="204" t="s">
         <v>2228</v>
       </c>
-      <c r="J82" s="198" t="s">
-        <v>2225</v>
+      <c r="J82" s="205" t="s">
+        <v>2232</v>
       </c>
       <c r="K82" s="190"/>
       <c r="L82" s="190"/>
     </row>
     <row r="83" ht="25.5" customHeight="1">
-      <c r="A83" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B83" s="203" t="s">
-        <v>2231</v>
-      </c>
-      <c r="C83" s="203" t="s">
-        <v>2232</v>
-      </c>
-      <c r="D83" s="203" t="s">
+      <c r="A83" s="324" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B83" s="196" t="s">
         <v>2233</v>
       </c>
-      <c r="E83" s="328" t="s">
-        <v>1520</v>
-      </c>
-      <c r="F83" s="202">
+      <c r="C83" s="196" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D83" s="230" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E83" s="194" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F83" s="195">
         <v>46139</v>
       </c>
-      <c r="G83" s="203" t="s">
-        <v>2234</v>
-      </c>
-      <c r="H83" s="204" t="s">
+      <c r="G83" s="196" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H83" s="197" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I83" s="197" t="s">
         <v>2235</v>
       </c>
-      <c r="I83" s="204" t="s">
-        <v>2233</v>
-      </c>
-      <c r="J83" s="205" t="s">
-        <v>2236</v>
+      <c r="J83" s="198" t="s">
+        <v>2239</v>
       </c>
       <c r="K83" s="190"/>
       <c r="L83" s="190"/>
     </row>
     <row r="84" ht="25.5" customHeight="1">
-      <c r="A84" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B84" s="196" t="s">
-        <v>2237</v>
-      </c>
-      <c r="C84" s="196" t="s">
-        <v>2238</v>
-      </c>
-      <c r="D84" s="196" t="s">
+      <c r="A84" s="324" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B84" s="203" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C84" s="203" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D84" s="212" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E84" s="194" t="s">
+        <v>2243</v>
+      </c>
+      <c r="F84" s="202">
+        <v>46139</v>
+      </c>
+      <c r="G84" s="203" t="s">
+        <v>2244</v>
+      </c>
+      <c r="H84" s="204" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I84" s="204" t="s">
+        <v>2242</v>
+      </c>
+      <c r="J84" s="205" t="s">
         <v>2239</v>
-      </c>
-      <c r="E84" s="327" t="s">
-        <v>1526</v>
-      </c>
-      <c r="F84" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G84" s="196" t="s">
-        <v>2240</v>
-      </c>
-      <c r="H84" s="197" t="s">
-        <v>2241</v>
-      </c>
-      <c r="I84" s="197" t="s">
-        <v>2239</v>
-      </c>
-      <c r="J84" s="198" t="s">
-        <v>2236</v>
       </c>
       <c r="K84" s="190"/>
       <c r="L84" s="190"/>
     </row>
     <row r="85" ht="25.5" customHeight="1">
-      <c r="A85" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B85" s="203" t="s">
-        <v>2242</v>
-      </c>
-      <c r="C85" s="203" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D85" s="203" t="s">
-        <v>2244</v>
-      </c>
-      <c r="E85" s="328" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F85" s="202">
+      <c r="A85" s="324" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B85" s="196" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C85" s="196" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D85" s="230" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E85" s="194" t="s">
+        <v>2249</v>
+      </c>
+      <c r="F85" s="195">
         <v>46139</v>
       </c>
-      <c r="G85" s="203" t="s">
-        <v>2245</v>
-      </c>
-      <c r="H85" s="204" t="s">
-        <v>2246</v>
-      </c>
-      <c r="I85" s="204" t="s">
-        <v>2244</v>
-      </c>
-      <c r="J85" s="205" t="s">
-        <v>2236</v>
+      <c r="G85" s="196" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H85" s="197" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I85" s="197" t="s">
+        <v>2248</v>
+      </c>
+      <c r="J85" s="198" t="s">
+        <v>2239</v>
       </c>
       <c r="K85" s="190"/>
       <c r="L85" s="190"/>
     </row>
     <row r="86" ht="25.5" customHeight="1">
-      <c r="A86" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B86" s="196" t="s">
-        <v>2247</v>
-      </c>
-      <c r="C86" s="196" t="s">
-        <v>2248</v>
-      </c>
-      <c r="D86" s="196" t="s">
-        <v>2249</v>
-      </c>
-      <c r="E86" s="327" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F86" s="195">
+      <c r="A86" s="208" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B86" s="203" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C86" s="203" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D86" s="212" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E86" s="194" t="s">
+        <v>2256</v>
+      </c>
+      <c r="F86" s="202">
         <v>46139</v>
       </c>
-      <c r="G86" s="196" t="s">
-        <v>2250</v>
-      </c>
-      <c r="H86" s="197" t="s">
-        <v>2251</v>
-      </c>
-      <c r="I86" s="197" t="s">
-        <v>2249</v>
-      </c>
-      <c r="J86" s="198" t="s">
-        <v>2236</v>
+      <c r="G86" s="203" t="s">
+        <v>2257</v>
+      </c>
+      <c r="H86" s="204" t="s">
+        <v>2258</v>
+      </c>
+      <c r="I86" s="204" t="s">
+        <v>2255</v>
+      </c>
+      <c r="J86" s="205" t="s">
+        <v>2259</v>
       </c>
       <c r="K86" s="190"/>
       <c r="L86" s="190"/>
     </row>
     <row r="87" ht="25.5" customHeight="1">
-      <c r="A87" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B87" s="203" t="s">
+      <c r="A87" s="325" t="s">
         <v>2252</v>
       </c>
-      <c r="C87" s="203" t="s">
-        <v>2253</v>
-      </c>
-      <c r="D87" s="203" t="s">
-        <v>2254</v>
-      </c>
-      <c r="E87" s="328" t="s">
-        <v>1544</v>
-      </c>
-      <c r="F87" s="202">
+      <c r="B87" s="196" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C87" s="196" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D87" s="230" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E87" s="194" t="s">
+        <v>2263</v>
+      </c>
+      <c r="F87" s="195">
         <v>46139</v>
       </c>
-      <c r="G87" s="203" t="s">
-        <v>2255</v>
-      </c>
-      <c r="H87" s="204" t="s">
-        <v>2256</v>
-      </c>
-      <c r="I87" s="204" t="s">
-        <v>2254</v>
-      </c>
-      <c r="J87" s="205" t="s">
-        <v>2236</v>
+      <c r="G87" s="196" t="s">
+        <v>2264</v>
+      </c>
+      <c r="H87" s="197" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I87" s="197" t="s">
+        <v>2262</v>
+      </c>
+      <c r="J87" s="198" t="s">
+        <v>2259</v>
       </c>
       <c r="K87" s="190"/>
       <c r="L87" s="190"/>
     </row>
     <row r="88" ht="25.5" customHeight="1">
-      <c r="A88" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B88" s="196" t="s">
-        <v>2257</v>
-      </c>
-      <c r="C88" s="196" t="s">
-        <v>2258</v>
-      </c>
-      <c r="D88" s="196" t="s">
+      <c r="A88" s="325" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B88" s="203" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C88" s="203" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D88" s="212" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E88" s="194" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F88" s="202">
+        <v>46139</v>
+      </c>
+      <c r="G88" s="203" t="s">
+        <v>2270</v>
+      </c>
+      <c r="H88" s="204" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I88" s="204" t="s">
+        <v>2268</v>
+      </c>
+      <c r="J88" s="205" t="s">
         <v>2259</v>
-      </c>
-      <c r="E88" s="327" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F88" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G88" s="196" t="s">
-        <v>2260</v>
-      </c>
-      <c r="H88" s="197" t="s">
-        <v>2261</v>
-      </c>
-      <c r="I88" s="197" t="s">
-        <v>2259</v>
-      </c>
-      <c r="J88" s="198" t="s">
-        <v>2236</v>
       </c>
       <c r="K88" s="190"/>
       <c r="L88" s="190"/>
     </row>
     <row r="89" ht="25.5" customHeight="1">
-      <c r="A89" s="326" t="s">
-        <v>2219</v>
-      </c>
-      <c r="B89" s="203" t="s">
-        <v>2262</v>
-      </c>
-      <c r="C89" s="203" t="s">
-        <v>2263</v>
-      </c>
-      <c r="D89" s="203" t="s">
-        <v>2264</v>
-      </c>
-      <c r="E89" s="329" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F89" s="202">
+      <c r="A89" s="325" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B89" s="196" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C89" s="196" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D89" s="230" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E89" s="194" t="s">
+        <v>2275</v>
+      </c>
+      <c r="F89" s="195">
         <v>46139</v>
       </c>
-      <c r="G89" s="203" t="s">
-        <v>2265</v>
-      </c>
-      <c r="H89" s="204" t="s">
-        <v>2266</v>
-      </c>
-      <c r="I89" s="204" t="s">
-        <v>2264</v>
-      </c>
-      <c r="J89" s="205" t="s">
-        <v>2267</v>
+      <c r="G89" s="196" t="s">
+        <v>2276</v>
+      </c>
+      <c r="H89" s="197" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I89" s="197" t="s">
+        <v>2274</v>
+      </c>
+      <c r="J89" s="198" t="s">
+        <v>2259</v>
       </c>
       <c r="K89" s="190"/>
       <c r="L89" s="190"/>
     </row>
     <row r="90" ht="25.5" customHeight="1">
-      <c r="A90" s="330" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B90" s="196" t="s">
-        <v>2268</v>
-      </c>
-      <c r="C90" s="196" t="s">
-        <v>2269</v>
-      </c>
-      <c r="D90" s="230" t="s">
-        <v>2270</v>
+      <c r="A90" s="325" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B90" s="203" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C90" s="203" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D90" s="212" t="s">
+        <v>2280</v>
       </c>
       <c r="E90" s="194" t="s">
-        <v>2271</v>
-      </c>
-      <c r="F90" s="195">
+        <v>2281</v>
+      </c>
+      <c r="F90" s="202">
         <v>46139</v>
       </c>
-      <c r="G90" s="196" t="s">
-        <v>2272</v>
-      </c>
-      <c r="H90" s="197" t="s">
-        <v>2273</v>
-      </c>
-      <c r="I90" s="197" t="s">
-        <v>2270</v>
-      </c>
-      <c r="J90" s="198" t="s">
-        <v>2274</v>
+      <c r="G90" s="203" t="s">
+        <v>2282</v>
+      </c>
+      <c r="H90" s="204" t="s">
+        <v>2283</v>
+      </c>
+      <c r="I90" s="204" t="s">
+        <v>2280</v>
+      </c>
+      <c r="J90" s="205" t="s">
+        <v>2259</v>
       </c>
       <c r="K90" s="190"/>
       <c r="L90" s="190"/>
     </row>
     <row r="91" ht="25.5" customHeight="1">
-      <c r="A91" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B91" s="203" t="s">
-        <v>2275</v>
-      </c>
-      <c r="C91" s="203" t="s">
-        <v>2276</v>
-      </c>
-      <c r="D91" s="212" t="s">
-        <v>2277</v>
+      <c r="A91" s="323" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B91" s="196" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C91" s="196" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D91" s="230" t="s">
+        <v>2285</v>
       </c>
       <c r="E91" s="194" t="s">
-        <v>2278</v>
-      </c>
-      <c r="F91" s="202">
+        <v>2287</v>
+      </c>
+      <c r="F91" s="195">
         <v>46139</v>
       </c>
-      <c r="G91" s="203" t="s">
-        <v>2279</v>
-      </c>
-      <c r="H91" s="204" t="s">
-        <v>2280</v>
-      </c>
-      <c r="I91" s="204" t="s">
-        <v>2277</v>
-      </c>
-      <c r="J91" s="205" t="s">
-        <v>2281</v>
+      <c r="G91" s="196" t="s">
+        <v>2288</v>
+      </c>
+      <c r="H91" s="197" t="s">
+        <v>2289</v>
+      </c>
+      <c r="I91" s="197" t="s">
+        <v>2285</v>
+      </c>
+      <c r="J91" s="198" t="s">
+        <v>2290</v>
       </c>
       <c r="K91" s="190"/>
       <c r="L91" s="190"/>
     </row>
     <row r="92" ht="25.5" customHeight="1">
-      <c r="A92" s="331" t="s">
-        <v>1619</v>
+      <c r="A92" s="324" t="s">
+        <v>2284</v>
       </c>
       <c r="B92" s="196" t="s">
-        <v>2282</v>
+        <v>2291</v>
       </c>
       <c r="C92" s="196" t="s">
-        <v>2283</v>
+        <v>2292</v>
       </c>
       <c r="D92" s="230" t="s">
-        <v>2284</v>
+        <v>1628</v>
       </c>
       <c r="E92" s="194" t="s">
-        <v>2285</v>
+        <v>1662</v>
       </c>
       <c r="F92" s="195">
         <v>46139</v>
       </c>
       <c r="G92" s="196" t="s">
-        <v>2286</v>
+        <v>2293</v>
       </c>
       <c r="H92" s="197" t="s">
-        <v>2287</v>
+        <v>2294</v>
       </c>
       <c r="I92" s="197" t="s">
-        <v>2284</v>
+        <v>1628</v>
       </c>
       <c r="J92" s="198" t="s">
-        <v>2281</v>
+        <v>2295</v>
       </c>
       <c r="K92" s="190"/>
       <c r="L92" s="190"/>
     </row>
     <row r="93" ht="25.5" customHeight="1">
-      <c r="A93" s="331" t="s">
-        <v>1619</v>
+      <c r="A93" s="324" t="s">
+        <v>2284</v>
       </c>
       <c r="B93" s="203" t="s">
-        <v>2288</v>
+        <v>2296</v>
       </c>
       <c r="C93" s="203" t="s">
-        <v>2289</v>
+        <v>2297</v>
       </c>
       <c r="D93" s="212" t="s">
-        <v>2290</v>
+        <v>2298</v>
       </c>
       <c r="E93" s="194" t="s">
-        <v>2291</v>
+        <v>2299</v>
       </c>
       <c r="F93" s="202">
         <v>46139</v>
       </c>
       <c r="G93" s="203" t="s">
-        <v>2292</v>
+        <v>2300</v>
       </c>
       <c r="H93" s="204" t="s">
-        <v>2293</v>
+        <v>2301</v>
       </c>
       <c r="I93" s="204" t="s">
-        <v>2290</v>
+        <v>2298</v>
       </c>
       <c r="J93" s="205" t="s">
-        <v>2281</v>
+        <v>2295</v>
       </c>
       <c r="K93" s="190"/>
       <c r="L93" s="190"/>
     </row>
     <row r="94" ht="25.5" customHeight="1">
-      <c r="A94" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B94" s="196" t="s">
-        <v>2294</v>
-      </c>
-      <c r="C94" s="196" t="s">
+      <c r="A94" s="324" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B94" s="203" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C94" s="203" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D94" s="212" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E94" s="194" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F94" s="202">
+        <v>46139</v>
+      </c>
+      <c r="G94" s="203" t="s">
+        <v>2306</v>
+      </c>
+      <c r="H94" s="204" t="s">
+        <v>2307</v>
+      </c>
+      <c r="I94" s="204" t="s">
+        <v>2304</v>
+      </c>
+      <c r="J94" s="205" t="s">
         <v>2295</v>
-      </c>
-      <c r="D94" s="230" t="s">
-        <v>2296</v>
-      </c>
-      <c r="E94" s="194" t="s">
-        <v>2297</v>
-      </c>
-      <c r="F94" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G94" s="196" t="s">
-        <v>2298</v>
-      </c>
-      <c r="H94" s="197" t="s">
-        <v>2299</v>
-      </c>
-      <c r="I94" s="197" t="s">
-        <v>2296</v>
-      </c>
-      <c r="J94" s="198" t="s">
-        <v>2281</v>
       </c>
       <c r="K94" s="190"/>
       <c r="L94" s="190"/>
     </row>
     <row r="95" ht="25.5" customHeight="1">
-      <c r="A95" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B95" s="203" t="s">
-        <v>2300</v>
-      </c>
-      <c r="C95" s="203" t="s">
-        <v>2301</v>
-      </c>
-      <c r="D95" s="212" t="s">
-        <v>2302</v>
+      <c r="A95" s="324" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B95" s="196" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C95" s="196" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D95" s="230" t="s">
+        <v>2310</v>
       </c>
       <c r="E95" s="194" t="s">
-        <v>2303</v>
-      </c>
-      <c r="F95" s="202">
+        <v>2311</v>
+      </c>
+      <c r="F95" s="195">
         <v>46139</v>
       </c>
-      <c r="G95" s="203" t="s">
-        <v>2304</v>
-      </c>
-      <c r="H95" s="204" t="s">
-        <v>2305</v>
-      </c>
-      <c r="I95" s="204" t="s">
-        <v>2302</v>
-      </c>
-      <c r="J95" s="205" t="s">
-        <v>2281</v>
+      <c r="G95" s="196" t="s">
+        <v>2312</v>
+      </c>
+      <c r="H95" s="197" t="s">
+        <v>2313</v>
+      </c>
+      <c r="I95" s="197" t="s">
+        <v>2310</v>
+      </c>
+      <c r="J95" s="198" t="s">
+        <v>2314</v>
       </c>
       <c r="K95" s="190"/>
       <c r="L95" s="190"/>
     </row>
     <row r="96" ht="25.5" customHeight="1">
-      <c r="A96" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B96" s="196" t="s">
-        <v>2306</v>
-      </c>
-      <c r="C96" s="196" t="s">
-        <v>2307</v>
-      </c>
-      <c r="D96" s="230" t="s">
-        <v>2308</v>
+      <c r="A96" s="324" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B96" s="326" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C96" s="326" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D96" s="229" t="s">
+        <v>2317</v>
       </c>
       <c r="E96" s="194" t="s">
-        <v>2309</v>
-      </c>
-      <c r="F96" s="195">
+        <v>2318</v>
+      </c>
+      <c r="F96" s="327">
         <v>46139</v>
       </c>
-      <c r="G96" s="196" t="s">
-        <v>2310</v>
-      </c>
-      <c r="H96" s="197" t="s">
-        <v>2311</v>
-      </c>
-      <c r="I96" s="197" t="s">
-        <v>2308</v>
-      </c>
-      <c r="J96" s="198" t="s">
-        <v>2312</v>
+      <c r="G96" s="326" t="s">
+        <v>2319</v>
+      </c>
+      <c r="H96" s="328" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I96" s="328" t="s">
+        <v>2317</v>
+      </c>
+      <c r="J96" s="329" t="s">
+        <v>2314</v>
       </c>
       <c r="K96" s="190"/>
       <c r="L96" s="190"/>
-    </row>
-    <row r="97" ht="25.5" customHeight="1">
-      <c r="A97" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B97" s="203" t="s">
-        <v>2313</v>
-      </c>
-      <c r="C97" s="203" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D97" s="212" t="s">
-        <v>2315</v>
-      </c>
-      <c r="E97" s="194" t="s">
-        <v>2316</v>
-      </c>
-      <c r="F97" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G97" s="203" t="s">
-        <v>2317</v>
-      </c>
-      <c r="H97" s="204" t="s">
-        <v>2318</v>
-      </c>
-      <c r="I97" s="204" t="s">
-        <v>2315</v>
-      </c>
-      <c r="J97" s="205" t="s">
-        <v>2312</v>
-      </c>
-      <c r="K97" s="190"/>
-      <c r="L97" s="190"/>
-    </row>
-    <row r="98" ht="25.5" customHeight="1">
-      <c r="A98" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B98" s="196" t="s">
-        <v>2319</v>
-      </c>
-      <c r="C98" s="196" t="s">
-        <v>2320</v>
-      </c>
-      <c r="D98" s="230" t="s">
-        <v>2321</v>
-      </c>
-      <c r="E98" s="194" t="s">
-        <v>2322</v>
-      </c>
-      <c r="F98" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G98" s="196" t="s">
-        <v>2323</v>
-      </c>
-      <c r="H98" s="197" t="s">
-        <v>2324</v>
-      </c>
-      <c r="I98" s="197" t="s">
-        <v>2321</v>
-      </c>
-      <c r="J98" s="198" t="s">
-        <v>2312</v>
-      </c>
-      <c r="K98" s="190"/>
-      <c r="L98" s="190"/>
-    </row>
-    <row r="99" ht="25.5" customHeight="1">
-      <c r="A99" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B99" s="203" t="s">
-        <v>2325</v>
-      </c>
-      <c r="C99" s="203" t="s">
-        <v>2326</v>
-      </c>
-      <c r="D99" s="212" t="s">
-        <v>2327</v>
-      </c>
-      <c r="E99" s="194" t="s">
-        <v>2328</v>
-      </c>
-      <c r="F99" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G99" s="203" t="s">
-        <v>2329</v>
-      </c>
-      <c r="H99" s="204" t="s">
-        <v>2330</v>
-      </c>
-      <c r="I99" s="204" t="s">
-        <v>2327</v>
-      </c>
-      <c r="J99" s="205" t="s">
-        <v>2312</v>
-      </c>
-      <c r="K99" s="190"/>
-      <c r="L99" s="190"/>
-    </row>
-    <row r="100" ht="25.5" customHeight="1">
-      <c r="A100" s="331" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B100" s="196" t="s">
-        <v>2331</v>
-      </c>
-      <c r="C100" s="196" t="s">
-        <v>2332</v>
-      </c>
-      <c r="D100" s="230" t="s">
-        <v>2333</v>
-      </c>
-      <c r="E100" s="194" t="s">
-        <v>2334</v>
-      </c>
-      <c r="F100" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G100" s="196" t="s">
-        <v>2335</v>
-      </c>
-      <c r="H100" s="197" t="s">
-        <v>2336</v>
-      </c>
-      <c r="I100" s="197" t="s">
-        <v>2333</v>
-      </c>
-      <c r="J100" s="198" t="s">
-        <v>2312</v>
-      </c>
-      <c r="K100" s="190"/>
-      <c r="L100" s="190"/>
-    </row>
-    <row r="101" ht="25.5" customHeight="1">
-      <c r="A101" s="208" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B101" s="203" t="s">
-        <v>2338</v>
-      </c>
-      <c r="C101" s="203" t="s">
-        <v>2339</v>
-      </c>
-      <c r="D101" s="212" t="s">
-        <v>2340</v>
-      </c>
-      <c r="E101" s="194" t="s">
-        <v>2341</v>
-      </c>
-      <c r="F101" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G101" s="203" t="s">
-        <v>2342</v>
-      </c>
-      <c r="H101" s="204" t="s">
-        <v>2343</v>
-      </c>
-      <c r="I101" s="204" t="s">
-        <v>2340</v>
-      </c>
-      <c r="J101" s="205" t="s">
-        <v>2344</v>
-      </c>
-      <c r="K101" s="190"/>
-      <c r="L101" s="190"/>
-    </row>
-    <row r="102" ht="25.5" customHeight="1">
-      <c r="A102" s="332" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B102" s="196" t="s">
-        <v>2345</v>
-      </c>
-      <c r="C102" s="196" t="s">
-        <v>2346</v>
-      </c>
-      <c r="D102" s="230" t="s">
-        <v>2347</v>
-      </c>
-      <c r="E102" s="194" t="s">
-        <v>2348</v>
-      </c>
-      <c r="F102" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G102" s="196" t="s">
-        <v>2349</v>
-      </c>
-      <c r="H102" s="197" t="s">
-        <v>2350</v>
-      </c>
-      <c r="I102" s="197" t="s">
-        <v>2347</v>
-      </c>
-      <c r="J102" s="198" t="s">
-        <v>2344</v>
-      </c>
-      <c r="K102" s="190"/>
-      <c r="L102" s="190"/>
-    </row>
-    <row r="103" ht="25.5" customHeight="1">
-      <c r="A103" s="332" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B103" s="203" t="s">
-        <v>2351</v>
-      </c>
-      <c r="C103" s="203" t="s">
-        <v>2352</v>
-      </c>
-      <c r="D103" s="212" t="s">
-        <v>2353</v>
-      </c>
-      <c r="E103" s="194" t="s">
-        <v>2354</v>
-      </c>
-      <c r="F103" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G103" s="203" t="s">
-        <v>2355</v>
-      </c>
-      <c r="H103" s="204" t="s">
-        <v>2356</v>
-      </c>
-      <c r="I103" s="204" t="s">
-        <v>2353</v>
-      </c>
-      <c r="J103" s="205" t="s">
-        <v>2344</v>
-      </c>
-      <c r="K103" s="190"/>
-      <c r="L103" s="190"/>
-    </row>
-    <row r="104" ht="25.5" customHeight="1">
-      <c r="A104" s="332" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B104" s="196" t="s">
-        <v>2357</v>
-      </c>
-      <c r="C104" s="196" t="s">
-        <v>2358</v>
-      </c>
-      <c r="D104" s="230" t="s">
-        <v>2359</v>
-      </c>
-      <c r="E104" s="194" t="s">
-        <v>2360</v>
-      </c>
-      <c r="F104" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G104" s="196" t="s">
-        <v>2361</v>
-      </c>
-      <c r="H104" s="197" t="s">
-        <v>2362</v>
-      </c>
-      <c r="I104" s="197" t="s">
-        <v>2359</v>
-      </c>
-      <c r="J104" s="198" t="s">
-        <v>2344</v>
-      </c>
-      <c r="K104" s="190"/>
-      <c r="L104" s="190"/>
-    </row>
-    <row r="105" ht="25.5" customHeight="1">
-      <c r="A105" s="332" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B105" s="203" t="s">
-        <v>2363</v>
-      </c>
-      <c r="C105" s="203" t="s">
-        <v>2364</v>
-      </c>
-      <c r="D105" s="212" t="s">
-        <v>2365</v>
-      </c>
-      <c r="E105" s="194" t="s">
-        <v>2366</v>
-      </c>
-      <c r="F105" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G105" s="203" t="s">
-        <v>2367</v>
-      </c>
-      <c r="H105" s="204" t="s">
-        <v>2368</v>
-      </c>
-      <c r="I105" s="204" t="s">
-        <v>2365</v>
-      </c>
-      <c r="J105" s="205" t="s">
-        <v>2344</v>
-      </c>
-      <c r="K105" s="190"/>
-      <c r="L105" s="190"/>
-    </row>
-    <row r="106" ht="25.5" customHeight="1">
-      <c r="A106" s="330" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B106" s="196" t="s">
-        <v>2370</v>
-      </c>
-      <c r="C106" s="196" t="s">
-        <v>2371</v>
-      </c>
-      <c r="D106" s="230" t="s">
-        <v>2372</v>
-      </c>
-      <c r="E106" s="194" t="s">
-        <v>2373</v>
-      </c>
-      <c r="F106" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G106" s="196" t="s">
-        <v>2374</v>
-      </c>
-      <c r="H106" s="197" t="s">
-        <v>2375</v>
-      </c>
-      <c r="I106" s="197" t="s">
-        <v>2372</v>
-      </c>
-      <c r="J106" s="198" t="s">
-        <v>2376</v>
-      </c>
-      <c r="K106" s="190"/>
-      <c r="L106" s="190"/>
-    </row>
-    <row r="107" ht="25.5" customHeight="1">
-      <c r="A107" s="331" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B107" s="203" t="s">
-        <v>2377</v>
-      </c>
-      <c r="C107" s="203" t="s">
-        <v>2378</v>
-      </c>
-      <c r="D107" s="212" t="s">
-        <v>2379</v>
-      </c>
-      <c r="E107" s="194" t="s">
-        <v>2380</v>
-      </c>
-      <c r="F107" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G107" s="203" t="s">
-        <v>2381</v>
-      </c>
-      <c r="H107" s="204" t="s">
-        <v>2382</v>
-      </c>
-      <c r="I107" s="204" t="s">
-        <v>2379</v>
-      </c>
-      <c r="J107" s="205" t="s">
-        <v>2376</v>
-      </c>
-      <c r="K107" s="190"/>
-      <c r="L107" s="190"/>
-    </row>
-    <row r="108" ht="25.5" customHeight="1">
-      <c r="A108" s="331" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B108" s="196" t="s">
-        <v>2383</v>
-      </c>
-      <c r="C108" s="196" t="s">
-        <v>2384</v>
-      </c>
-      <c r="D108" s="230" t="s">
-        <v>2385</v>
-      </c>
-      <c r="E108" s="194" t="s">
-        <v>2386</v>
-      </c>
-      <c r="F108" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G108" s="196" t="s">
-        <v>2387</v>
-      </c>
-      <c r="H108" s="197" t="s">
-        <v>2388</v>
-      </c>
-      <c r="I108" s="197" t="s">
-        <v>2385</v>
-      </c>
-      <c r="J108" s="198" t="s">
-        <v>2376</v>
-      </c>
-      <c r="K108" s="190"/>
-      <c r="L108" s="190"/>
-    </row>
-    <row r="109" ht="25.5" customHeight="1">
-      <c r="A109" s="331" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B109" s="203" t="s">
-        <v>2389</v>
-      </c>
-      <c r="C109" s="203" t="s">
-        <v>2390</v>
-      </c>
-      <c r="D109" s="212" t="s">
-        <v>2391</v>
-      </c>
-      <c r="E109" s="194" t="s">
-        <v>2392</v>
-      </c>
-      <c r="F109" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G109" s="203" t="s">
-        <v>2393</v>
-      </c>
-      <c r="H109" s="204" t="s">
-        <v>2394</v>
-      </c>
-      <c r="I109" s="204" t="s">
-        <v>2391</v>
-      </c>
-      <c r="J109" s="205" t="s">
-        <v>2395</v>
-      </c>
-      <c r="K109" s="190"/>
-      <c r="L109" s="190"/>
-    </row>
-    <row r="110" ht="25.5" customHeight="1">
-      <c r="A110" s="331" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B110" s="196" t="s">
-        <v>2396</v>
-      </c>
-      <c r="C110" s="196" t="s">
-        <v>2397</v>
-      </c>
-      <c r="D110" s="230" t="s">
-        <v>2398</v>
-      </c>
-      <c r="E110" s="194" t="s">
-        <v>2399</v>
-      </c>
-      <c r="F110" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G110" s="196" t="s">
-        <v>2400</v>
-      </c>
-      <c r="H110" s="197" t="s">
-        <v>2401</v>
-      </c>
-      <c r="I110" s="197" t="s">
-        <v>2398</v>
-      </c>
-      <c r="J110" s="198" t="s">
-        <v>2395</v>
-      </c>
-      <c r="K110" s="190"/>
-      <c r="L110" s="190"/>
-    </row>
-    <row r="111" ht="25.5" customHeight="1">
-      <c r="A111" s="331" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B111" s="203" t="s">
-        <v>2402</v>
-      </c>
-      <c r="C111" s="203" t="s">
-        <v>2403</v>
-      </c>
-      <c r="D111" s="212" t="s">
-        <v>2404</v>
-      </c>
-      <c r="E111" s="194" t="s">
-        <v>2405</v>
-      </c>
-      <c r="F111" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G111" s="203" t="s">
-        <v>2406</v>
-      </c>
-      <c r="H111" s="204" t="s">
-        <v>2407</v>
-      </c>
-      <c r="I111" s="204" t="s">
-        <v>2404</v>
-      </c>
-      <c r="J111" s="205" t="s">
-        <v>2395</v>
-      </c>
-      <c r="K111" s="190"/>
-      <c r="L111" s="190"/>
-    </row>
-    <row r="112" ht="25.5" customHeight="1">
-      <c r="A112" s="330" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B112" s="196" t="s">
-        <v>2409</v>
-      </c>
-      <c r="C112" s="196" t="s">
-        <v>2410</v>
-      </c>
-      <c r="D112" s="230" t="s">
-        <v>2409</v>
-      </c>
-      <c r="E112" s="194" t="s">
-        <v>2411</v>
-      </c>
-      <c r="F112" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G112" s="196" t="s">
-        <v>2412</v>
-      </c>
-      <c r="H112" s="197" t="s">
-        <v>2413</v>
-      </c>
-      <c r="I112" s="197" t="s">
-        <v>2409</v>
-      </c>
-      <c r="J112" s="198" t="s">
-        <v>2414</v>
-      </c>
-      <c r="K112" s="190"/>
-      <c r="L112" s="190"/>
-    </row>
-    <row r="113" ht="25.5" customHeight="1">
-      <c r="A113" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B113" s="203" t="s">
-        <v>2415</v>
-      </c>
-      <c r="C113" s="203" t="s">
-        <v>2416</v>
-      </c>
-      <c r="D113" s="212" t="s">
-        <v>2417</v>
-      </c>
-      <c r="E113" s="194" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F113" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G113" s="203" t="s">
-        <v>2418</v>
-      </c>
-      <c r="H113" s="204" t="s">
-        <v>2419</v>
-      </c>
-      <c r="I113" s="204" t="s">
-        <v>2417</v>
-      </c>
-      <c r="J113" s="205" t="s">
-        <v>2420</v>
-      </c>
-      <c r="K113" s="190"/>
-      <c r="L113" s="190"/>
-    </row>
-    <row r="114" ht="25.5" customHeight="1">
-      <c r="A114" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B114" s="196" t="s">
-        <v>2421</v>
-      </c>
-      <c r="C114" s="196" t="s">
-        <v>2422</v>
-      </c>
-      <c r="D114" s="230" t="s">
-        <v>1628</v>
-      </c>
-      <c r="E114" s="194" t="s">
-        <v>1662</v>
-      </c>
-      <c r="F114" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G114" s="196" t="s">
-        <v>2423</v>
-      </c>
-      <c r="H114" s="197" t="s">
-        <v>2424</v>
-      </c>
-      <c r="I114" s="197" t="s">
-        <v>1628</v>
-      </c>
-      <c r="J114" s="198" t="s">
-        <v>2420</v>
-      </c>
-      <c r="K114" s="190"/>
-      <c r="L114" s="190"/>
-    </row>
-    <row r="115" ht="25.5" customHeight="1">
-      <c r="A115" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B115" s="203" t="s">
-        <v>2425</v>
-      </c>
-      <c r="C115" s="203" t="s">
-        <v>2426</v>
-      </c>
-      <c r="D115" s="212" t="s">
-        <v>2427</v>
-      </c>
-      <c r="E115" s="194" t="s">
-        <v>2428</v>
-      </c>
-      <c r="F115" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G115" s="203" t="s">
-        <v>2429</v>
-      </c>
-      <c r="H115" s="204" t="s">
-        <v>2430</v>
-      </c>
-      <c r="I115" s="204" t="s">
-        <v>2427</v>
-      </c>
-      <c r="J115" s="205" t="s">
-        <v>2420</v>
-      </c>
-      <c r="K115" s="190"/>
-      <c r="L115" s="190"/>
-    </row>
-    <row r="116" ht="25.5" customHeight="1">
-      <c r="A116" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B116" s="196" t="s">
-        <v>2431</v>
-      </c>
-      <c r="C116" s="196" t="s">
-        <v>2432</v>
-      </c>
-      <c r="D116" s="230" t="s">
-        <v>2433</v>
-      </c>
-      <c r="E116" s="194" t="s">
-        <v>2434</v>
-      </c>
-      <c r="F116" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G116" s="196" t="s">
-        <v>2435</v>
-      </c>
-      <c r="H116" s="197" t="s">
-        <v>2436</v>
-      </c>
-      <c r="I116" s="197" t="s">
-        <v>2433</v>
-      </c>
-      <c r="J116" s="198" t="s">
-        <v>2420</v>
-      </c>
-      <c r="K116" s="190"/>
-      <c r="L116" s="190"/>
-    </row>
-    <row r="117" ht="25.5" customHeight="1">
-      <c r="A117" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B117" s="203" t="s">
-        <v>2437</v>
-      </c>
-      <c r="C117" s="203" t="s">
-        <v>2438</v>
-      </c>
-      <c r="D117" s="212" t="s">
-        <v>2439</v>
-      </c>
-      <c r="E117" s="194" t="s">
-        <v>2440</v>
-      </c>
-      <c r="F117" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G117" s="203" t="s">
-        <v>2441</v>
-      </c>
-      <c r="H117" s="204" t="s">
-        <v>2442</v>
-      </c>
-      <c r="I117" s="204" t="s">
-        <v>2439</v>
-      </c>
-      <c r="J117" s="205" t="s">
-        <v>2420</v>
-      </c>
-      <c r="K117" s="190"/>
-      <c r="L117" s="190"/>
-    </row>
-    <row r="118" ht="25.5" customHeight="1">
-      <c r="A118" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B118" s="196" t="s">
-        <v>2443</v>
-      </c>
-      <c r="C118" s="196" t="s">
-        <v>2444</v>
-      </c>
-      <c r="D118" s="230" t="s">
-        <v>2445</v>
-      </c>
-      <c r="E118" s="194" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F118" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G118" s="196" t="s">
-        <v>2447</v>
-      </c>
-      <c r="H118" s="197" t="s">
-        <v>2448</v>
-      </c>
-      <c r="I118" s="197" t="s">
-        <v>2445</v>
-      </c>
-      <c r="J118" s="198" t="s">
-        <v>2449</v>
-      </c>
-      <c r="K118" s="190"/>
-      <c r="L118" s="190"/>
-    </row>
-    <row r="119" ht="25.5" customHeight="1">
-      <c r="A119" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B119" s="235" t="s">
-        <v>2450</v>
-      </c>
-      <c r="C119" s="235" t="s">
-        <v>2451</v>
-      </c>
-      <c r="D119" s="233" t="s">
-        <v>2452</v>
-      </c>
-      <c r="E119" s="194" t="s">
-        <v>2453</v>
-      </c>
-      <c r="F119" s="234">
-        <v>46139</v>
-      </c>
-      <c r="G119" s="235" t="s">
-        <v>2454</v>
-      </c>
-      <c r="H119" s="236" t="s">
-        <v>2455</v>
-      </c>
-      <c r="I119" s="236" t="s">
-        <v>2452</v>
-      </c>
-      <c r="J119" s="237" t="s">
-        <v>2456</v>
-      </c>
-      <c r="K119" s="190"/>
-      <c r="L119" s="190"/>
-    </row>
-    <row r="120" ht="25.5" customHeight="1">
-      <c r="A120" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B120" s="203" t="s">
-        <v>2457</v>
-      </c>
-      <c r="C120" s="203" t="s">
-        <v>2458</v>
-      </c>
-      <c r="D120" s="212" t="s">
-        <v>2459</v>
-      </c>
-      <c r="E120" s="194" t="s">
-        <v>2460</v>
-      </c>
-      <c r="F120" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G120" s="203" t="s">
-        <v>2461</v>
-      </c>
-      <c r="H120" s="204" t="s">
-        <v>2462</v>
-      </c>
-      <c r="I120" s="204" t="s">
-        <v>2459</v>
-      </c>
-      <c r="J120" s="205" t="s">
-        <v>2463</v>
-      </c>
-      <c r="K120" s="190"/>
-      <c r="L120" s="190"/>
-    </row>
-    <row r="121" ht="25.5" customHeight="1">
-      <c r="A121" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B121" s="196" t="s">
-        <v>2464</v>
-      </c>
-      <c r="C121" s="196" t="s">
-        <v>2465</v>
-      </c>
-      <c r="D121" s="230" t="s">
-        <v>2466</v>
-      </c>
-      <c r="E121" s="194" t="s">
-        <v>2467</v>
-      </c>
-      <c r="F121" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G121" s="196" t="s">
-        <v>2468</v>
-      </c>
-      <c r="H121" s="197" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I121" s="197" t="s">
-        <v>2466</v>
-      </c>
-      <c r="J121" s="198" t="s">
-        <v>2470</v>
-      </c>
-      <c r="K121" s="190"/>
-      <c r="L121" s="190"/>
-    </row>
-    <row r="122" ht="25.5" customHeight="1">
-      <c r="A122" s="331" t="s">
-        <v>2408</v>
-      </c>
-      <c r="B122" s="333" t="s">
-        <v>2471</v>
-      </c>
-      <c r="C122" s="333" t="s">
-        <v>2472</v>
-      </c>
-      <c r="D122" s="229" t="s">
-        <v>2473</v>
-      </c>
-      <c r="E122" s="194" t="s">
-        <v>2474</v>
-      </c>
-      <c r="F122" s="334">
-        <v>46139</v>
-      </c>
-      <c r="G122" s="333" t="s">
-        <v>2475</v>
-      </c>
-      <c r="H122" s="335" t="s">
-        <v>2476</v>
-      </c>
-      <c r="I122" s="335" t="s">
-        <v>2473</v>
-      </c>
-      <c r="J122" s="336" t="s">
-        <v>2449</v>
-      </c>
-      <c r="K122" s="190"/>
-      <c r="L122" s="190"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26077,58 +25557,6 @@
     <hyperlink r:id="rId94" ref="I95" tooltip=""/>
     <hyperlink r:id="rId95" ref="H96" tooltip=""/>
     <hyperlink r:id="rId95" ref="I96" tooltip=""/>
-    <hyperlink r:id="rId96" ref="H97" tooltip=""/>
-    <hyperlink r:id="rId96" ref="I97" tooltip=""/>
-    <hyperlink r:id="rId97" ref="H98" tooltip=""/>
-    <hyperlink r:id="rId97" ref="I98" tooltip=""/>
-    <hyperlink r:id="rId98" ref="H99" tooltip=""/>
-    <hyperlink r:id="rId98" ref="I99" tooltip=""/>
-    <hyperlink r:id="rId99" ref="H100" tooltip=""/>
-    <hyperlink r:id="rId99" ref="I100" tooltip=""/>
-    <hyperlink r:id="rId100" ref="H101" tooltip=""/>
-    <hyperlink r:id="rId100" ref="I101" tooltip=""/>
-    <hyperlink r:id="rId101" ref="H102" tooltip=""/>
-    <hyperlink r:id="rId101" ref="I102" tooltip=""/>
-    <hyperlink r:id="rId102" ref="H103" tooltip=""/>
-    <hyperlink r:id="rId102" ref="I103" tooltip=""/>
-    <hyperlink r:id="rId103" ref="H104" tooltip=""/>
-    <hyperlink r:id="rId103" ref="I104" tooltip=""/>
-    <hyperlink r:id="rId104" ref="H105" tooltip=""/>
-    <hyperlink r:id="rId104" ref="I105" tooltip=""/>
-    <hyperlink r:id="rId105" ref="H106" tooltip=""/>
-    <hyperlink r:id="rId105" ref="I106" tooltip=""/>
-    <hyperlink r:id="rId106" ref="H107" tooltip=""/>
-    <hyperlink r:id="rId106" ref="I107" tooltip=""/>
-    <hyperlink r:id="rId107" ref="H108" tooltip=""/>
-    <hyperlink r:id="rId107" ref="I108" tooltip=""/>
-    <hyperlink r:id="rId108" ref="H109" tooltip=""/>
-    <hyperlink r:id="rId108" ref="I109" tooltip=""/>
-    <hyperlink r:id="rId109" ref="H110" tooltip=""/>
-    <hyperlink r:id="rId109" ref="I110" tooltip=""/>
-    <hyperlink r:id="rId110" ref="H111" tooltip=""/>
-    <hyperlink r:id="rId110" ref="I111" tooltip=""/>
-    <hyperlink r:id="rId111" ref="H112" tooltip=""/>
-    <hyperlink r:id="rId111" ref="I112" tooltip=""/>
-    <hyperlink r:id="rId112" ref="H113" tooltip=""/>
-    <hyperlink r:id="rId112" ref="I113" tooltip=""/>
-    <hyperlink r:id="rId113" ref="H114" tooltip=""/>
-    <hyperlink r:id="rId113" ref="I114" tooltip=""/>
-    <hyperlink r:id="rId114" ref="H115" tooltip=""/>
-    <hyperlink r:id="rId114" ref="I115" tooltip=""/>
-    <hyperlink r:id="rId115" ref="H116" tooltip=""/>
-    <hyperlink r:id="rId115" ref="I116" tooltip=""/>
-    <hyperlink r:id="rId116" ref="H117" tooltip=""/>
-    <hyperlink r:id="rId116" ref="I117" tooltip=""/>
-    <hyperlink r:id="rId117" ref="H118" tooltip=""/>
-    <hyperlink r:id="rId117" ref="I118" tooltip=""/>
-    <hyperlink r:id="rId118" ref="H119" tooltip=""/>
-    <hyperlink r:id="rId118" ref="I119" tooltip=""/>
-    <hyperlink r:id="rId119" ref="H120" tooltip=""/>
-    <hyperlink r:id="rId119" ref="I120" tooltip=""/>
-    <hyperlink r:id="rId120" ref="H121" tooltip=""/>
-    <hyperlink r:id="rId120" ref="I121" tooltip=""/>
-    <hyperlink r:id="rId121" ref="H122" tooltip=""/>
-    <hyperlink r:id="rId121" ref="I122" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -26156,7 +25584,7 @@
         <v>1725</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2477</v>
+        <v>2321</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -26168,124 +25596,124 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2478</v>
+        <v>2322</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2479</v>
+        <v>2323</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2480</v>
+        <v>2324</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>2481</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="2" ht="19.5">
       <c r="A2" s="43" t="s">
         <v>1744</v>
       </c>
-      <c r="B2" s="337" t="s">
+      <c r="B2" s="330" t="s">
         <v>1776</v>
       </c>
-      <c r="C2" s="337" t="s">
+      <c r="C2" s="330" t="s">
         <v>1752</v>
       </c>
-      <c r="D2" s="337" t="s">
+      <c r="D2" s="330" t="s">
         <v>1836</v>
       </c>
-      <c r="E2" s="338" t="s">
-        <v>2482</v>
-      </c>
-      <c r="F2" s="339" t="s">
-        <v>2483</v>
-      </c>
-      <c r="G2" s="340">
+      <c r="E2" s="331" t="s">
+        <v>2326</v>
+      </c>
+      <c r="F2" s="332" t="s">
+        <v>2327</v>
+      </c>
+      <c r="G2" s="333">
         <v>45986</v>
       </c>
-      <c r="H2" s="337" t="s">
-        <v>2484</v>
-      </c>
-      <c r="I2" s="341" t="s">
-        <v>2485</v>
-      </c>
-      <c r="J2" s="342" t="str">
+      <c r="H2" s="330" t="s">
+        <v>2328</v>
+      </c>
+      <c r="I2" s="334" t="s">
+        <v>2329</v>
+      </c>
+      <c r="J2" s="335" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_/view?usp=drivesdk","Mr. Abhishek Singh-Mr. Aniket Paul-Rafi -Specialization - Cyber Security and Forensics - I")</f>
         <v xml:space="preserve">Mr. Abhishek Singh-Mr. Aniket Paul-Rafi -Specialization - Cyber Security and Forensics - I</v>
       </c>
-      <c r="K2" s="343" t="s">
-        <v>2486</v>
+      <c r="K2" s="336" t="s">
+        <v>2330</v>
       </c>
     </row>
     <row r="3" ht="19.5">
       <c r="A3" s="43" t="s">
         <v>1744</v>
       </c>
-      <c r="B3" s="337" t="s">
-        <v>2487</v>
-      </c>
-      <c r="C3" s="337" t="s">
-        <v>2488</v>
-      </c>
-      <c r="D3" s="337" t="s">
-        <v>2489</v>
-      </c>
-      <c r="E3" s="338" t="s">
-        <v>2490</v>
-      </c>
-      <c r="F3" s="339" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G3" s="344">
+      <c r="B3" s="330" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C3" s="330" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D3" s="330" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E3" s="331" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F3" s="332" t="s">
+        <v>2335</v>
+      </c>
+      <c r="G3" s="337">
         <v>45986</v>
       </c>
-      <c r="H3" s="337" t="s">
-        <v>2492</v>
-      </c>
-      <c r="I3" s="341" t="s">
-        <v>2493</v>
-      </c>
-      <c r="J3" s="342" t="str">
+      <c r="H3" s="330" t="s">
+        <v>2336</v>
+      </c>
+      <c r="I3" s="334" t="s">
+        <v>2337</v>
+      </c>
+      <c r="J3" s="335" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu/view?usp=drivesdk","Ms. Renuka Parmar-Mr. Gaurav Kumar-Ms. Priya Soni-Specialization - Full Stack Web Development - I")</f>
         <v xml:space="preserve">Ms. Renuka Parmar-Mr. Gaurav Kumar-Ms. Priya Soni-Specialization - Full Stack Web Development - I</v>
       </c>
-      <c r="K3" s="343" t="s">
-        <v>2486</v>
+      <c r="K3" s="336" t="s">
+        <v>2330</v>
       </c>
     </row>
     <row r="4" ht="19.5">
-      <c r="A4" s="345" t="s">
+      <c r="A4" s="338" t="s">
         <v>153</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>2494</v>
+        <v>2338</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2495</v>
+        <v>2339</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>2496</v>
+        <v>2340</v>
       </c>
       <c r="E4" s="268" t="s">
-        <v>2497</v>
+        <v>2341</v>
       </c>
       <c r="F4" s="269" t="s">
-        <v>2498</v>
-      </c>
-      <c r="G4" s="346">
+        <v>2342</v>
+      </c>
+      <c r="G4" s="339">
         <v>46000</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2499</v>
+        <v>2343</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>2500</v>
+        <v>2344</v>
       </c>
       <c r="J4" s="29" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X/view?usp=drivesdk","Mr. Satish Chauhan-Mr. Meet Soni -Dr. Shubhrajyoti Kundu-Electrical and Electronics Engineering")</f>
         <v xml:space="preserve">Mr. Satish Chauhan-Mr. Meet Soni -Dr. Shubhrajyoti Kundu-Electrical and Electronics Engineering</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>2501</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="5" ht="19.5">
@@ -26293,359 +25721,359 @@
         <v>153</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2502</v>
+        <v>2346</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2503</v>
+        <v>2347</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>1877</v>
       </c>
       <c r="E5" s="268" t="s">
-        <v>2504</v>
+        <v>2348</v>
       </c>
       <c r="F5" s="269" t="s">
-        <v>2505</v>
-      </c>
-      <c r="G5" s="346">
+        <v>2349</v>
+      </c>
+      <c r="G5" s="339">
         <v>46049</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>2506</v>
+        <v>2350</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>2507</v>
+        <v>2351</v>
       </c>
       <c r="J5" s="29" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z/view?usp=drivesdk","Dr. Kartik Pandya-Mr. Mahit Jain-Mr. Nishith Shahu-Basic Electrical Engineering")</f>
         <v xml:space="preserve">Dr. Kartik Pandya-Mr. Mahit Jain-Mr. Nishith Shahu-Basic Electrical Engineering</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>2501</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="6" ht="19.5">
-      <c r="A6" s="347" t="s">
+      <c r="A6" s="340" t="s">
         <v>153</v>
       </c>
       <c r="B6" s="268" t="s">
-        <v>2508</v>
+        <v>2352</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>2509</v>
+        <v>2353</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>2510</v>
+        <v>2354</v>
       </c>
       <c r="E6" s="268" t="s">
-        <v>2511</v>
+        <v>2355</v>
       </c>
       <c r="F6" s="269" t="s">
-        <v>2512</v>
-      </c>
-      <c r="G6" s="346">
+        <v>2356</v>
+      </c>
+      <c r="G6" s="339">
         <v>46112</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2513</v>
+        <v>2357</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>2514</v>
+        <v>2358</v>
       </c>
       <c r="J6" s="29" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk/view?usp=drivesdk","Mr. Ankitsinh Zala- Ms. Divya Garg-Ms. Niti Shah-CVPDE")</f>
         <v xml:space="preserve">Mr. Ankitsinh Zala- Ms. Divya Garg-Ms. Niti Shah-CVPDE</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>2501</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="7" ht="38.25">
-      <c r="A7" s="348" t="s">
+      <c r="A7" s="341" t="s">
         <v>231</v>
       </c>
-      <c r="B7" s="349" t="s">
-        <v>2515</v>
+      <c r="B7" s="342" t="s">
+        <v>2359</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>2516</v>
+        <v>2360</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>2517</v>
+        <v>2361</v>
       </c>
       <c r="E7" s="274" t="s">
-        <v>2518</v>
+        <v>2362</v>
       </c>
       <c r="F7" s="275" t="s">
-        <v>2519</v>
+        <v>2363</v>
       </c>
       <c r="G7" s="38">
         <v>46045</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>2520</v>
+        <v>2364</v>
       </c>
       <c r="I7" s="40" t="s">
-        <v>2521</v>
+        <v>2365</v>
       </c>
       <c r="J7" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH/view?usp=drivesdk","Mr. Purvesh Valanad- Mr.  Mujahid Mirchiwala- Mr. Gaurav Sahu-PC-1 (D.C Circuit)")</f>
         <v xml:space="preserve">Mr. Purvesh Valanad- Mr.  Mujahid Mirchiwala- Mr. Gaurav Sahu-PC-1 (D.C Circuit)</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>2522</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="8" ht="38.25">
-      <c r="A8" s="348" t="s">
+      <c r="A8" s="341" t="s">
         <v>231</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>2523</v>
+        <v>2367</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>2524</v>
+        <v>2368</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>2525</v>
+        <v>2369</v>
       </c>
       <c r="E8" s="274" t="s">
-        <v>2526</v>
+        <v>2370</v>
       </c>
       <c r="F8" s="275" t="s">
-        <v>2527</v>
+        <v>2371</v>
       </c>
       <c r="G8" s="38">
         <v>46045</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>2528</v>
+        <v>2372</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>2529</v>
+        <v>2373</v>
       </c>
       <c r="J8" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb/view?usp=drivesdk","Mr. Mayank Vyas-Mr.  Ankit Patel -Mr.  Nishant Hadiya-Introduction to Electrical Safety &amp; Management")</f>
         <v xml:space="preserve">Mr. Mayank Vyas-Mr.  Ankit Patel -Mr.  Nishant Hadiya-Introduction to Electrical Safety &amp; Management</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>2530</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="9" ht="25.5">
-      <c r="A9" s="348" t="s">
+      <c r="A9" s="341" t="s">
         <v>231</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>2531</v>
+        <v>2375</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>2532</v>
+        <v>2376</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>1940</v>
       </c>
       <c r="E9" s="274" t="s">
-        <v>2533</v>
+        <v>2377</v>
       </c>
       <c r="F9" s="275" t="s">
-        <v>2534</v>
+        <v>2378</v>
       </c>
       <c r="G9" s="38">
         <v>46045</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>2535</v>
+        <v>2379</v>
       </c>
       <c r="I9" s="40" t="s">
-        <v>2536</v>
+        <v>2380</v>
       </c>
       <c r="J9" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk/view?usp=drivesdk","Ms. Hetal Prajapati- Mr. Pavez Vasovala -Mr. Apoorv Prajapati-Fundamental of Electrical Engineering")</f>
         <v xml:space="preserve">Ms. Hetal Prajapati- Mr. Pavez Vasovala -Mr. Apoorv Prajapati-Fundamental of Electrical Engineering</v>
       </c>
       <c r="K9" s="42" t="s">
-        <v>2530</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="10" ht="38.25">
-      <c r="A10" s="350" t="s">
+      <c r="A10" s="343" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="349" t="s">
-        <v>2537</v>
+      <c r="B10" s="342" t="s">
+        <v>2381</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>2538</v>
+        <v>2382</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>2539</v>
+        <v>2383</v>
       </c>
       <c r="E10" s="274" t="s">
-        <v>2540</v>
+        <v>2384</v>
       </c>
       <c r="F10" s="275" t="s">
-        <v>2541</v>
+        <v>2385</v>
       </c>
       <c r="G10" s="38">
         <v>46045</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>2542</v>
+        <v>2386</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>2543</v>
+        <v>2387</v>
       </c>
       <c r="J10" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD/view?usp=drivesdk","Mr. Krunal Kayasth-Mr.Jayesh Mahant-Mr.Manthan Thakkar-Engineering Graphics ")</f>
         <v xml:space="preserve">Mr. Krunal Kayasth-Mr.Jayesh Mahant-Mr.Manthan Thakkar-Engineering Graphics </v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>2530</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="11" ht="38.25">
-      <c r="A11" s="350" t="s">
+      <c r="A11" s="343" t="s">
         <v>231</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>2544</v>
+        <v>2388</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>2545</v>
+        <v>2389</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>2546</v>
+        <v>2390</v>
       </c>
       <c r="E11" s="274" t="s">
-        <v>2547</v>
+        <v>2391</v>
       </c>
       <c r="F11" s="275" t="s">
-        <v>2548</v>
+        <v>2392</v>
       </c>
       <c r="G11" s="38">
         <v>46045</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>2549</v>
+        <v>2393</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>2550</v>
+        <v>2394</v>
       </c>
       <c r="J11" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE/view?usp=drivesdk","Ms. Bhumi Bhoi-Mr. Piyush Mali-Ms. Shreen Gazala-Internet Of Things")</f>
         <v xml:space="preserve">Ms. Bhumi Bhoi-Mr. Piyush Mali-Ms. Shreen Gazala-Internet Of Things</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>2530</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="12" ht="38.25">
-      <c r="A12" s="350" t="s">
+      <c r="A12" s="343" t="s">
         <v>231</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>2551</v>
+        <v>2395</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>2552</v>
+        <v>2396</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>2553</v>
+        <v>2397</v>
       </c>
       <c r="E12" s="274" t="s">
-        <v>2554</v>
+        <v>2398</v>
       </c>
       <c r="F12" s="275" t="s">
-        <v>2555</v>
+        <v>2399</v>
       </c>
       <c r="G12" s="38">
         <v>46045</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>2556</v>
+        <v>2400</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>2557</v>
+        <v>2401</v>
       </c>
       <c r="J12" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ/view?usp=drivesdk","Mr. Ashish Pandey-Ms. Prachi Patel-Mr. Ravi Bhardwaj-Information Security")</f>
         <v xml:space="preserve">Mr. Ashish Pandey-Ms. Prachi Patel-Mr. Ravi Bhardwaj-Information Security</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>2530</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="13" ht="38.25">
-      <c r="A13" s="350" t="s">
+      <c r="A13" s="343" t="s">
         <v>231</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>2558</v>
+        <v>2402</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>2559</v>
+        <v>2403</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>2560</v>
+        <v>2404</v>
       </c>
       <c r="E13" s="274" t="s">
-        <v>2561</v>
+        <v>2405</v>
       </c>
       <c r="F13" s="275" t="s">
-        <v>2562</v>
+        <v>2406</v>
       </c>
       <c r="G13" s="38">
         <v>46045</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>2563</v>
+        <v>2407</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>2564</v>
+        <v>2408</v>
       </c>
       <c r="J13" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP/view?usp=drivesdk","Mr. Kausal kalariya-Ms. Bipasha Mandal-Ms. Hemali Nimavat-operating system ")</f>
         <v xml:space="preserve">Mr. Kausal kalariya-Ms. Bipasha Mandal-Ms. Hemali Nimavat-operating system </v>
       </c>
       <c r="K13" s="42" t="s">
-        <v>2530</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="14" ht="38.25">
-      <c r="A14" s="351" t="s">
+      <c r="A14" s="344" t="s">
         <v>231</v>
       </c>
-      <c r="B14" s="352" t="s">
-        <v>2565</v>
+      <c r="B14" s="345" t="s">
+        <v>2409</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2566</v>
+        <v>2410</v>
       </c>
       <c r="D14" s="274" t="s">
-        <v>2567</v>
+        <v>2411</v>
       </c>
       <c r="E14" s="274" t="s">
-        <v>2568</v>
+        <v>2412</v>
       </c>
       <c r="F14" s="275" t="s">
-        <v>2569</v>
+        <v>2413</v>
       </c>
       <c r="G14" s="38">
         <v>46045</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>2570</v>
+        <v>2414</v>
       </c>
       <c r="I14" s="40" t="s">
-        <v>2571</v>
+        <v>2415</v>
       </c>
       <c r="J14" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx/view?usp=drivesdk","Ms. Mansi Rana-Ms. Kavita Parmar-Mr. Bankim Parmar-Object Oriented Programming with C++")</f>
         <v xml:space="preserve">Ms. Mansi Rana-Ms. Kavita Parmar-Mr. Bankim Parmar-Object Oriented Programming with C++</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>2572</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="15" ht="63.75">
@@ -26653,35 +26081,35 @@
         <v>1988</v>
       </c>
       <c r="B15" s="302" t="s">
-        <v>2573</v>
+        <v>2417</v>
       </c>
       <c r="C15" s="302" t="s">
-        <v>2574</v>
+        <v>2418</v>
       </c>
       <c r="D15" s="302" t="s">
-        <v>2575</v>
+        <v>2419</v>
       </c>
       <c r="E15" s="295" t="s">
-        <v>2576</v>
+        <v>2420</v>
       </c>
       <c r="F15" s="297" t="s">
-        <v>2577</v>
-      </c>
-      <c r="G15" s="353">
+        <v>2421</v>
+      </c>
+      <c r="G15" s="346">
         <v>45995</v>
       </c>
-      <c r="H15" s="354" t="s">
-        <v>2578</v>
-      </c>
-      <c r="I15" s="355" t="s">
-        <v>2579</v>
-      </c>
-      <c r="J15" s="356" t="str">
+      <c r="H15" s="347" t="s">
+        <v>2422</v>
+      </c>
+      <c r="I15" s="348" t="s">
+        <v>2423</v>
+      </c>
+      <c r="J15" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx/view?usp=drivesdk","Ms. DEVANSHI THAKKAR-Ms. AMITA TAILOR-Ms. SHILPA KHANT-Web Design and Development")</f>
         <v xml:space="preserve">Ms. DEVANSHI THAKKAR-Ms. AMITA TAILOR-Ms. SHILPA KHANT-Web Design and Development</v>
       </c>
-      <c r="K15" s="357" t="s">
-        <v>2580</v>
+      <c r="K15" s="350" t="s">
+        <v>2424</v>
       </c>
     </row>
     <row r="16" ht="51">
@@ -26689,215 +26117,215 @@
         <v>1988</v>
       </c>
       <c r="B16" s="302" t="s">
-        <v>2581</v>
+        <v>2425</v>
       </c>
       <c r="C16" s="302" t="s">
-        <v>2582</v>
+        <v>2426</v>
       </c>
       <c r="D16" s="302" t="s">
-        <v>2583</v>
+        <v>2427</v>
       </c>
       <c r="E16" s="295" t="s">
-        <v>2584</v>
+        <v>2428</v>
       </c>
       <c r="F16" s="297" t="s">
-        <v>2585</v>
-      </c>
-      <c r="G16" s="353">
+        <v>2429</v>
+      </c>
+      <c r="G16" s="346">
         <v>45995</v>
       </c>
-      <c r="H16" s="354" t="s">
-        <v>2586</v>
-      </c>
-      <c r="I16" s="355" t="s">
-        <v>2587</v>
-      </c>
-      <c r="J16" s="356" t="str">
+      <c r="H16" s="347" t="s">
+        <v>2430</v>
+      </c>
+      <c r="I16" s="348" t="s">
+        <v>2431</v>
+      </c>
+      <c r="J16" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY/view?usp=drivesdk","Ms. VAIBHAVI PANDYA-Ms. RIYA DESAI-Mr.HARDIK KUMAR-Data Structure ")</f>
         <v xml:space="preserve">Ms. VAIBHAVI PANDYA-Ms. RIYA DESAI-Mr.HARDIK KUMAR-Data Structure </v>
       </c>
-      <c r="K16" s="357" t="s">
-        <v>2580</v>
+      <c r="K16" s="350" t="s">
+        <v>2424</v>
       </c>
     </row>
     <row r="17" ht="51">
       <c r="A17" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="B17" s="354" t="s">
-        <v>2588</v>
-      </c>
-      <c r="C17" s="358" t="s">
-        <v>2589</v>
-      </c>
-      <c r="D17" s="354" t="s">
-        <v>2590</v>
+      <c r="B17" s="347" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C17" s="351" t="s">
+        <v>2433</v>
+      </c>
+      <c r="D17" s="347" t="s">
+        <v>2434</v>
       </c>
       <c r="E17" s="296" t="s">
-        <v>2591</v>
+        <v>2435</v>
       </c>
       <c r="F17" s="297" t="s">
-        <v>2592</v>
-      </c>
-      <c r="G17" s="353">
+        <v>2436</v>
+      </c>
+      <c r="G17" s="346">
         <v>45995</v>
       </c>
-      <c r="H17" s="354" t="s">
-        <v>2593</v>
-      </c>
-      <c r="I17" s="355" t="s">
-        <v>2594</v>
-      </c>
-      <c r="J17" s="356" t="str">
+      <c r="H17" s="347" t="s">
+        <v>2437</v>
+      </c>
+      <c r="I17" s="348" t="s">
+        <v>2438</v>
+      </c>
+      <c r="J17" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9/view?usp=drivesdk","Ms. BHAVYA GAJIWALA-Ms. KAVYA PRAJAPATI-Ms. POONAM FALDU-Computer Network")</f>
         <v xml:space="preserve">Ms. BHAVYA GAJIWALA-Ms. KAVYA PRAJAPATI-Ms. POONAM FALDU-Computer Network</v>
       </c>
-      <c r="K17" s="357" t="s">
-        <v>2595</v>
+      <c r="K17" s="350" t="s">
+        <v>2439</v>
       </c>
     </row>
     <row r="18" ht="51">
       <c r="A18" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="B18" s="354" t="s">
-        <v>2596</v>
-      </c>
-      <c r="C18" s="358" t="s">
-        <v>2597</v>
-      </c>
-      <c r="D18" s="354" t="s">
-        <v>2598</v>
+      <c r="B18" s="347" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C18" s="351" t="s">
+        <v>2441</v>
+      </c>
+      <c r="D18" s="347" t="s">
+        <v>2442</v>
       </c>
       <c r="E18" s="296" t="s">
-        <v>2599</v>
+        <v>2443</v>
       </c>
       <c r="F18" s="297" t="s">
-        <v>2600</v>
-      </c>
-      <c r="G18" s="353">
+        <v>2444</v>
+      </c>
+      <c r="G18" s="346">
         <v>45995</v>
       </c>
-      <c r="H18" s="354" t="s">
-        <v>2601</v>
-      </c>
-      <c r="I18" s="355" t="s">
-        <v>2602</v>
-      </c>
-      <c r="J18" s="356" t="str">
+      <c r="H18" s="347" t="s">
+        <v>2445</v>
+      </c>
+      <c r="I18" s="348" t="s">
+        <v>2446</v>
+      </c>
+      <c r="J18" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/159BT_GO9SchY3qO-sK9fZg4H87gfmKd8/view?usp=drivesdk","Ms. KALPANA PRAJAPATI-Ms. DEVIKA KSHTRIYA -Mr. VIJAY VASAIYA-.Net Programming with C# ")</f>
         <v xml:space="preserve">Ms. KALPANA PRAJAPATI-Ms. DEVIKA KSHTRIYA -Mr. VIJAY VASAIYA-.Net Programming with C# </v>
       </c>
-      <c r="K18" s="357" t="s">
-        <v>2595</v>
+      <c r="K18" s="350" t="s">
+        <v>2439</v>
       </c>
     </row>
     <row r="19" ht="25.5">
       <c r="A19" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="B19" s="354" t="s">
-        <v>2603</v>
-      </c>
-      <c r="C19" s="358" t="s">
-        <v>2604</v>
-      </c>
-      <c r="D19" s="354" t="s">
-        <v>2605</v>
+      <c r="B19" s="347" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C19" s="351" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D19" s="347" t="s">
+        <v>2449</v>
       </c>
       <c r="E19" s="296" t="s">
         <v>741</v>
       </c>
       <c r="F19" s="297" t="s">
-        <v>2606</v>
-      </c>
-      <c r="G19" s="353">
+        <v>2450</v>
+      </c>
+      <c r="G19" s="346">
         <v>45995</v>
       </c>
-      <c r="H19" s="354" t="s">
-        <v>2607</v>
-      </c>
-      <c r="I19" s="355" t="s">
-        <v>2608</v>
-      </c>
-      <c r="J19" s="356" t="str">
+      <c r="H19" s="347" t="s">
+        <v>2451</v>
+      </c>
+      <c r="I19" s="348" t="s">
+        <v>2452</v>
+      </c>
+      <c r="J19" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH/view?usp=drivesdk","Ms. Vrunda patel-Mr. Ankit Padariya, -Mr. Suraj singh-Database Management System")</f>
         <v xml:space="preserve">Ms. Vrunda patel-Mr. Ankit Padariya, -Mr. Suraj singh-Database Management System</v>
       </c>
-      <c r="K19" s="357" t="s">
-        <v>2595</v>
+      <c r="K19" s="350" t="s">
+        <v>2439</v>
       </c>
     </row>
     <row r="20" ht="21.75">
       <c r="A20" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="B20" s="354" t="s">
-        <v>2609</v>
-      </c>
-      <c r="C20" s="358" t="s">
-        <v>2610</v>
-      </c>
-      <c r="D20" s="354" t="s">
-        <v>2611</v>
+      <c r="B20" s="347" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C20" s="351" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D20" s="347" t="s">
+        <v>2455</v>
       </c>
       <c r="E20" s="296" t="s">
-        <v>2612</v>
+        <v>2456</v>
       </c>
       <c r="F20" s="297" t="s">
-        <v>2613</v>
-      </c>
-      <c r="G20" s="353">
+        <v>2457</v>
+      </c>
+      <c r="G20" s="346">
         <v>45995</v>
       </c>
-      <c r="H20" s="354" t="s">
-        <v>2614</v>
-      </c>
-      <c r="I20" s="355" t="s">
-        <v>2615</v>
-      </c>
-      <c r="J20" s="356" t="str">
+      <c r="H20" s="347" t="s">
+        <v>2458</v>
+      </c>
+      <c r="I20" s="348" t="s">
+        <v>2459</v>
+      </c>
+      <c r="J20" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr/view?usp=drivesdk","Ms. Radhika Thakkar-BK Soni-Ms. Bhavya shah-Java")</f>
         <v xml:space="preserve">Ms. Radhika Thakkar-BK Soni-Ms. Bhavya shah-Java</v>
       </c>
-      <c r="K20" s="357" t="s">
-        <v>2595</v>
+      <c r="K20" s="350" t="s">
+        <v>2439</v>
       </c>
     </row>
     <row r="21" ht="38.25">
       <c r="A21" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="B21" s="354" t="s">
-        <v>2616</v>
-      </c>
-      <c r="C21" s="359" t="s">
-        <v>2617</v>
+      <c r="B21" s="347" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C21" s="352" t="s">
+        <v>2461</v>
       </c>
       <c r="D21" s="295" t="s">
-        <v>2618</v>
+        <v>2462</v>
       </c>
       <c r="E21" s="296" t="s">
-        <v>2619</v>
+        <v>2463</v>
       </c>
       <c r="F21" s="297" t="s">
-        <v>2620</v>
-      </c>
-      <c r="G21" s="353">
+        <v>2464</v>
+      </c>
+      <c r="G21" s="346">
         <v>45995</v>
       </c>
-      <c r="H21" s="354" t="s">
-        <v>2621</v>
-      </c>
-      <c r="I21" s="355" t="s">
-        <v>2622</v>
-      </c>
-      <c r="J21" s="356" t="str">
+      <c r="H21" s="347" t="s">
+        <v>2465</v>
+      </c>
+      <c r="I21" s="348" t="s">
+        <v>2466</v>
+      </c>
+      <c r="J21" s="349" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY/view?usp=drivesdk","Ms. Shivani Shelke-Ms. Shivani Gupta-Mr. Suraj Singh-Data Communication Network")</f>
         <v xml:space="preserve">Ms. Shivani Shelke-Ms. Shivani Gupta-Mr. Suraj Singh-Data Communication Network</v>
       </c>
-      <c r="K21" s="357" t="s">
-        <v>2595</v>
+      <c r="K21" s="350" t="s">
+        <v>2439</v>
       </c>
     </row>
     <row r="22" ht="16.5">
@@ -26905,35 +26333,35 @@
         <v>2112</v>
       </c>
       <c r="B22" s="307" t="s">
-        <v>2623</v>
-      </c>
-      <c r="C22" s="360" t="s">
-        <v>2624</v>
-      </c>
-      <c r="D22" s="360" t="s">
-        <v>2625</v>
+        <v>2467</v>
+      </c>
+      <c r="C22" s="353" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D22" s="353" t="s">
+        <v>2469</v>
       </c>
       <c r="E22" s="106" t="s">
-        <v>2626</v>
+        <v>2470</v>
       </c>
       <c r="F22" s="305" t="s">
-        <v>2627</v>
+        <v>2471</v>
       </c>
       <c r="G22" s="108">
         <v>46059</v>
       </c>
       <c r="H22" s="109" t="s">
-        <v>2628</v>
+        <v>2472</v>
       </c>
       <c r="I22" s="110" t="s">
-        <v>2629</v>
+        <v>2473</v>
       </c>
       <c r="J22" s="111" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe/view?usp=drivesdk","Dr. Hiral Shah-Ms. Rachana S. Kumar- Mr. Harshrajsinh Rana-Pharmaceutics")</f>
         <v xml:space="preserve">Dr. Hiral Shah-Ms. Rachana S. Kumar- Mr. Harshrajsinh Rana-Pharmaceutics</v>
       </c>
       <c r="K22" s="112" t="s">
-        <v>2630</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="23" ht="16.5">
@@ -26941,142 +26369,142 @@
         <v>2112</v>
       </c>
       <c r="B23" s="109" t="s">
-        <v>2631</v>
-      </c>
-      <c r="C23" s="361" t="s">
-        <v>2632</v>
-      </c>
-      <c r="D23" s="361" t="s">
-        <v>2633</v>
+        <v>2475</v>
+      </c>
+      <c r="C23" s="354" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D23" s="354" t="s">
+        <v>2477</v>
       </c>
       <c r="E23" s="106" t="s">
-        <v>2634</v>
+        <v>2478</v>
       </c>
       <c r="F23" s="305" t="s">
-        <v>2635</v>
+        <v>2479</v>
       </c>
       <c r="G23" s="108">
         <v>46059</v>
       </c>
       <c r="H23" s="109" t="s">
-        <v>2636</v>
+        <v>2480</v>
       </c>
       <c r="I23" s="110" t="s">
-        <v>2637</v>
+        <v>2481</v>
       </c>
       <c r="J23" s="111" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1/view?usp=drivesdk","Ms. Tora Shah-Ms. Bhargavi Mistry-Ms. Krutika Agarwal-Pharmaceutics –Theory")</f>
         <v xml:space="preserve">Ms. Tora Shah-Ms. Bhargavi Mistry-Ms. Krutika Agarwal-Pharmaceutics –Theory</v>
       </c>
       <c r="K23" s="112" t="s">
-        <v>2630</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="24" ht="15.75">
-      <c r="A24" s="362" t="s">
+      <c r="A24" s="355" t="s">
         <v>1988</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2638</v>
-      </c>
-      <c r="C24" s="363" t="s">
-        <v>2639</v>
-      </c>
-      <c r="D24" s="363" t="s">
-        <v>2640</v>
-      </c>
-      <c r="E24" s="364" t="s">
-        <v>2641</v>
+        <v>2482</v>
+      </c>
+      <c r="C24" s="356" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D24" s="356" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E24" s="357" t="s">
+        <v>2485</v>
       </c>
       <c r="F24" s="305" t="s">
-        <v>2642</v>
+        <v>2486</v>
       </c>
       <c r="G24" s="108">
         <v>46049</v>
       </c>
       <c r="H24" s="109" t="s">
-        <v>2643</v>
+        <v>2487</v>
       </c>
       <c r="I24" s="110" t="s">
-        <v>2644</v>
+        <v>2488</v>
       </c>
       <c r="J24" s="111" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1wOuYeHtarx_tKiscCvISOnpheAA3LoXB/view?usp=drivesdk","Mr. Ashish Shah-Mr. Vikash Verma-Mr. Ishan Desai-Power System - I ")</f>
         <v xml:space="preserve">Mr. Ashish Shah-Mr. Vikash Verma-Mr. Ishan Desai-Power System - I </v>
       </c>
       <c r="K24" s="112" t="s">
-        <v>2645</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="25" ht="15.75">
-      <c r="A25" s="362" t="s">
+      <c r="A25" s="355" t="s">
         <v>1988</v>
       </c>
-      <c r="B25" s="365" t="s">
-        <v>2646</v>
-      </c>
-      <c r="C25" s="366" t="s">
-        <v>2647</v>
-      </c>
-      <c r="D25" s="366" t="s">
-        <v>2648</v>
-      </c>
-      <c r="E25" s="367" t="s">
-        <v>2649</v>
+      <c r="B25" s="358" t="s">
+        <v>2490</v>
+      </c>
+      <c r="C25" s="359" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D25" s="359" t="s">
+        <v>2492</v>
+      </c>
+      <c r="E25" s="360" t="s">
+        <v>2493</v>
       </c>
       <c r="F25" s="305" t="s">
-        <v>2650</v>
+        <v>2494</v>
       </c>
       <c r="G25" s="179">
         <v>46049</v>
       </c>
       <c r="H25" s="319" t="s">
-        <v>2651</v>
+        <v>2495</v>
       </c>
       <c r="I25" s="320" t="s">
-        <v>2652</v>
+        <v>2496</v>
       </c>
       <c r="J25" s="321" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e/view?usp=drivesdk","Mrs. Priyanka Patel-Mr. Priyank Makwana-Ms. Krishna Gohil-Mathematics - I")</f>
         <v xml:space="preserve">Mrs. Priyanka Patel-Mr. Priyank Makwana-Ms. Krishna Gohil-Mathematics - I</v>
       </c>
       <c r="K25" s="322" t="s">
-        <v>2653</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="26" ht="293.25">
-      <c r="A26" s="368" t="s">
-        <v>2654</v>
-      </c>
-      <c r="B26" s="369" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C26" s="369" t="s">
-        <v>2656</v>
-      </c>
-      <c r="D26" s="370" t="s">
-        <v>2657</v>
-      </c>
-      <c r="E26" s="371" t="s">
-        <v>2658</v>
-      </c>
-      <c r="F26" s="372" t="s">
-        <v>2659</v>
-      </c>
-      <c r="G26" s="373">
+      <c r="A26" s="361" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B26" s="362" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C26" s="362" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D26" s="363" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E26" s="364" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F26" s="365" t="s">
+        <v>2503</v>
+      </c>
+      <c r="G26" s="366">
         <v>46139</v>
       </c>
-      <c r="H26" s="374" t="s">
-        <v>2660</v>
-      </c>
-      <c r="I26" s="375" t="s">
-        <v>2661</v>
-      </c>
-      <c r="J26" s="375" t="s">
-        <v>2662</v>
-      </c>
-      <c r="K26" s="376" t="s">
-        <v>2663</v>
+      <c r="H26" s="367" t="s">
+        <v>2504</v>
+      </c>
+      <c r="I26" s="368" t="s">
+        <v>2505</v>
+      </c>
+      <c r="J26" s="368" t="s">
+        <v>2506</v>
+      </c>
+      <c r="K26" s="369" t="s">
+        <v>2507</v>
       </c>
       <c r="L26" s="190"/>
       <c r="M26" s="190"/>
@@ -27086,16 +26514,16 @@
         <v>231</v>
       </c>
       <c r="B27" s="203" t="s">
-        <v>2664</v>
+        <v>2508</v>
       </c>
       <c r="C27" s="203" t="s">
-        <v>2665</v>
-      </c>
-      <c r="D27" s="377" t="s">
-        <v>2666</v>
+        <v>2509</v>
+      </c>
+      <c r="D27" s="370" t="s">
+        <v>2510</v>
       </c>
       <c r="E27" s="212" t="s">
-        <v>2667</v>
+        <v>2511</v>
       </c>
       <c r="F27" s="194" t="s">
         <v>1595</v>
@@ -27104,16 +26532,16 @@
         <v>46139</v>
       </c>
       <c r="H27" s="203" t="s">
-        <v>2668</v>
+        <v>2512</v>
       </c>
       <c r="I27" s="204" t="s">
-        <v>2669</v>
+        <v>2513</v>
       </c>
       <c r="J27" s="204" t="s">
-        <v>2670</v>
+        <v>2514</v>
       </c>
       <c r="K27" s="205" t="s">
-        <v>2671</v>
+        <v>2515</v>
       </c>
       <c r="L27" s="190"/>
       <c r="M27" s="190"/>
@@ -27123,367 +26551,367 @@
         <v>1619</v>
       </c>
       <c r="B28" s="196" t="s">
-        <v>2672</v>
+        <v>2516</v>
       </c>
       <c r="C28" s="196" t="s">
-        <v>2673</v>
-      </c>
-      <c r="D28" s="378" t="s">
-        <v>2674</v>
+        <v>2517</v>
+      </c>
+      <c r="D28" s="371" t="s">
+        <v>2518</v>
       </c>
       <c r="E28" s="230" t="s">
-        <v>2675</v>
+        <v>2519</v>
       </c>
       <c r="F28" s="194" t="s">
-        <v>2676</v>
+        <v>2520</v>
       </c>
       <c r="G28" s="195">
         <v>46139</v>
       </c>
       <c r="H28" s="196" t="s">
-        <v>2677</v>
+        <v>2521</v>
       </c>
       <c r="I28" s="197" t="s">
-        <v>2678</v>
+        <v>2522</v>
       </c>
       <c r="J28" s="197" t="s">
-        <v>2679</v>
+        <v>2523</v>
       </c>
       <c r="K28" s="198" t="s">
-        <v>2680</v>
+        <v>2524</v>
       </c>
       <c r="L28" s="190"/>
       <c r="M28" s="190"/>
     </row>
     <row r="29" ht="293.25">
-      <c r="A29" s="379" t="s">
+      <c r="A29" s="372" t="s">
         <v>1619</v>
       </c>
       <c r="B29" s="203" t="s">
-        <v>2681</v>
+        <v>2525</v>
       </c>
       <c r="C29" s="203" t="s">
-        <v>2682</v>
-      </c>
-      <c r="D29" s="377" t="s">
-        <v>2683</v>
+        <v>2526</v>
+      </c>
+      <c r="D29" s="370" t="s">
+        <v>2527</v>
       </c>
       <c r="E29" s="212" t="s">
-        <v>2684</v>
+        <v>2528</v>
       </c>
       <c r="F29" s="194" t="s">
-        <v>2685</v>
+        <v>2529</v>
       </c>
       <c r="G29" s="202">
         <v>46139</v>
       </c>
       <c r="H29" s="203" t="s">
-        <v>2686</v>
+        <v>2530</v>
       </c>
       <c r="I29" s="204" t="s">
-        <v>2687</v>
+        <v>2531</v>
       </c>
       <c r="J29" s="204" t="s">
-        <v>2688</v>
+        <v>2532</v>
       </c>
       <c r="K29" s="205" t="s">
-        <v>2680</v>
+        <v>2524</v>
       </c>
       <c r="L29" s="190"/>
       <c r="M29" s="190"/>
     </row>
     <row r="30" ht="293.25">
-      <c r="A30" s="379" t="s">
+      <c r="A30" s="372" t="s">
         <v>1619</v>
       </c>
       <c r="B30" s="196" t="s">
-        <v>2689</v>
+        <v>2533</v>
       </c>
       <c r="C30" s="196" t="s">
-        <v>2690</v>
-      </c>
-      <c r="D30" s="378" t="s">
-        <v>2691</v>
+        <v>2534</v>
+      </c>
+      <c r="D30" s="371" t="s">
+        <v>2535</v>
       </c>
       <c r="E30" s="230" t="s">
-        <v>2692</v>
+        <v>2536</v>
       </c>
       <c r="F30" s="194" t="s">
-        <v>2693</v>
+        <v>2537</v>
       </c>
       <c r="G30" s="195">
         <v>46139</v>
       </c>
       <c r="H30" s="196" t="s">
-        <v>2694</v>
+        <v>2538</v>
       </c>
       <c r="I30" s="197" t="s">
-        <v>2695</v>
+        <v>2539</v>
       </c>
       <c r="J30" s="197" t="s">
-        <v>2696</v>
+        <v>2540</v>
       </c>
       <c r="K30" s="198" t="s">
-        <v>2680</v>
+        <v>2524</v>
       </c>
       <c r="L30" s="190"/>
       <c r="M30" s="190"/>
     </row>
     <row r="31" ht="293.25">
-      <c r="A31" s="379" t="s">
+      <c r="A31" s="372" t="s">
         <v>1619</v>
       </c>
       <c r="B31" s="203" t="s">
-        <v>2697</v>
+        <v>2541</v>
       </c>
       <c r="C31" s="203" t="s">
-        <v>2698</v>
-      </c>
-      <c r="D31" s="377" t="s">
-        <v>2699</v>
+        <v>2542</v>
+      </c>
+      <c r="D31" s="370" t="s">
+        <v>2543</v>
       </c>
       <c r="E31" s="212" t="s">
-        <v>2700</v>
+        <v>2544</v>
       </c>
       <c r="F31" s="194" t="s">
-        <v>2701</v>
+        <v>2545</v>
       </c>
       <c r="G31" s="202">
         <v>46139</v>
       </c>
       <c r="H31" s="203" t="s">
-        <v>2702</v>
+        <v>2546</v>
       </c>
       <c r="I31" s="204" t="s">
-        <v>2703</v>
+        <v>2547</v>
       </c>
       <c r="J31" s="204" t="s">
-        <v>2704</v>
+        <v>2548</v>
       </c>
       <c r="K31" s="205" t="s">
-        <v>2274</v>
+        <v>2225</v>
       </c>
       <c r="L31" s="190"/>
       <c r="M31" s="190"/>
     </row>
     <row r="32" ht="293.25">
       <c r="A32" s="191" t="s">
-        <v>2337</v>
+        <v>2252</v>
       </c>
       <c r="B32" s="196" t="s">
-        <v>2705</v>
+        <v>2549</v>
       </c>
       <c r="C32" s="196" t="s">
-        <v>2706</v>
-      </c>
-      <c r="D32" s="378" t="s">
-        <v>2707</v>
+        <v>2550</v>
+      </c>
+      <c r="D32" s="371" t="s">
+        <v>2551</v>
       </c>
       <c r="E32" s="230" t="s">
-        <v>2708</v>
+        <v>2552</v>
       </c>
       <c r="F32" s="194" t="s">
-        <v>2709</v>
+        <v>2553</v>
       </c>
       <c r="G32" s="195">
         <v>46139</v>
       </c>
       <c r="H32" s="196" t="s">
-        <v>2710</v>
+        <v>2554</v>
       </c>
       <c r="I32" s="197" t="s">
-        <v>2711</v>
+        <v>2555</v>
       </c>
       <c r="J32" s="197" t="s">
-        <v>2712</v>
+        <v>2556</v>
       </c>
       <c r="K32" s="198" t="s">
-        <v>2713</v>
+        <v>2557</v>
       </c>
       <c r="L32" s="190"/>
       <c r="M32" s="190"/>
     </row>
     <row r="33" ht="293.25">
       <c r="A33" s="227" t="s">
-        <v>2369</v>
+        <v>2558</v>
       </c>
       <c r="B33" s="203" t="s">
-        <v>2714</v>
+        <v>2559</v>
       </c>
       <c r="C33" s="203" t="s">
-        <v>2715</v>
-      </c>
-      <c r="D33" s="377" t="s">
-        <v>2716</v>
+        <v>2560</v>
+      </c>
+      <c r="D33" s="370" t="s">
+        <v>2561</v>
       </c>
       <c r="E33" s="212" t="s">
-        <v>2717</v>
+        <v>2562</v>
       </c>
       <c r="F33" s="194" t="s">
-        <v>2718</v>
+        <v>2563</v>
       </c>
       <c r="G33" s="202">
         <v>46139</v>
       </c>
       <c r="H33" s="203" t="s">
-        <v>2719</v>
+        <v>2564</v>
       </c>
       <c r="I33" s="204" t="s">
-        <v>2720</v>
+        <v>2565</v>
       </c>
       <c r="J33" s="204" t="s">
-        <v>2721</v>
+        <v>2566</v>
       </c>
       <c r="K33" s="205" t="s">
-        <v>2722</v>
+        <v>2567</v>
       </c>
       <c r="L33" s="190"/>
       <c r="M33" s="190"/>
     </row>
     <row r="34" ht="293.25">
-      <c r="A34" s="380" t="s">
-        <v>2369</v>
+      <c r="A34" s="373" t="s">
+        <v>2558</v>
       </c>
       <c r="B34" s="196" t="s">
-        <v>2723</v>
+        <v>2568</v>
       </c>
       <c r="C34" s="196" t="s">
-        <v>2724</v>
-      </c>
-      <c r="D34" s="378" t="s">
-        <v>2725</v>
+        <v>2569</v>
+      </c>
+      <c r="D34" s="371" t="s">
+        <v>2570</v>
       </c>
       <c r="E34" s="230" t="s">
-        <v>2726</v>
+        <v>2571</v>
       </c>
       <c r="F34" s="194" t="s">
-        <v>2727</v>
+        <v>2572</v>
       </c>
       <c r="G34" s="195">
         <v>46139</v>
       </c>
       <c r="H34" s="196" t="s">
-        <v>2728</v>
+        <v>2573</v>
       </c>
       <c r="I34" s="197" t="s">
-        <v>2729</v>
+        <v>2574</v>
       </c>
       <c r="J34" s="197" t="s">
-        <v>2730</v>
+        <v>2575</v>
       </c>
       <c r="K34" s="198" t="s">
-        <v>2722</v>
+        <v>2567</v>
       </c>
       <c r="L34" s="190"/>
       <c r="M34" s="190"/>
     </row>
     <row r="35" ht="293.25">
-      <c r="A35" s="380" t="s">
-        <v>2369</v>
+      <c r="A35" s="373" t="s">
+        <v>2558</v>
       </c>
       <c r="B35" s="203" t="s">
-        <v>2731</v>
+        <v>2576</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>2732</v>
-      </c>
-      <c r="D35" s="377" t="s">
-        <v>2733</v>
+        <v>2577</v>
+      </c>
+      <c r="D35" s="370" t="s">
+        <v>2578</v>
       </c>
       <c r="E35" s="212" t="s">
-        <v>2734</v>
+        <v>2579</v>
       </c>
       <c r="F35" s="194" t="s">
-        <v>2735</v>
+        <v>2580</v>
       </c>
       <c r="G35" s="202">
         <v>46139</v>
       </c>
       <c r="H35" s="203" t="s">
-        <v>2736</v>
+        <v>2581</v>
       </c>
       <c r="I35" s="204" t="s">
-        <v>2737</v>
+        <v>2582</v>
       </c>
       <c r="J35" s="204" t="s">
-        <v>2738</v>
+        <v>2583</v>
       </c>
       <c r="K35" s="205" t="s">
-        <v>2722</v>
+        <v>2567</v>
       </c>
       <c r="L35" s="190"/>
       <c r="M35" s="190"/>
     </row>
     <row r="36" ht="293.25">
-      <c r="A36" s="380" t="s">
-        <v>2369</v>
+      <c r="A36" s="373" t="s">
+        <v>2558</v>
       </c>
       <c r="B36" s="196" t="s">
-        <v>2739</v>
+        <v>2584</v>
       </c>
       <c r="C36" s="196" t="s">
-        <v>2740</v>
-      </c>
-      <c r="D36" s="378" t="s">
-        <v>2741</v>
+        <v>2585</v>
+      </c>
+      <c r="D36" s="371" t="s">
+        <v>2586</v>
       </c>
       <c r="E36" s="230" t="s">
-        <v>2742</v>
+        <v>2587</v>
       </c>
       <c r="F36" s="194" t="s">
-        <v>2743</v>
+        <v>2588</v>
       </c>
       <c r="G36" s="195">
         <v>46139</v>
       </c>
       <c r="H36" s="196" t="s">
-        <v>2744</v>
+        <v>2589</v>
       </c>
       <c r="I36" s="197" t="s">
-        <v>2745</v>
+        <v>2590</v>
       </c>
       <c r="J36" s="197" t="s">
-        <v>2746</v>
+        <v>2591</v>
       </c>
       <c r="K36" s="198" t="s">
-        <v>2722</v>
+        <v>2567</v>
       </c>
       <c r="L36" s="190"/>
       <c r="M36" s="190"/>
     </row>
     <row r="37" ht="293.25">
-      <c r="A37" s="380" t="s">
-        <v>2369</v>
+      <c r="A37" s="373" t="s">
+        <v>2558</v>
       </c>
       <c r="B37" s="203" t="s">
-        <v>2747</v>
+        <v>2592</v>
       </c>
       <c r="C37" s="203" t="s">
-        <v>2748</v>
-      </c>
-      <c r="D37" s="377" t="s">
-        <v>2749</v>
+        <v>2593</v>
+      </c>
+      <c r="D37" s="370" t="s">
+        <v>2594</v>
       </c>
       <c r="E37" s="212" t="s">
-        <v>2750</v>
+        <v>2595</v>
       </c>
       <c r="F37" s="194" t="s">
-        <v>2751</v>
+        <v>2596</v>
       </c>
       <c r="G37" s="202">
         <v>46139</v>
       </c>
       <c r="H37" s="203" t="s">
-        <v>2752</v>
+        <v>2597</v>
       </c>
       <c r="I37" s="204" t="s">
-        <v>2753</v>
+        <v>2598</v>
       </c>
       <c r="J37" s="204" t="s">
-        <v>2754</v>
+        <v>2599</v>
       </c>
       <c r="K37" s="205" t="s">
-        <v>2722</v>
+        <v>2567</v>
       </c>
       <c r="L37" s="190"/>
       <c r="M37" s="190"/>
@@ -27493,108 +26921,108 @@
         <v>1652</v>
       </c>
       <c r="B38" s="196" t="s">
-        <v>2755</v>
+        <v>2600</v>
       </c>
       <c r="C38" s="196" t="s">
-        <v>2756</v>
-      </c>
-      <c r="D38" s="378" t="s">
-        <v>2757</v>
+        <v>2601</v>
+      </c>
+      <c r="D38" s="371" t="s">
+        <v>2602</v>
       </c>
       <c r="E38" s="230" t="s">
-        <v>2758</v>
+        <v>2603</v>
       </c>
       <c r="F38" s="194" t="s">
-        <v>2759</v>
+        <v>2604</v>
       </c>
       <c r="G38" s="195">
         <v>46139</v>
       </c>
       <c r="H38" s="196" t="s">
-        <v>2760</v>
+        <v>2605</v>
       </c>
       <c r="I38" s="197" t="s">
-        <v>2761</v>
+        <v>2606</v>
       </c>
       <c r="J38" s="197" t="s">
-        <v>2762</v>
+        <v>2607</v>
       </c>
       <c r="K38" s="198" t="s">
-        <v>2763</v>
+        <v>2608</v>
       </c>
       <c r="L38" s="190"/>
       <c r="M38" s="190"/>
     </row>
     <row r="39" ht="293.25">
-      <c r="A39" s="379" t="s">
+      <c r="A39" s="372" t="s">
         <v>1652</v>
       </c>
       <c r="B39" s="203" t="s">
-        <v>2764</v>
+        <v>2609</v>
       </c>
       <c r="C39" s="203" t="s">
-        <v>2765</v>
-      </c>
-      <c r="D39" s="377" t="s">
-        <v>2766</v>
+        <v>2610</v>
+      </c>
+      <c r="D39" s="370" t="s">
+        <v>2611</v>
       </c>
       <c r="E39" s="212" t="s">
-        <v>2767</v>
+        <v>2612</v>
       </c>
       <c r="F39" s="194" t="s">
-        <v>2768</v>
+        <v>2613</v>
       </c>
       <c r="G39" s="202">
         <v>46139</v>
       </c>
       <c r="H39" s="203" t="s">
-        <v>2769</v>
+        <v>2614</v>
       </c>
       <c r="I39" s="204" t="s">
-        <v>2770</v>
+        <v>2615</v>
       </c>
       <c r="J39" s="204" t="s">
-        <v>2771</v>
+        <v>2616</v>
       </c>
       <c r="K39" s="205" t="s">
-        <v>2763</v>
+        <v>2608</v>
       </c>
       <c r="L39" s="190"/>
       <c r="M39" s="190"/>
     </row>
     <row r="40" ht="293.25">
-      <c r="A40" s="379" t="s">
+      <c r="A40" s="372" t="s">
         <v>1652</v>
       </c>
       <c r="B40" s="196" t="s">
-        <v>2772</v>
+        <v>2617</v>
       </c>
       <c r="C40" s="196" t="s">
-        <v>2773</v>
+        <v>2618</v>
       </c>
       <c r="D40" s="196" t="s">
-        <v>2774</v>
+        <v>2619</v>
       </c>
       <c r="E40" s="230" t="s">
-        <v>2775</v>
-      </c>
-      <c r="F40" s="381" t="s">
-        <v>2776</v>
-      </c>
-      <c r="G40" s="382">
+        <v>2620</v>
+      </c>
+      <c r="F40" s="374" t="s">
+        <v>2621</v>
+      </c>
+      <c r="G40" s="375">
         <v>46139</v>
       </c>
       <c r="H40" s="196" t="s">
-        <v>2777</v>
+        <v>2622</v>
       </c>
       <c r="I40" s="197" t="s">
-        <v>2778</v>
+        <v>2623</v>
       </c>
       <c r="J40" s="197" t="s">
-        <v>2779</v>
+        <v>2624</v>
       </c>
       <c r="K40" s="198" t="s">
-        <v>2780</v>
+        <v>2625</v>
       </c>
       <c r="L40" s="190"/>
       <c r="M40" s="190"/>
@@ -27604,108 +27032,108 @@
         <v>153</v>
       </c>
       <c r="B41" s="203" t="s">
-        <v>2781</v>
+        <v>2626</v>
       </c>
       <c r="C41" s="203" t="s">
-        <v>2782</v>
+        <v>2627</v>
       </c>
       <c r="D41" s="203" t="s">
-        <v>2783</v>
+        <v>2628</v>
       </c>
       <c r="E41" s="212" t="s">
-        <v>2784</v>
+        <v>2629</v>
       </c>
       <c r="F41" s="194" t="s">
         <v>1668</v>
       </c>
-      <c r="G41" s="383">
+      <c r="G41" s="376">
         <v>46139</v>
       </c>
       <c r="H41" s="203" t="s">
-        <v>2785</v>
+        <v>2630</v>
       </c>
       <c r="I41" s="204" t="s">
-        <v>2786</v>
+        <v>2631</v>
       </c>
       <c r="J41" s="204" t="s">
-        <v>2787</v>
+        <v>2632</v>
       </c>
       <c r="K41" s="205" t="s">
-        <v>2788</v>
+        <v>2633</v>
       </c>
       <c r="L41" s="190"/>
       <c r="M41" s="190"/>
     </row>
     <row r="42" ht="293.25">
-      <c r="A42" s="380" t="s">
+      <c r="A42" s="373" t="s">
         <v>153</v>
       </c>
       <c r="B42" s="196" t="s">
-        <v>2789</v>
+        <v>2634</v>
       </c>
       <c r="C42" s="196" t="s">
-        <v>2790</v>
+        <v>2635</v>
       </c>
       <c r="D42" s="196" t="s">
-        <v>2791</v>
+        <v>2636</v>
       </c>
       <c r="E42" s="230" t="s">
-        <v>2792</v>
+        <v>2637</v>
       </c>
       <c r="F42" s="194" t="s">
         <v>1674</v>
       </c>
-      <c r="G42" s="382">
+      <c r="G42" s="375">
         <v>46139</v>
       </c>
       <c r="H42" s="196" t="s">
-        <v>2793</v>
+        <v>2638</v>
       </c>
       <c r="I42" s="197" t="s">
-        <v>2794</v>
+        <v>2639</v>
       </c>
       <c r="J42" s="197" t="s">
-        <v>2795</v>
+        <v>2640</v>
       </c>
       <c r="K42" s="198" t="s">
-        <v>2796</v>
+        <v>2641</v>
       </c>
       <c r="L42" s="190"/>
       <c r="M42" s="190"/>
     </row>
     <row r="43" ht="293.25">
-      <c r="A43" s="380" t="s">
+      <c r="A43" s="373" t="s">
         <v>153</v>
       </c>
       <c r="B43" s="203" t="s">
-        <v>2797</v>
+        <v>2642</v>
       </c>
       <c r="C43" s="203" t="s">
-        <v>2798</v>
+        <v>2643</v>
       </c>
       <c r="D43" s="203" t="s">
-        <v>2799</v>
+        <v>2644</v>
       </c>
       <c r="E43" s="212" t="s">
-        <v>2800</v>
+        <v>2645</v>
       </c>
       <c r="F43" s="194" t="s">
         <v>1680</v>
       </c>
-      <c r="G43" s="383">
+      <c r="G43" s="376">
         <v>46139</v>
       </c>
       <c r="H43" s="203" t="s">
-        <v>2801</v>
+        <v>2646</v>
       </c>
       <c r="I43" s="204" t="s">
-        <v>2802</v>
+        <v>2647</v>
       </c>
       <c r="J43" s="204" t="s">
-        <v>2803</v>
+        <v>2648</v>
       </c>
       <c r="K43" s="205" t="s">
-        <v>2796</v>
+        <v>2641</v>
       </c>
       <c r="L43" s="190"/>
       <c r="M43" s="190"/>
@@ -27789,59 +27217,59 @@
   <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="384" t="s">
-        <v>2804</v>
-      </c>
-      <c r="B1" s="384" t="s">
-        <v>2805</v>
+      <c r="A1" s="377" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B1" s="377" t="s">
+        <v>2650</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="385" t="s">
-        <v>2806</v>
-      </c>
-      <c r="B2" s="385" t="s">
-        <v>2807</v>
+      <c r="A2" s="378" t="s">
+        <v>2651</v>
+      </c>
+      <c r="B2" s="378" t="s">
+        <v>2652</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="385" t="s">
-        <v>2808</v>
-      </c>
-      <c r="B3" s="385" t="s">
-        <v>2809</v>
+      <c r="A3" s="378" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B3" s="378" t="s">
+        <v>2654</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="385" t="s">
-        <v>2810</v>
-      </c>
-      <c r="B4" s="385" t="s">
-        <v>2811</v>
+      <c r="A4" s="378" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B4" s="378" t="s">
+        <v>2656</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="385" t="s">
-        <v>2812</v>
-      </c>
-      <c r="B5" s="385" t="s">
-        <v>2813</v>
+      <c r="A5" s="378" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B5" s="378" t="s">
+        <v>2658</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="385" t="s">
-        <v>2814</v>
-      </c>
-      <c r="B6" s="385" t="s">
-        <v>2809</v>
+      <c r="A6" s="378" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B6" s="378" t="s">
+        <v>2654</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="385" t="s">
-        <v>2815</v>
-      </c>
-      <c r="B7" s="385" t="s">
-        <v>2816</v>
+      <c r="A7" s="378" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B7" s="378" t="s">
+        <v>2661</v>
       </c>
     </row>
   </sheetData>
@@ -27861,153 +27289,153 @@
   <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="385" t="s">
-        <v>2817</v>
-      </c>
-      <c r="B1" s="385" t="s">
-        <v>2818</v>
-      </c>
-      <c r="C1" s="385" t="s">
-        <v>2819</v>
-      </c>
-      <c r="D1" s="385" t="s">
-        <v>2820</v>
-      </c>
-      <c r="E1" s="385" t="s">
-        <v>2821</v>
-      </c>
-      <c r="F1" s="385" t="s">
-        <v>2822</v>
-      </c>
-      <c r="G1" s="385" t="s">
-        <v>2823</v>
-      </c>
-      <c r="H1" s="385" t="s">
-        <v>2824</v>
-      </c>
-      <c r="I1" s="385" t="s">
-        <v>2825</v>
-      </c>
-      <c r="J1" s="385" t="s">
-        <v>2826</v>
-      </c>
-      <c r="K1" s="385" t="s">
-        <v>2827</v>
-      </c>
-      <c r="L1" s="385" t="s">
-        <v>2828</v>
-      </c>
-      <c r="M1" s="385" t="s">
-        <v>2829</v>
-      </c>
-      <c r="N1" s="385" t="s">
-        <v>2830</v>
-      </c>
-      <c r="O1" s="385" t="s">
-        <v>2831</v>
-      </c>
-      <c r="P1" s="385" t="s">
-        <v>2832</v>
-      </c>
-      <c r="Q1" s="385" t="s">
-        <v>2833</v>
-      </c>
-      <c r="R1" s="385" t="s">
-        <v>2834</v>
-      </c>
-      <c r="S1" s="385" t="s">
-        <v>2835</v>
-      </c>
-      <c r="T1" s="385" t="s">
-        <v>2836</v>
-      </c>
-      <c r="U1" s="385" t="s">
-        <v>2837</v>
-      </c>
-      <c r="V1" s="385" t="s">
-        <v>2838</v>
-      </c>
-      <c r="W1" s="385" t="s">
-        <v>2839</v>
-      </c>
-      <c r="X1" s="385" t="s">
-        <v>2840</v>
-      </c>
-      <c r="Y1" s="385" t="s">
-        <v>2841</v>
-      </c>
-      <c r="Z1" s="385" t="s">
-        <v>2842</v>
-      </c>
-      <c r="AA1" s="385" t="s">
-        <v>2843</v>
-      </c>
-      <c r="AB1" s="385" t="s">
-        <v>2844</v>
-      </c>
-      <c r="AC1" s="385" t="s">
-        <v>2845</v>
+      <c r="A1" s="378" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B1" s="378" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C1" s="378" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D1" s="378" t="s">
+        <v>2665</v>
+      </c>
+      <c r="E1" s="378" t="s">
+        <v>2666</v>
+      </c>
+      <c r="F1" s="378" t="s">
+        <v>2667</v>
+      </c>
+      <c r="G1" s="378" t="s">
+        <v>2668</v>
+      </c>
+      <c r="H1" s="378" t="s">
+        <v>2669</v>
+      </c>
+      <c r="I1" s="378" t="s">
+        <v>2670</v>
+      </c>
+      <c r="J1" s="378" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K1" s="378" t="s">
+        <v>2672</v>
+      </c>
+      <c r="L1" s="378" t="s">
+        <v>2673</v>
+      </c>
+      <c r="M1" s="378" t="s">
+        <v>2674</v>
+      </c>
+      <c r="N1" s="378" t="s">
+        <v>2675</v>
+      </c>
+      <c r="O1" s="378" t="s">
+        <v>2676</v>
+      </c>
+      <c r="P1" s="378" t="s">
+        <v>2677</v>
+      </c>
+      <c r="Q1" s="378" t="s">
+        <v>2678</v>
+      </c>
+      <c r="R1" s="378" t="s">
+        <v>2679</v>
+      </c>
+      <c r="S1" s="378" t="s">
+        <v>2680</v>
+      </c>
+      <c r="T1" s="378" t="s">
+        <v>2681</v>
+      </c>
+      <c r="U1" s="378" t="s">
+        <v>2682</v>
+      </c>
+      <c r="V1" s="378" t="s">
+        <v>2683</v>
+      </c>
+      <c r="W1" s="378" t="s">
+        <v>2684</v>
+      </c>
+      <c r="X1" s="378" t="s">
+        <v>2685</v>
+      </c>
+      <c r="Y1" s="378" t="s">
+        <v>2686</v>
+      </c>
+      <c r="Z1" s="378" t="s">
+        <v>2687</v>
+      </c>
+      <c r="AA1" s="378" t="s">
+        <v>2688</v>
+      </c>
+      <c r="AB1" s="378" t="s">
+        <v>2689</v>
+      </c>
+      <c r="AC1" s="378" t="s">
+        <v>2690</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="385" t="s">
-        <v>2846</v>
-      </c>
-      <c r="B2" s="385" t="s">
-        <v>2847</v>
-      </c>
-      <c r="C2" s="385" t="s">
-        <v>2848</v>
-      </c>
-      <c r="D2" s="385">
+      <c r="A2" s="378" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B2" s="378" t="s">
+        <v>2692</v>
+      </c>
+      <c r="C2" s="378" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D2" s="378">
         <v>650628832</v>
       </c>
-      <c r="E2" s="385">
+      <c r="E2" s="378">
         <v>1</v>
       </c>
-      <c r="F2" s="385">
+      <c r="F2" s="378">
         <v>2</v>
       </c>
-      <c r="G2" s="385" t="s">
-        <v>2849</v>
-      </c>
-      <c r="H2" s="385" t="s">
-        <v>2850</v>
-      </c>
-      <c r="I2" s="385" t="s">
-        <v>2850</v>
-      </c>
-      <c r="J2" s="385" t="s">
-        <v>2851</v>
-      </c>
-      <c r="K2" s="385" t="s">
-        <v>2852</v>
-      </c>
-      <c r="L2" s="385" t="s">
-        <v>2852</v>
-      </c>
-      <c r="M2" s="385" t="s">
-        <v>2853</v>
-      </c>
-      <c r="N2" s="385" t="b">
+      <c r="G2" s="378" t="s">
+        <v>2694</v>
+      </c>
+      <c r="H2" s="378" t="s">
+        <v>2695</v>
+      </c>
+      <c r="I2" s="378" t="s">
+        <v>2695</v>
+      </c>
+      <c r="J2" s="378" t="s">
+        <v>2696</v>
+      </c>
+      <c r="K2" s="378" t="s">
+        <v>2697</v>
+      </c>
+      <c r="L2" s="378" t="s">
+        <v>2697</v>
+      </c>
+      <c r="M2" s="378" t="s">
+        <v>2698</v>
+      </c>
+      <c r="N2" s="378" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="385" t="s">
-        <v>2854</v>
-      </c>
-      <c r="P2" s="385" t="b">
+      <c r="O2" s="378" t="s">
+        <v>2699</v>
+      </c>
+      <c r="P2" s="378" t="b">
         <v>0</v>
       </c>
-      <c r="R2" s="385" t="b">
+      <c r="R2" s="378" t="b">
         <v>1</v>
       </c>
-      <c r="S2" s="385" t="b">
+      <c r="S2" s="378" t="b">
         <v>0</v>
       </c>
-      <c r="X2" s="385" t="b">
+      <c r="X2" s="378" t="b">
         <v>0</v>
       </c>
-      <c r="AA2" s="385" t="b">
+      <c r="AA2" s="378" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28017,4 +27445,1109 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col bestFit="1" min="2" max="2" width="13.140625"/>
+    <col bestFit="1" min="3" max="3" width="11.3515625"/>
+    <col bestFit="1" min="4" max="5" width="11.00390625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="379" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B1" s="380" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C1" s="380" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D1" s="380" t="s">
+        <v>2701</v>
+      </c>
+      <c r="E1" s="380" t="s">
+        <v>2702</v>
+      </c>
+      <c r="F1" s="380" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="380" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="380" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="381" t="s">
+        <v>2703</v>
+      </c>
+      <c r="J1" s="381" t="s">
+        <v>2704</v>
+      </c>
+      <c r="K1" s="381" t="s">
+        <v>2705</v>
+      </c>
+      <c r="L1" s="382" t="s">
+        <v>2706</v>
+      </c>
+      <c r="M1" s="383"/>
+      <c r="N1" s="383"/>
+    </row>
+    <row r="2" ht="25.5" customHeight="1">
+      <c r="A2" s="384" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B2" s="385" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C2" s="386" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D2" s="386" t="s">
+        <v>2710</v>
+      </c>
+      <c r="E2" s="386" t="s">
+        <v>2711</v>
+      </c>
+      <c r="F2" s="187" t="s">
+        <v>2712</v>
+      </c>
+      <c r="G2" s="387" t="s">
+        <v>1507</v>
+      </c>
+      <c r="H2" s="388">
+        <v>46139</v>
+      </c>
+      <c r="I2" s="187" t="s">
+        <v>2713</v>
+      </c>
+      <c r="J2" s="188" t="s">
+        <v>2714</v>
+      </c>
+      <c r="K2" s="188" t="s">
+        <v>2712</v>
+      </c>
+      <c r="L2" s="189" t="s">
+        <v>2715</v>
+      </c>
+      <c r="M2" s="190"/>
+      <c r="N2" s="190"/>
+    </row>
+    <row r="3" ht="25.5" customHeight="1">
+      <c r="A3" s="389"/>
+      <c r="B3" s="390" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C3" s="390" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D3" s="390" t="s">
+        <v>2718</v>
+      </c>
+      <c r="E3" s="390" t="s">
+        <v>2719</v>
+      </c>
+      <c r="F3" s="196" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G3" s="391" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H3" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I3" s="196" t="s">
+        <v>2721</v>
+      </c>
+      <c r="J3" s="197" t="s">
+        <v>2722</v>
+      </c>
+      <c r="K3" s="197" t="s">
+        <v>2720</v>
+      </c>
+      <c r="L3" s="198" t="s">
+        <v>2715</v>
+      </c>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+    </row>
+    <row r="4" ht="25.5" customHeight="1">
+      <c r="A4" s="393"/>
+      <c r="B4" s="394" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C4" s="394" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D4" s="394" t="s">
+        <v>2725</v>
+      </c>
+      <c r="E4" s="394" t="s">
+        <v>2726</v>
+      </c>
+      <c r="F4" s="203" t="s">
+        <v>2727</v>
+      </c>
+      <c r="G4" s="395" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H4" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I4" s="203" t="s">
+        <v>2728</v>
+      </c>
+      <c r="J4" s="204" t="s">
+        <v>2729</v>
+      </c>
+      <c r="K4" s="204" t="s">
+        <v>2727</v>
+      </c>
+      <c r="L4" s="205" t="s">
+        <v>2730</v>
+      </c>
+      <c r="M4" s="190"/>
+      <c r="N4" s="190"/>
+    </row>
+    <row r="5" ht="25.5" customHeight="1">
+      <c r="A5" s="389"/>
+      <c r="B5" s="390" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C5" s="390" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D5" s="390" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E5" s="390" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F5" s="196" t="s">
+        <v>2735</v>
+      </c>
+      <c r="G5" s="391" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H5" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I5" s="196" t="s">
+        <v>2736</v>
+      </c>
+      <c r="J5" s="197" t="s">
+        <v>2737</v>
+      </c>
+      <c r="K5" s="197" t="s">
+        <v>2735</v>
+      </c>
+      <c r="L5" s="198" t="s">
+        <v>2730</v>
+      </c>
+      <c r="M5" s="190"/>
+      <c r="N5" s="190"/>
+    </row>
+    <row r="6" ht="25.5" customHeight="1">
+      <c r="A6" s="393"/>
+      <c r="B6" s="394" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C6" s="394" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D6" s="394" t="s">
+        <v>2740</v>
+      </c>
+      <c r="E6" s="394" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F6" s="203" t="s">
+        <v>2742</v>
+      </c>
+      <c r="G6" s="395" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H6" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I6" s="203" t="s">
+        <v>2743</v>
+      </c>
+      <c r="J6" s="204" t="s">
+        <v>2744</v>
+      </c>
+      <c r="K6" s="204" t="s">
+        <v>2742</v>
+      </c>
+      <c r="L6" s="205" t="s">
+        <v>2730</v>
+      </c>
+      <c r="M6" s="190"/>
+      <c r="N6" s="190"/>
+    </row>
+    <row r="7" ht="25.5" customHeight="1">
+      <c r="A7" s="389"/>
+      <c r="B7" s="390" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C7" s="390" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D7" s="390" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E7" s="390" t="s">
+        <v>2748</v>
+      </c>
+      <c r="F7" s="196" t="s">
+        <v>2749</v>
+      </c>
+      <c r="G7" s="391" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H7" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I7" s="196" t="s">
+        <v>2750</v>
+      </c>
+      <c r="J7" s="197" t="s">
+        <v>2751</v>
+      </c>
+      <c r="K7" s="197" t="s">
+        <v>2749</v>
+      </c>
+      <c r="L7" s="198" t="s">
+        <v>2730</v>
+      </c>
+      <c r="M7" s="190"/>
+      <c r="N7" s="190"/>
+    </row>
+    <row r="8" ht="25.5" customHeight="1">
+      <c r="A8" s="393"/>
+      <c r="B8" s="394" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C8" s="394" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D8" s="394" t="s">
+        <v>2754</v>
+      </c>
+      <c r="E8" s="394" t="s">
+        <v>2755</v>
+      </c>
+      <c r="F8" s="203" t="s">
+        <v>2756</v>
+      </c>
+      <c r="G8" s="395" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H8" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I8" s="203" t="s">
+        <v>2757</v>
+      </c>
+      <c r="J8" s="204" t="s">
+        <v>2758</v>
+      </c>
+      <c r="K8" s="204" t="s">
+        <v>2756</v>
+      </c>
+      <c r="L8" s="205" t="s">
+        <v>2730</v>
+      </c>
+      <c r="M8" s="190"/>
+      <c r="N8" s="190"/>
+    </row>
+    <row r="9" ht="25.5" customHeight="1">
+      <c r="A9" s="389"/>
+      <c r="B9" s="390" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C9" s="390" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D9" s="390" t="s">
+        <v>2761</v>
+      </c>
+      <c r="E9" s="390" t="s">
+        <v>2762</v>
+      </c>
+      <c r="F9" s="196" t="s">
+        <v>2763</v>
+      </c>
+      <c r="G9" s="391" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H9" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I9" s="196" t="s">
+        <v>2764</v>
+      </c>
+      <c r="J9" s="197" t="s">
+        <v>2765</v>
+      </c>
+      <c r="K9" s="197" t="s">
+        <v>2763</v>
+      </c>
+      <c r="L9" s="198" t="s">
+        <v>2730</v>
+      </c>
+      <c r="M9" s="190"/>
+      <c r="N9" s="190"/>
+    </row>
+    <row r="10" ht="25.5" customHeight="1">
+      <c r="A10" s="393"/>
+      <c r="B10" s="394" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C10" s="394" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D10" s="394" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E10" s="394" t="s">
+        <v>2768</v>
+      </c>
+      <c r="F10" s="203" t="s">
+        <v>2769</v>
+      </c>
+      <c r="G10" s="397" t="s">
+        <v>1557</v>
+      </c>
+      <c r="H10" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I10" s="203" t="s">
+        <v>2770</v>
+      </c>
+      <c r="J10" s="204" t="s">
+        <v>2771</v>
+      </c>
+      <c r="K10" s="204" t="s">
+        <v>2769</v>
+      </c>
+      <c r="L10" s="205" t="s">
+        <v>2772</v>
+      </c>
+      <c r="M10" s="190"/>
+      <c r="N10" s="190"/>
+    </row>
+    <row r="11" ht="25.5" customHeight="1">
+      <c r="A11" s="389"/>
+      <c r="B11" s="390" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C11" s="390" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D11" s="398" t="s">
+        <v>2775</v>
+      </c>
+      <c r="E11" s="398" t="s">
+        <v>2776</v>
+      </c>
+      <c r="F11" s="230" t="s">
+        <v>2777</v>
+      </c>
+      <c r="G11" s="194" t="s">
+        <v>2778</v>
+      </c>
+      <c r="H11" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I11" s="196" t="s">
+        <v>2779</v>
+      </c>
+      <c r="J11" s="197" t="s">
+        <v>2780</v>
+      </c>
+      <c r="K11" s="197" t="s">
+        <v>2777</v>
+      </c>
+      <c r="L11" s="198" t="s">
+        <v>2232</v>
+      </c>
+      <c r="M11" s="190"/>
+      <c r="N11" s="190"/>
+    </row>
+    <row r="12" ht="25.5" customHeight="1">
+      <c r="A12" s="393"/>
+      <c r="B12" s="394" t="s">
+        <v>2781</v>
+      </c>
+      <c r="C12" s="394" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D12" s="399" t="s">
+        <v>2783</v>
+      </c>
+      <c r="E12" s="399" t="s">
+        <v>2784</v>
+      </c>
+      <c r="F12" s="212" t="s">
+        <v>2785</v>
+      </c>
+      <c r="G12" s="194" t="s">
+        <v>2786</v>
+      </c>
+      <c r="H12" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I12" s="203" t="s">
+        <v>2787</v>
+      </c>
+      <c r="J12" s="204" t="s">
+        <v>2788</v>
+      </c>
+      <c r="K12" s="204" t="s">
+        <v>2785</v>
+      </c>
+      <c r="L12" s="205" t="s">
+        <v>2232</v>
+      </c>
+      <c r="M12" s="190"/>
+      <c r="N12" s="190"/>
+    </row>
+    <row r="13" ht="25.5" customHeight="1">
+      <c r="A13" s="389"/>
+      <c r="B13" s="390" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C13" s="390" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D13" s="398" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E13" s="398" t="s">
+        <v>2783</v>
+      </c>
+      <c r="F13" s="230" t="s">
+        <v>2792</v>
+      </c>
+      <c r="G13" s="194" t="s">
+        <v>2793</v>
+      </c>
+      <c r="H13" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I13" s="196" t="s">
+        <v>2794</v>
+      </c>
+      <c r="J13" s="197" t="s">
+        <v>2795</v>
+      </c>
+      <c r="K13" s="197" t="s">
+        <v>2792</v>
+      </c>
+      <c r="L13" s="198" t="s">
+        <v>2232</v>
+      </c>
+      <c r="M13" s="190"/>
+      <c r="N13" s="190"/>
+    </row>
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="A14" s="393"/>
+      <c r="B14" s="394" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C14" s="394" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D14" s="399" t="s">
+        <v>2798</v>
+      </c>
+      <c r="E14" s="399" t="s">
+        <v>2799</v>
+      </c>
+      <c r="F14" s="212" t="s">
+        <v>2800</v>
+      </c>
+      <c r="G14" s="194" t="s">
+        <v>2801</v>
+      </c>
+      <c r="H14" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I14" s="203" t="s">
+        <v>2802</v>
+      </c>
+      <c r="J14" s="204" t="s">
+        <v>2803</v>
+      </c>
+      <c r="K14" s="204" t="s">
+        <v>2800</v>
+      </c>
+      <c r="L14" s="205" t="s">
+        <v>2232</v>
+      </c>
+      <c r="M14" s="190"/>
+      <c r="N14" s="190"/>
+    </row>
+    <row r="15" ht="25.5" customHeight="1">
+      <c r="A15" s="393"/>
+      <c r="B15" s="394" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C15" s="394" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D15" s="399" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E15" s="399" t="s">
+        <v>2807</v>
+      </c>
+      <c r="F15" s="212" t="s">
+        <v>2808</v>
+      </c>
+      <c r="G15" s="194" t="s">
+        <v>2809</v>
+      </c>
+      <c r="H15" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I15" s="203" t="s">
+        <v>2810</v>
+      </c>
+      <c r="J15" s="204" t="s">
+        <v>2811</v>
+      </c>
+      <c r="K15" s="204" t="s">
+        <v>2808</v>
+      </c>
+      <c r="L15" s="205" t="s">
+        <v>2239</v>
+      </c>
+      <c r="M15" s="190"/>
+      <c r="N15" s="190"/>
+    </row>
+    <row r="16" ht="25.5" customHeight="1">
+      <c r="A16" s="389"/>
+      <c r="B16" s="390" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C16" s="390" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D16" s="398" t="s">
+        <v>2814</v>
+      </c>
+      <c r="E16" s="398" t="s">
+        <v>2815</v>
+      </c>
+      <c r="F16" s="230" t="s">
+        <v>2816</v>
+      </c>
+      <c r="G16" s="194" t="s">
+        <v>2817</v>
+      </c>
+      <c r="H16" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I16" s="196" t="s">
+        <v>2818</v>
+      </c>
+      <c r="J16" s="197" t="s">
+        <v>2819</v>
+      </c>
+      <c r="K16" s="197" t="s">
+        <v>2816</v>
+      </c>
+      <c r="L16" s="198" t="s">
+        <v>2239</v>
+      </c>
+      <c r="M16" s="190"/>
+      <c r="N16" s="190"/>
+    </row>
+    <row r="17" ht="25.5" customHeight="1">
+      <c r="A17" s="323" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B17" s="390" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C17" s="390" t="s">
+        <v>2821</v>
+      </c>
+      <c r="D17" s="398" t="s">
+        <v>2822</v>
+      </c>
+      <c r="E17" s="398" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F17" s="230" t="s">
+        <v>2824</v>
+      </c>
+      <c r="G17" s="194" t="s">
+        <v>2825</v>
+      </c>
+      <c r="H17" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I17" s="196" t="s">
+        <v>2826</v>
+      </c>
+      <c r="J17" s="197" t="s">
+        <v>2827</v>
+      </c>
+      <c r="K17" s="197" t="s">
+        <v>2824</v>
+      </c>
+      <c r="L17" s="198" t="s">
+        <v>2828</v>
+      </c>
+      <c r="M17" s="190"/>
+      <c r="N17" s="190"/>
+    </row>
+    <row r="18" ht="25.5" customHeight="1">
+      <c r="A18" s="393"/>
+      <c r="B18" s="394" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C18" s="394" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D18" s="399" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E18" s="399" t="s">
+        <v>2832</v>
+      </c>
+      <c r="F18" s="212" t="s">
+        <v>2833</v>
+      </c>
+      <c r="G18" s="194" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H18" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I18" s="203" t="s">
+        <v>2835</v>
+      </c>
+      <c r="J18" s="204" t="s">
+        <v>2836</v>
+      </c>
+      <c r="K18" s="204" t="s">
+        <v>2833</v>
+      </c>
+      <c r="L18" s="205" t="s">
+        <v>2828</v>
+      </c>
+      <c r="M18" s="190"/>
+      <c r="N18" s="190"/>
+    </row>
+    <row r="19" ht="25.5" customHeight="1">
+      <c r="A19" s="389"/>
+      <c r="B19" s="390" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C19" s="390" t="s">
+        <v>2838</v>
+      </c>
+      <c r="D19" s="398" t="s">
+        <v>2839</v>
+      </c>
+      <c r="E19" s="398" t="s">
+        <v>2840</v>
+      </c>
+      <c r="F19" s="230" t="s">
+        <v>2841</v>
+      </c>
+      <c r="G19" s="194" t="s">
+        <v>2842</v>
+      </c>
+      <c r="H19" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I19" s="196" t="s">
+        <v>2843</v>
+      </c>
+      <c r="J19" s="197" t="s">
+        <v>2844</v>
+      </c>
+      <c r="K19" s="197" t="s">
+        <v>2841</v>
+      </c>
+      <c r="L19" s="198" t="s">
+        <v>2828</v>
+      </c>
+      <c r="M19" s="190"/>
+      <c r="N19" s="190"/>
+    </row>
+    <row r="20" ht="25.5" customHeight="1">
+      <c r="A20" s="393"/>
+      <c r="B20" s="394" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C20" s="394" t="s">
+        <v>2846</v>
+      </c>
+      <c r="D20" s="399" t="s">
+        <v>2847</v>
+      </c>
+      <c r="E20" s="399" t="s">
+        <v>2848</v>
+      </c>
+      <c r="F20" s="212" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G20" s="194" t="s">
+        <v>2850</v>
+      </c>
+      <c r="H20" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I20" s="203" t="s">
+        <v>2851</v>
+      </c>
+      <c r="J20" s="204" t="s">
+        <v>2852</v>
+      </c>
+      <c r="K20" s="204" t="s">
+        <v>2849</v>
+      </c>
+      <c r="L20" s="205" t="s">
+        <v>2853</v>
+      </c>
+      <c r="M20" s="190"/>
+      <c r="N20" s="190"/>
+    </row>
+    <row r="21" ht="25.5" customHeight="1">
+      <c r="A21" s="389"/>
+      <c r="B21" s="390" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C21" s="390" t="s">
+        <v>2855</v>
+      </c>
+      <c r="D21" s="398" t="s">
+        <v>2856</v>
+      </c>
+      <c r="E21" s="398" t="s">
+        <v>2857</v>
+      </c>
+      <c r="F21" s="230" t="s">
+        <v>2858</v>
+      </c>
+      <c r="G21" s="194" t="s">
+        <v>2859</v>
+      </c>
+      <c r="H21" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I21" s="196" t="s">
+        <v>2860</v>
+      </c>
+      <c r="J21" s="197" t="s">
+        <v>2861</v>
+      </c>
+      <c r="K21" s="197" t="s">
+        <v>2858</v>
+      </c>
+      <c r="L21" s="198" t="s">
+        <v>2853</v>
+      </c>
+      <c r="M21" s="190"/>
+      <c r="N21" s="190"/>
+    </row>
+    <row r="22" ht="25.5" customHeight="1">
+      <c r="A22" s="393"/>
+      <c r="B22" s="394" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C22" s="394" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D22" s="399" t="s">
+        <v>2864</v>
+      </c>
+      <c r="E22" s="399" t="s">
+        <v>2865</v>
+      </c>
+      <c r="F22" s="212" t="s">
+        <v>2866</v>
+      </c>
+      <c r="G22" s="194" t="s">
+        <v>2867</v>
+      </c>
+      <c r="H22" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I22" s="203" t="s">
+        <v>2868</v>
+      </c>
+      <c r="J22" s="204" t="s">
+        <v>2869</v>
+      </c>
+      <c r="K22" s="204" t="s">
+        <v>2866</v>
+      </c>
+      <c r="L22" s="205" t="s">
+        <v>2853</v>
+      </c>
+      <c r="M22" s="190"/>
+      <c r="N22" s="190"/>
+    </row>
+    <row r="23" ht="25.5" customHeight="1">
+      <c r="A23" s="393"/>
+      <c r="B23" s="394" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C23" s="394" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D23" s="399" t="s">
+        <v>2872</v>
+      </c>
+      <c r="E23" s="399" t="s">
+        <v>2873</v>
+      </c>
+      <c r="F23" s="212" t="s">
+        <v>2874</v>
+      </c>
+      <c r="G23" s="194" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H23" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I23" s="203" t="s">
+        <v>2875</v>
+      </c>
+      <c r="J23" s="204" t="s">
+        <v>2876</v>
+      </c>
+      <c r="K23" s="204" t="s">
+        <v>2874</v>
+      </c>
+      <c r="L23" s="205" t="s">
+        <v>2295</v>
+      </c>
+      <c r="M23" s="190"/>
+      <c r="N23" s="190"/>
+    </row>
+    <row r="24" ht="25.5" customHeight="1">
+      <c r="A24" s="389"/>
+      <c r="B24" s="390" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C24" s="390" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D24" s="398" t="s">
+        <v>2879</v>
+      </c>
+      <c r="E24" s="398" t="s">
+        <v>2880</v>
+      </c>
+      <c r="F24" s="230" t="s">
+        <v>2881</v>
+      </c>
+      <c r="G24" s="194" t="s">
+        <v>2882</v>
+      </c>
+      <c r="H24" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I24" s="196" t="s">
+        <v>2883</v>
+      </c>
+      <c r="J24" s="197" t="s">
+        <v>2884</v>
+      </c>
+      <c r="K24" s="197" t="s">
+        <v>2881</v>
+      </c>
+      <c r="L24" s="198" t="s">
+        <v>2295</v>
+      </c>
+      <c r="M24" s="190"/>
+      <c r="N24" s="190"/>
+    </row>
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25" s="400"/>
+      <c r="B25" s="401" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C25" s="401" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D25" s="402" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E25" s="402" t="s">
+        <v>2888</v>
+      </c>
+      <c r="F25" s="233" t="s">
+        <v>2889</v>
+      </c>
+      <c r="G25" s="194" t="s">
+        <v>2890</v>
+      </c>
+      <c r="H25" s="403">
+        <v>46139</v>
+      </c>
+      <c r="I25" s="235" t="s">
+        <v>2891</v>
+      </c>
+      <c r="J25" s="236" t="s">
+        <v>2892</v>
+      </c>
+      <c r="K25" s="236" t="s">
+        <v>2889</v>
+      </c>
+      <c r="L25" s="237" t="s">
+        <v>2893</v>
+      </c>
+      <c r="M25" s="190"/>
+      <c r="N25" s="190"/>
+    </row>
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26" s="393"/>
+      <c r="B26" s="394" t="s">
+        <v>2894</v>
+      </c>
+      <c r="C26" s="394" t="s">
+        <v>2895</v>
+      </c>
+      <c r="D26" s="399" t="s">
+        <v>2896</v>
+      </c>
+      <c r="E26" s="399" t="s">
+        <v>2897</v>
+      </c>
+      <c r="F26" s="212" t="s">
+        <v>2898</v>
+      </c>
+      <c r="G26" s="194" t="s">
+        <v>2899</v>
+      </c>
+      <c r="H26" s="396">
+        <v>46139</v>
+      </c>
+      <c r="I26" s="203" t="s">
+        <v>2900</v>
+      </c>
+      <c r="J26" s="204" t="s">
+        <v>2901</v>
+      </c>
+      <c r="K26" s="204" t="s">
+        <v>2898</v>
+      </c>
+      <c r="L26" s="205" t="s">
+        <v>2902</v>
+      </c>
+      <c r="M26" s="190"/>
+      <c r="N26" s="190"/>
+    </row>
+    <row r="27" ht="25.5" customHeight="1">
+      <c r="A27" s="389"/>
+      <c r="B27" s="390" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C27" s="390" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D27" s="398" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E27" s="398" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F27" s="230" t="s">
+        <v>2907</v>
+      </c>
+      <c r="G27" s="194" t="s">
+        <v>2908</v>
+      </c>
+      <c r="H27" s="392">
+        <v>46139</v>
+      </c>
+      <c r="I27" s="196" t="s">
+        <v>2909</v>
+      </c>
+      <c r="J27" s="197" t="s">
+        <v>2910</v>
+      </c>
+      <c r="K27" s="197" t="s">
+        <v>2907</v>
+      </c>
+      <c r="L27" s="198" t="s">
+        <v>2911</v>
+      </c>
+      <c r="M27" s="190"/>
+      <c r="N27" s="190"/>
+    </row>
+    <row r="28" ht="25.5" customHeight="1"/>
+    <row r="29" ht="25.5" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="J2" tooltip=""/>
+    <hyperlink r:id="rId1" ref="K2" tooltip=""/>
+    <hyperlink r:id="rId2" ref="J3" tooltip=""/>
+    <hyperlink r:id="rId2" ref="K3" tooltip=""/>
+    <hyperlink r:id="rId3" ref="J4" tooltip=""/>
+    <hyperlink r:id="rId3" ref="K4" tooltip=""/>
+    <hyperlink r:id="rId4" ref="J5" tooltip=""/>
+    <hyperlink r:id="rId4" ref="K5" tooltip=""/>
+    <hyperlink r:id="rId5" ref="J6" tooltip=""/>
+    <hyperlink r:id="rId5" ref="K6" tooltip=""/>
+    <hyperlink r:id="rId6" ref="J7" tooltip=""/>
+    <hyperlink r:id="rId6" ref="K7" tooltip=""/>
+    <hyperlink r:id="rId7" ref="J8" tooltip=""/>
+    <hyperlink r:id="rId7" ref="K8" tooltip=""/>
+    <hyperlink r:id="rId8" ref="J9" tooltip=""/>
+    <hyperlink r:id="rId8" ref="K9" tooltip=""/>
+    <hyperlink r:id="rId9" ref="J10" tooltip=""/>
+    <hyperlink r:id="rId9" ref="K10" tooltip=""/>
+    <hyperlink r:id="rId10" ref="J11" tooltip=""/>
+    <hyperlink r:id="rId10" ref="K11" tooltip=""/>
+    <hyperlink r:id="rId11" ref="J12" tooltip=""/>
+    <hyperlink r:id="rId11" ref="K12" tooltip=""/>
+    <hyperlink r:id="rId12" ref="J13" tooltip=""/>
+    <hyperlink r:id="rId12" ref="K13" tooltip=""/>
+    <hyperlink r:id="rId13" ref="J14" tooltip=""/>
+    <hyperlink r:id="rId13" ref="K14" tooltip=""/>
+    <hyperlink r:id="rId14" ref="J15" tooltip=""/>
+    <hyperlink r:id="rId14" ref="K15" tooltip=""/>
+    <hyperlink r:id="rId15" ref="J16" tooltip=""/>
+    <hyperlink r:id="rId15" ref="K16" tooltip=""/>
+    <hyperlink r:id="rId16" ref="J17" tooltip=""/>
+    <hyperlink r:id="rId16" ref="K17" tooltip=""/>
+    <hyperlink r:id="rId17" ref="J18" tooltip=""/>
+    <hyperlink r:id="rId17" ref="K18" tooltip=""/>
+    <hyperlink r:id="rId18" ref="J19" tooltip=""/>
+    <hyperlink r:id="rId18" ref="K19" tooltip=""/>
+    <hyperlink r:id="rId19" ref="J20" tooltip=""/>
+    <hyperlink r:id="rId19" ref="K20" tooltip=""/>
+    <hyperlink r:id="rId20" ref="J21" tooltip=""/>
+    <hyperlink r:id="rId20" ref="K21" tooltip=""/>
+    <hyperlink r:id="rId21" ref="J22" tooltip=""/>
+    <hyperlink r:id="rId21" ref="K22" tooltip=""/>
+    <hyperlink r:id="rId22" ref="J23" tooltip=""/>
+    <hyperlink r:id="rId22" ref="K23" tooltip=""/>
+    <hyperlink r:id="rId23" ref="J24" tooltip=""/>
+    <hyperlink r:id="rId23" ref="K24" tooltip=""/>
+    <hyperlink r:id="rId24" ref="J25" tooltip=""/>
+    <hyperlink r:id="rId24" ref="K25" tooltip=""/>
+    <hyperlink r:id="rId25" ref="J26" tooltip=""/>
+    <hyperlink r:id="rId25" ref="K26" tooltip=""/>
+    <hyperlink r:id="rId26" ref="J27" tooltip=""/>
+    <hyperlink r:id="rId26" ref="K27" tooltip=""/>
+  </hyperlinks>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/certificates data.xlsx
+++ b/certificates data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="2912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="2913">
   <si>
     <t xml:space="preserve">Program Name</t>
   </si>
@@ -8743,6 +8743,9 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/17aUuH1zh2QFm_baUArun_GgIrWADaZnP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>PIA</t>
   </si>
   <si>
     <t xml:space="preserve">Dr Nirav, </t>
@@ -9293,7 +9296,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="71">
+  <borders count="70">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -10239,21 +10242,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="2"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="none"/>
@@ -10269,7 +10257,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="404">
+  <cellXfs count="406">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -11355,46 +11343,52 @@
     <xf fontId="34" fillId="6" borderId="25" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="35" fillId="6" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="4" borderId="31" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="34" fillId="6" borderId="36" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="6" borderId="67" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="50" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="50" fillId="4" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="34" fillId="4" borderId="31" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
+    <xf fontId="0" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="50" fillId="6" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="6" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="50" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="34" fillId="6" borderId="36" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="6" borderId="67" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="50" fillId="4" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="50" fillId="6" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="69" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
+    <xf fontId="0" fillId="6" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="50" fillId="6" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="50" fillId="6" borderId="70" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="50" fillId="6" borderId="69" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="34" fillId="6" borderId="48" numFmtId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -27537,7 +27531,9 @@
       <c r="N2" s="190"/>
     </row>
     <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="389"/>
+      <c r="A3" s="389" t="s">
+        <v>2707</v>
+      </c>
       <c r="B3" s="390" t="s">
         <v>2716</v>
       </c>
@@ -27575,26 +27571,28 @@
       <c r="N3" s="190"/>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="393"/>
-      <c r="B4" s="394" t="s">
+      <c r="A4" s="389" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B4" s="393" t="s">
         <v>2723</v>
       </c>
-      <c r="C4" s="394" t="s">
+      <c r="C4" s="393" t="s">
         <v>2724</v>
       </c>
-      <c r="D4" s="394" t="s">
+      <c r="D4" s="393" t="s">
         <v>2725</v>
       </c>
-      <c r="E4" s="394" t="s">
+      <c r="E4" s="393" t="s">
         <v>2726</v>
       </c>
       <c r="F4" s="203" t="s">
         <v>2727</v>
       </c>
-      <c r="G4" s="395" t="s">
+      <c r="G4" s="394" t="s">
         <v>1520</v>
       </c>
-      <c r="H4" s="396">
+      <c r="H4" s="395">
         <v>46139</v>
       </c>
       <c r="I4" s="203" t="s">
@@ -27613,7 +27611,9 @@
       <c r="N4" s="190"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="389"/>
+      <c r="A5" s="389" t="s">
+        <v>2707</v>
+      </c>
       <c r="B5" s="390" t="s">
         <v>2731</v>
       </c>
@@ -27651,26 +27651,28 @@
       <c r="N5" s="190"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="393"/>
-      <c r="B6" s="394" t="s">
+      <c r="A6" s="389" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B6" s="393" t="s">
         <v>2738</v>
       </c>
-      <c r="C6" s="394" t="s">
+      <c r="C6" s="393" t="s">
         <v>2739</v>
       </c>
-      <c r="D6" s="394" t="s">
+      <c r="D6" s="393" t="s">
         <v>2740</v>
       </c>
-      <c r="E6" s="394" t="s">
+      <c r="E6" s="393" t="s">
         <v>2741</v>
       </c>
       <c r="F6" s="203" t="s">
         <v>2742</v>
       </c>
-      <c r="G6" s="395" t="s">
+      <c r="G6" s="394" t="s">
         <v>1532</v>
       </c>
-      <c r="H6" s="396">
+      <c r="H6" s="395">
         <v>46139</v>
       </c>
       <c r="I6" s="203" t="s">
@@ -27689,7 +27691,9 @@
       <c r="N6" s="190"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="389"/>
+      <c r="A7" s="389" t="s">
+        <v>2707</v>
+      </c>
       <c r="B7" s="390" t="s">
         <v>2745</v>
       </c>
@@ -27727,26 +27731,28 @@
       <c r="N7" s="190"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="393"/>
-      <c r="B8" s="394" t="s">
+      <c r="A8" s="389" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B8" s="393" t="s">
         <v>2752</v>
       </c>
-      <c r="C8" s="394" t="s">
+      <c r="C8" s="393" t="s">
         <v>2753</v>
       </c>
-      <c r="D8" s="394" t="s">
+      <c r="D8" s="393" t="s">
         <v>2754</v>
       </c>
-      <c r="E8" s="394" t="s">
+      <c r="E8" s="393" t="s">
         <v>2755</v>
       </c>
       <c r="F8" s="203" t="s">
         <v>2756</v>
       </c>
-      <c r="G8" s="395" t="s">
+      <c r="G8" s="394" t="s">
         <v>1544</v>
       </c>
-      <c r="H8" s="396">
+      <c r="H8" s="395">
         <v>46139</v>
       </c>
       <c r="I8" s="203" t="s">
@@ -27765,7 +27771,9 @@
       <c r="N8" s="190"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="389"/>
+      <c r="A9" s="389" t="s">
+        <v>2707</v>
+      </c>
       <c r="B9" s="390" t="s">
         <v>2759</v>
       </c>
@@ -27803,26 +27811,28 @@
       <c r="N9" s="190"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="393"/>
-      <c r="B10" s="394" t="s">
+      <c r="A10" s="389" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B10" s="393" t="s">
         <v>2766</v>
       </c>
-      <c r="C10" s="394" t="s">
+      <c r="C10" s="393" t="s">
         <v>2767</v>
       </c>
-      <c r="D10" s="394" t="s">
+      <c r="D10" s="393" t="s">
         <v>2482</v>
       </c>
-      <c r="E10" s="394" t="s">
+      <c r="E10" s="393" t="s">
         <v>2768</v>
       </c>
       <c r="F10" s="203" t="s">
         <v>2769</v>
       </c>
-      <c r="G10" s="397" t="s">
+      <c r="G10" s="396" t="s">
         <v>1557</v>
       </c>
-      <c r="H10" s="396">
+      <c r="H10" s="395">
         <v>46139</v>
       </c>
       <c r="I10" s="203" t="s">
@@ -27841,7 +27851,9 @@
       <c r="N10" s="190"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="389"/>
+      <c r="A11" s="397" t="s">
+        <v>1619</v>
+      </c>
       <c r="B11" s="390" t="s">
         <v>2773</v>
       </c>
@@ -27879,17 +27891,19 @@
       <c r="N11" s="190"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="393"/>
-      <c r="B12" s="394" t="s">
+      <c r="A12" s="399" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B12" s="393" t="s">
         <v>2781</v>
       </c>
-      <c r="C12" s="394" t="s">
+      <c r="C12" s="393" t="s">
         <v>2782</v>
       </c>
-      <c r="D12" s="399" t="s">
+      <c r="D12" s="400" t="s">
         <v>2783</v>
       </c>
-      <c r="E12" s="399" t="s">
+      <c r="E12" s="400" t="s">
         <v>2784</v>
       </c>
       <c r="F12" s="212" t="s">
@@ -27898,7 +27912,7 @@
       <c r="G12" s="194" t="s">
         <v>2786</v>
       </c>
-      <c r="H12" s="396">
+      <c r="H12" s="395">
         <v>46139</v>
       </c>
       <c r="I12" s="203" t="s">
@@ -27917,7 +27931,9 @@
       <c r="N12" s="190"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="389"/>
+      <c r="A13" s="399" t="s">
+        <v>1619</v>
+      </c>
       <c r="B13" s="390" t="s">
         <v>2789</v>
       </c>
@@ -27955,17 +27971,19 @@
       <c r="N13" s="190"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="393"/>
-      <c r="B14" s="394" t="s">
+      <c r="A14" s="399" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B14" s="393" t="s">
         <v>2796</v>
       </c>
-      <c r="C14" s="394" t="s">
+      <c r="C14" s="393" t="s">
         <v>2797</v>
       </c>
-      <c r="D14" s="399" t="s">
+      <c r="D14" s="400" t="s">
         <v>2798</v>
       </c>
-      <c r="E14" s="399" t="s">
+      <c r="E14" s="400" t="s">
         <v>2799</v>
       </c>
       <c r="F14" s="212" t="s">
@@ -27974,7 +27992,7 @@
       <c r="G14" s="194" t="s">
         <v>2801</v>
       </c>
-      <c r="H14" s="396">
+      <c r="H14" s="395">
         <v>46139</v>
       </c>
       <c r="I14" s="203" t="s">
@@ -27993,17 +28011,19 @@
       <c r="N14" s="190"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="393"/>
-      <c r="B15" s="394" t="s">
+      <c r="A15" s="399" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B15" s="393" t="s">
         <v>2804</v>
       </c>
-      <c r="C15" s="394" t="s">
+      <c r="C15" s="393" t="s">
         <v>2805</v>
       </c>
-      <c r="D15" s="399" t="s">
+      <c r="D15" s="400" t="s">
         <v>2806</v>
       </c>
-      <c r="E15" s="399" t="s">
+      <c r="E15" s="400" t="s">
         <v>2807</v>
       </c>
       <c r="F15" s="212" t="s">
@@ -28012,7 +28032,7 @@
       <c r="G15" s="194" t="s">
         <v>2809</v>
       </c>
-      <c r="H15" s="396">
+      <c r="H15" s="395">
         <v>46139</v>
       </c>
       <c r="I15" s="203" t="s">
@@ -28031,7 +28051,9 @@
       <c r="N15" s="190"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="389"/>
+      <c r="A16" s="399" t="s">
+        <v>1619</v>
+      </c>
       <c r="B16" s="390" t="s">
         <v>2812</v>
       </c>
@@ -28109,17 +28131,19 @@
       <c r="N17" s="190"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="393"/>
-      <c r="B18" s="394" t="s">
+      <c r="A18" s="324" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B18" s="393" t="s">
         <v>2829</v>
       </c>
-      <c r="C18" s="394" t="s">
+      <c r="C18" s="393" t="s">
         <v>2830</v>
       </c>
-      <c r="D18" s="399" t="s">
+      <c r="D18" s="400" t="s">
         <v>2831</v>
       </c>
-      <c r="E18" s="399" t="s">
+      <c r="E18" s="400" t="s">
         <v>2832</v>
       </c>
       <c r="F18" s="212" t="s">
@@ -28128,7 +28152,7 @@
       <c r="G18" s="194" t="s">
         <v>2834</v>
       </c>
-      <c r="H18" s="396">
+      <c r="H18" s="395">
         <v>46139</v>
       </c>
       <c r="I18" s="203" t="s">
@@ -28147,7 +28171,9 @@
       <c r="N18" s="190"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="389"/>
+      <c r="A19" s="324" t="s">
+        <v>2558</v>
+      </c>
       <c r="B19" s="390" t="s">
         <v>2837</v>
       </c>
@@ -28185,17 +28211,19 @@
       <c r="N19" s="190"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="393"/>
-      <c r="B20" s="394" t="s">
+      <c r="A20" s="324" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B20" s="393" t="s">
         <v>2845</v>
       </c>
-      <c r="C20" s="394" t="s">
+      <c r="C20" s="393" t="s">
         <v>2846</v>
       </c>
-      <c r="D20" s="399" t="s">
+      <c r="D20" s="400" t="s">
         <v>2847</v>
       </c>
-      <c r="E20" s="399" t="s">
+      <c r="E20" s="400" t="s">
         <v>2848</v>
       </c>
       <c r="F20" s="212" t="s">
@@ -28204,7 +28232,7 @@
       <c r="G20" s="194" t="s">
         <v>2850</v>
       </c>
-      <c r="H20" s="396">
+      <c r="H20" s="395">
         <v>46139</v>
       </c>
       <c r="I20" s="203" t="s">
@@ -28223,7 +28251,9 @@
       <c r="N20" s="190"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="389"/>
+      <c r="A21" s="324" t="s">
+        <v>2558</v>
+      </c>
       <c r="B21" s="390" t="s">
         <v>2854</v>
       </c>
@@ -28261,17 +28291,19 @@
       <c r="N21" s="190"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="393"/>
-      <c r="B22" s="394" t="s">
+      <c r="A22" s="324" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B22" s="393" t="s">
         <v>2862</v>
       </c>
-      <c r="C22" s="394" t="s">
+      <c r="C22" s="393" t="s">
         <v>2863</v>
       </c>
-      <c r="D22" s="399" t="s">
+      <c r="D22" s="400" t="s">
         <v>2864</v>
       </c>
-      <c r="E22" s="399" t="s">
+      <c r="E22" s="400" t="s">
         <v>2865</v>
       </c>
       <c r="F22" s="212" t="s">
@@ -28280,7 +28312,7 @@
       <c r="G22" s="194" t="s">
         <v>2867</v>
       </c>
-      <c r="H22" s="396">
+      <c r="H22" s="395">
         <v>46139</v>
       </c>
       <c r="I22" s="203" t="s">
@@ -28299,36 +28331,38 @@
       <c r="N22" s="190"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="393"/>
-      <c r="B23" s="394" t="s">
+      <c r="A23" s="401" t="s">
         <v>2870</v>
       </c>
-      <c r="C23" s="394" t="s">
+      <c r="B23" s="393" t="s">
         <v>2871</v>
       </c>
-      <c r="D23" s="399" t="s">
+      <c r="C23" s="393" t="s">
         <v>2872</v>
       </c>
-      <c r="E23" s="399" t="s">
+      <c r="D23" s="400" t="s">
         <v>2873</v>
       </c>
+      <c r="E23" s="400" t="s">
+        <v>2874</v>
+      </c>
       <c r="F23" s="212" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="G23" s="194" t="s">
         <v>1655</v>
       </c>
-      <c r="H23" s="396">
+      <c r="H23" s="395">
         <v>46139</v>
       </c>
       <c r="I23" s="203" t="s">
+        <v>2876</v>
+      </c>
+      <c r="J23" s="204" t="s">
+        <v>2877</v>
+      </c>
+      <c r="K23" s="204" t="s">
         <v>2875</v>
-      </c>
-      <c r="J23" s="204" t="s">
-        <v>2876</v>
-      </c>
-      <c r="K23" s="204" t="s">
-        <v>2874</v>
       </c>
       <c r="L23" s="205" t="s">
         <v>2295</v>
@@ -28337,36 +28371,38 @@
       <c r="N23" s="190"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="389"/>
+      <c r="A24" s="402" t="s">
+        <v>2870</v>
+      </c>
       <c r="B24" s="390" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="C24" s="390" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="D24" s="398" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="E24" s="398" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="F24" s="230" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="G24" s="194" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="H24" s="392">
         <v>46139</v>
       </c>
       <c r="I24" s="196" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="J24" s="197" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="K24" s="197" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="L24" s="198" t="s">
         <v>2295</v>
@@ -28375,115 +28411,121 @@
       <c r="N24" s="190"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="400"/>
-      <c r="B25" s="401" t="s">
-        <v>2885</v>
-      </c>
-      <c r="C25" s="401" t="s">
+      <c r="A25" s="402" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B25" s="403" t="s">
         <v>2886</v>
       </c>
-      <c r="D25" s="402" t="s">
+      <c r="C25" s="403" t="s">
         <v>2887</v>
       </c>
-      <c r="E25" s="402" t="s">
+      <c r="D25" s="404" t="s">
         <v>2888</v>
       </c>
+      <c r="E25" s="404" t="s">
+        <v>2889</v>
+      </c>
       <c r="F25" s="233" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="G25" s="194" t="s">
+        <v>2891</v>
+      </c>
+      <c r="H25" s="405">
+        <v>46139</v>
+      </c>
+      <c r="I25" s="235" t="s">
+        <v>2892</v>
+      </c>
+      <c r="J25" s="236" t="s">
+        <v>2893</v>
+      </c>
+      <c r="K25" s="236" t="s">
         <v>2890</v>
       </c>
-      <c r="H25" s="403">
-        <v>46139</v>
-      </c>
-      <c r="I25" s="235" t="s">
-        <v>2891</v>
-      </c>
-      <c r="J25" s="236" t="s">
-        <v>2892</v>
-      </c>
-      <c r="K25" s="236" t="s">
-        <v>2889</v>
-      </c>
       <c r="L25" s="237" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="M25" s="190"/>
       <c r="N25" s="190"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="393"/>
-      <c r="B26" s="394" t="s">
-        <v>2894</v>
-      </c>
-      <c r="C26" s="394" t="s">
+      <c r="A26" s="402" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B26" s="393" t="s">
         <v>2895</v>
       </c>
-      <c r="D26" s="399" t="s">
+      <c r="C26" s="393" t="s">
         <v>2896</v>
       </c>
-      <c r="E26" s="399" t="s">
+      <c r="D26" s="400" t="s">
         <v>2897</v>
       </c>
+      <c r="E26" s="400" t="s">
+        <v>2898</v>
+      </c>
       <c r="F26" s="212" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="G26" s="194" t="s">
+        <v>2900</v>
+      </c>
+      <c r="H26" s="395">
+        <v>46139</v>
+      </c>
+      <c r="I26" s="203" t="s">
+        <v>2901</v>
+      </c>
+      <c r="J26" s="204" t="s">
+        <v>2902</v>
+      </c>
+      <c r="K26" s="204" t="s">
         <v>2899</v>
       </c>
-      <c r="H26" s="396">
-        <v>46139</v>
-      </c>
-      <c r="I26" s="203" t="s">
-        <v>2900</v>
-      </c>
-      <c r="J26" s="204" t="s">
-        <v>2901</v>
-      </c>
-      <c r="K26" s="204" t="s">
-        <v>2898</v>
-      </c>
       <c r="L26" s="205" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="M26" s="190"/>
       <c r="N26" s="190"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="389"/>
+      <c r="A27" s="402" t="s">
+        <v>2870</v>
+      </c>
       <c r="B27" s="390" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="C27" s="390" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="D27" s="398" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="E27" s="398" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="F27" s="230" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="G27" s="194" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="H27" s="392">
         <v>46139</v>
       </c>
       <c r="I27" s="196" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="J27" s="197" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="K27" s="197" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="L27" s="198" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="M27" s="190"/>
       <c r="N27" s="190"/>

--- a/certificates data.xlsx
+++ b/certificates data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3070" uniqueCount="3070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3060" uniqueCount="3060">
   <si>
     <t xml:space="preserve">Program Name</t>
   </si>
@@ -7143,1771 +7143,1741 @@
     <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:11 AM</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Anoop K S </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nikita V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaumarabhritya Part B</t>
+  </si>
+  <si>
+    <t>2526ECD0458</t>
+  </si>
+  <si>
+    <t>1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:12 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Rahul Jadhav</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Vivek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Methodology and Medical-statistics</t>
+  </si>
+  <si>
+    <t>2526ECD0459</t>
+  </si>
+  <si>
+    <t>1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPER ( Pharmacy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vivek Joshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Seena Sunil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human Anatomy and Physiology</t>
+  </si>
+  <si>
+    <t>2526ECD0465</t>
+  </si>
+  <si>
+    <t>1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:56 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Devshree Parmar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Yash Janve</t>
+  </si>
+  <si>
+    <t>Pharmacology–Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0466</t>
+  </si>
+  <si>
+    <t>1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Vrundaben Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Jenish Bhagat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community Pharmacy &amp; Management – Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0467</t>
+  </si>
+  <si>
+    <t>177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Rasana Yadav </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Soniya Yadav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmacotherapeutics – Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0468</t>
+  </si>
+  <si>
+    <t>14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Srushti Shah </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Vishva Patel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital &amp; Clinical Pharmacy – Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0469</t>
+  </si>
+  <si>
+    <t>1wcLOrmkHORoFVytxRv78yqDEh1-IRszk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wcLOrmkHORoFVytxRv78yqDEh1-IRszk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIA AYurveda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Narendra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Tanjila</t>
+  </si>
+  <si>
+    <t>2526ECD0483</t>
+  </si>
+  <si>
+    <t>1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:51 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aswini Patil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Veena</t>
+  </si>
+  <si>
+    <t>12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:52 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Mahadevi B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Parth Akhani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dravyaguna Vigyan paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0486</t>
+  </si>
+  <si>
+    <t>1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. POONAM BHOJAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. HARISANKAR K T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agad Tantra evam Vidhi Vaidyaka part B</t>
+  </si>
+  <si>
+    <t>2526ECD0488</t>
+  </si>
+  <si>
+    <t>12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Mrunal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Akshatha K </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roga Nidan evam Vikriti Vigyan Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0489</t>
+  </si>
+  <si>
+    <t>1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:53 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Vasuprada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. MAULI VAISHNAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prasuti Tantra evam Stree Roga Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0494</t>
+  </si>
+  <si>
+    <t>1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>PIPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Tularam Barot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms Swathi G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biopharmaceutics &amp; Pharmacokinetics</t>
+  </si>
+  <si>
+    <t>1YVHFyliDEGRe-vNTVP0Wt8BC37xF1omL</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YVHFyliDEGRe-vNTVP0Wt8BC37xF1omL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 5 2026 4:48 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Mohit Buddhadev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Priyal Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical Research</t>
+  </si>
+  <si>
+    <t>1VDw44rE9HXpXw0KK2zzyKeE_swS-ShiU</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VDw44rE9HXpXw0KK2zzyKeE_swS-ShiU/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. S.P Nayak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. John Kirubakaran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical Pharmacokinetics &amp; Pharmacotherapeutic Drug Monitoring</t>
+  </si>
+  <si>
+    <t>1ciSm0S55F2CP6xM9kGhMfiSNJU_GWvFO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ciSm0S55F2CP6xM9kGhMfiSNJU_GWvFO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Bipin Shaji</t>
+  </si>
+  <si>
+    <t>1NuzxpEn3l_LZhSXU-gEkwOuY913Wf3qK</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NuzxpEn3l_LZhSXU-gEkwOuY913Wf3qK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 5 2026 4:49 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name to be Printed on certificate 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc ID - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc URL - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link to merged Doc - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document Merge Status - 3 E - content Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialization - Cyber Security and Forensics - I</t>
+  </si>
+  <si>
+    <t>2526ECD0164</t>
+  </si>
+  <si>
+    <t>1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 3:44 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Renuka Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Gaurav Kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Priya Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialization - Full Stack Web Development - I</t>
+  </si>
+  <si>
+    <t>2526ECD0165</t>
+  </si>
+  <si>
+    <t>1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Satish Chauhan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Meet Soni </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Shubhrajyoti Kundu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical and Electronics Engineering</t>
+  </si>
+  <si>
+    <t>2526ECD0166</t>
+  </si>
+  <si>
+    <t>1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 4:33 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Kartik Pandya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Mahit Jain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Electrical Engineering</t>
+  </si>
+  <si>
+    <t>2526ECD0167</t>
+  </si>
+  <si>
+    <t>1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ankitsinh Zala</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Divya Garg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Niti Shah</t>
+  </si>
+  <si>
+    <t>CVPDE</t>
+  </si>
+  <si>
+    <t>2526ECD0168</t>
+  </si>
+  <si>
+    <t>1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Purvesh Valanad</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr.  Mujahid Mirchiwala</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Gaurav Sahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC-1 (D.C Circuit)</t>
+  </si>
+  <si>
+    <t>2526ECD0205</t>
+  </si>
+  <si>
+    <t>1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:15 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Mayank Vyas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.  Ankit Patel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.  Nishant Hadiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction to Electrical Safety &amp; Management</t>
+  </si>
+  <si>
+    <t>2526ECD0206</t>
+  </si>
+  <si>
+    <t>1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:16 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Hetal Prajapati</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Pavez Vasovala </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamental of Electrical Engineering</t>
+  </si>
+  <si>
+    <t>2526ECD0207</t>
+  </si>
+  <si>
+    <t>1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Krunal Kayasth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.Jayesh Mahant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.Manthan Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Graphics </t>
+  </si>
+  <si>
+    <t>2526ECD0208</t>
+  </si>
+  <si>
+    <t>1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bhumi Bhoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Piyush Mali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Shreen Gazala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Of Things</t>
+  </si>
+  <si>
+    <t>2526ECD0209</t>
+  </si>
+  <si>
+    <t>19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ashish Pandey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Prachi Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ravi Bhardwaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Security</t>
+  </si>
+  <si>
+    <t>2526ECD0210</t>
+  </si>
+  <si>
+    <t>1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Kausal kalariya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bipasha Mandal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Hemali Nimavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operating system </t>
+  </si>
+  <si>
+    <t>2526ECD0211</t>
+  </si>
+  <si>
+    <t>1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Mansi Rana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Kavita Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Bankim Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object Oriented Programming with C++</t>
+  </si>
+  <si>
+    <t>2526ECD0212</t>
+  </si>
+  <si>
+    <t>1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:17 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. DEVANSHI THAKKAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. AMITA TAILOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. SHILPA KHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web Design and Development</t>
+  </si>
+  <si>
+    <t>2526ECD0346</t>
+  </si>
+  <si>
+    <t>1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:47 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. VAIBHAVI PANDYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. RIYA DESAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr.HARDIK KUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Structure </t>
+  </si>
+  <si>
+    <t>2526ECD0347</t>
+  </si>
+  <si>
+    <t>1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. BHAVYA GAJIWALA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. KAVYA PRAJAPATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. POONAM FALDU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Network</t>
+  </si>
+  <si>
+    <t>2526ECD0348</t>
+  </si>
+  <si>
+    <t>1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:48 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. KALPANA PRAJAPATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. DEVIKA KSHTRIYA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. VIJAY VASAIYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.Net Programming with C# </t>
+  </si>
+  <si>
+    <t>2526ECD0349</t>
+  </si>
+  <si>
+    <t>159BT_GO9SchY3qO-sK9fZg4H87gfmKd8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/159BT_GO9SchY3qO-sK9fZg4H87gfmKd8/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Vrunda patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ankit Padariya, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Suraj singh</t>
+  </si>
+  <si>
+    <t>2526ECD0350</t>
+  </si>
+  <si>
+    <t>1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Radhika Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BK Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bhavya shah</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>2526ECD0351</t>
+  </si>
+  <si>
+    <t>1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Shivani Shelke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Shivani Gupta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Suraj Singh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Communication Network</t>
+  </si>
+  <si>
+    <t>2526ECD0352</t>
+  </si>
+  <si>
+    <t>1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Hiral Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Rachana S. Kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Harshrajsinh Rana</t>
+  </si>
+  <si>
+    <t>Pharmaceutics</t>
+  </si>
+  <si>
+    <t>2526ECD0353</t>
+  </si>
+  <si>
+    <t>16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 3:20 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Tora Shah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Bhargavi Mistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Krutika Agarwal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmaceutics –Theory</t>
+  </si>
+  <si>
+    <t>2526ECD0354</t>
+  </si>
+  <si>
+    <t>1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mrs. Priyanka Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Priyank Makwana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Krishna Gohil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematics - I</t>
+  </si>
+  <si>
+    <t>2526ECD405</t>
+  </si>
+  <si>
+    <t>1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 28 2026 5:51 AM</t>
+  </si>
+  <si>
+    <t>Physiotheraphy</t>
+  </si>
+  <si>
+    <t>Dr.Pooja</t>
+  </si>
+  <si>
+    <t>Dr.Vrunda</t>
+  </si>
+  <si>
+    <t>Dr.Siddharth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomechanics and Kinesiology-I</t>
+  </si>
+  <si>
+    <t>2526ECD426</t>
+  </si>
+  <si>
+    <t>1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Pooja-Dr.Vrunda-Dr.Siddharth-Biomechanics and Kinesiology-I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:49 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Bhavik Thacker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Sonal Poojara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Vaishali Nathwani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied physics</t>
+  </si>
+  <si>
+    <t>1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Bhavik Thacker-Ms. Sonal Poojara-Ms. Vaishali Nathwani-Applied physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 2:16 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Ravi Joshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Amarjeet Kaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Mital Kanani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachana Sharir (Human Anatomy) Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0460</t>
+  </si>
+  <si>
+    <t>1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Ravi Joshi-Dr.Amarjeet Kaur-Dr.Mital Kanani-Rachana Sharir (Human Anatomy) Paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:09 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nikita P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Kruti P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Smita Rai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dravyaguna Vigyan paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0461</t>
+  </si>
+  <si>
+    <t>1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nikita P-Dr. Kruti P-Dr.Smita Rai-Dravyaguna Vigyan paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Palak C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Jignesha P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Milind C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rasashastra evam Bhaishajyakalpana paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0462</t>
+  </si>
+  <si>
+    <t>1fZiljGMmRqmPperHUIzG1NAFD138oohm</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fZiljGMmRqmPperHUIzG1NAFD138oohm/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Palak C-Dr. Jignesha P-Dr. Milind C-Rasashastra evam Bhaishajyakalpana paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Reshma Shaji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Vivek M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Archana Panchaksharimath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swasthavritta evam Yoga Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0463</t>
+  </si>
+  <si>
+    <t>1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Reshma Shaji-Dr. Vivek M-Dr. Archana Panchaksharimath-Swasthavritta evam Yoga Paper 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Sathish Mittapalli </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Rahul Barot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Janavi Raut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmaceutical Organic Chemistry</t>
+  </si>
+  <si>
+    <t>2526ECD0464</t>
+  </si>
+  <si>
+    <t>15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Sathish Mittapalli - Mr. Rahul Barot -Ms. Janavi Raut-Pharmaceutical Organic Chemistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:54 AM</t>
+  </si>
+  <si>
+    <t>JNHMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Uma Sahoo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Upma Raval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Vinit Tapas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physiology and Biochemistry</t>
+  </si>
+  <si>
+    <t>2526ECD0476</t>
+  </si>
+  <si>
+    <t>1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Uma Sahoo-Dr Upma Raval-Dr Vinit Tapas-Physiology and Biochemistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:18 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Naresh Bhusara </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Nayana Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Neelima Sharan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homoeopathic Pharmacy</t>
+  </si>
+  <si>
+    <t>2526ECD0477</t>
+  </si>
+  <si>
+    <t>11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Naresh Bhusara -Dr Nayana Patel-Dr Neelima Sharan-Homoeopathic Pharmacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Vani Oza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Archana Tegwal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Preeti Mulani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homoeopathic Materia Medica</t>
+  </si>
+  <si>
+    <t>2526ECD0478</t>
+  </si>
+  <si>
+    <t>1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Vani Oza-Dr Archana Tegwal-Dr Preeti Mulani-Homoeopathic Materia Medica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Pragya Srivastva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Preeti Pathak </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Amar Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pathology and Microbiology</t>
+  </si>
+  <si>
+    <t>2526ECD0479</t>
+  </si>
+  <si>
+    <t>1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Pragya Srivastva-Dr Preeti Pathak -Dr Amar Thakkar-Pathology and Microbiology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Smit Dad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Astha Rawal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Dhwani Thakkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice of Medicine</t>
+  </si>
+  <si>
+    <t>2526ECD0480</t>
+  </si>
+  <si>
+    <t>1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Smit Dad-Dr Astha Rawal-Dr Dhwani Thakkar-Practice of Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aparna Bagul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Rajalekshmi R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Hari Sankar M S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swasthavritta evam Yoga Paper 1</t>
+  </si>
+  <si>
+    <t>2526ECD0481</t>
+  </si>
+  <si>
+    <t>1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Aparna Bagul-Dr Rajalekshmi R-Dr Hari Sankar M S-Swasthavritta evam Yoga Paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:58 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Jaiminikumari Mahendrasinh Rathod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nishant Nareshbhai Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
+  </si>
+  <si>
+    <t>2526ECD0482</t>
+  </si>
+  <si>
+    <t>1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE-Dr. Jaiminikumari Mahendrasinh Rathod-Dr. Nishant Nareshbhai Patel-Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. PARIKSHIT RAMAKANT SHIRODE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. PRAJAPATI HARSHADKUMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shalya Tantra Paper 2</t>
+  </si>
+  <si>
+    <t>2526ECD0491</t>
+  </si>
+  <si>
+    <t>1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari-Dr. PARIKSHIT RAMAKANT SHIRODE -Dr. PRAJAPATI HARSHADKUMAR-Shalya Tantra Paper 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 5:07 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Jalpa Zalawadia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sumit Das Lala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krishnamraju Putta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop and Manufacturing Practice</t>
+  </si>
+  <si>
+    <t>1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Jalpa Zalawadia-Dr. Sumit Das Lala-Krishnamraju Putta-Workshop and Manufacturing Practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:24 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vishal Jain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Nishant Rajput</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Omprakash Bharti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elements of Thermal and Fluid Sciences</t>
+  </si>
+  <si>
+    <t>1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vishal Jain-Mr. Nishant Rajput-Dr. Omprakash Bharti-Elements of Thermal and Fluid Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:26 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Manan Shah </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Akash Shukla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Hitesh Dave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Graphics and Design</t>
+  </si>
+  <si>
+    <t>1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Manan Shah -Mr. Akash Shukla-Mr. Hitesh Dave-Engineering Graphics and Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Kalmesh Parmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. Swati Prajapati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elements of Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>1Qpkh7V28vWumf7dxUwEu-eF9NLCVIJ8E</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Qpkh7V28vWumf7dxUwEu-eF9NLCVIJ8E/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Kalmesh Parmar-Mr. Vishal Jain-Ms. Swati Prajapati-Elements of Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>PIPTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Rushikesh Joshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Pooja Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Tanvi Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomedical Physics</t>
+  </si>
+  <si>
+    <t>1puGdke6h1uPM_P2PZDipi-LWpucG4B4D</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1puGdke6h1uPM_P2PZDipi-LWpucG4B4D/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Rushikesh Joshi-Dr.Pooja Soni-Dr.Tanvi Patel-Biomedical Physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 4 2026 4:11 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Sandip Parekh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Gopi Panchmatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Darpan Vanavi</t>
+  </si>
+  <si>
+    <t>Electrotherapy-II</t>
+  </si>
+  <si>
+    <t>1DxtGtfqKb0TJxGXIFjJlPRpEAviIaSz3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DxtGtfqKb0TJxGXIFjJlPRpEAviIaSz3/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Sandip Parekh-Dr.Gopi Panchmatia-Dr.Darpan Vanavi-Electrotherapy-II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Monali Soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Payal Bhardva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Parth Prajapati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise Therapy II</t>
+  </si>
+  <si>
+    <t>1ra54wyU7EBWabC2HDdED01oTtce-nVXL</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ra54wyU7EBWabC2HDdED01oTtce-nVXL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Monali Soni-Dr.Payal Bhardva-Dr.Parth Prajapati-Exercise Therapy II</t>
+  </si>
+  <si>
+    <t>PIAYR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dr. Sambu Surendran</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Sahil Patel</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Dhriti Khandelwal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shalya Tantra Paper 1</t>
   </si>
   <si>
-    <t>2526ECD0455</t>
-  </si>
-  <si>
-    <t>1932qQ9e91it8wqRW1XB9cY_eKbmgu3Ct</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1932qQ9e91it8wqRW1XB9cY_eKbmgu3Ct/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:12 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Anoop K S </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nikita V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaumarabhritya Part B</t>
-  </si>
-  <si>
-    <t>2526ECD0458</t>
-  </si>
-  <si>
-    <t>1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1LrwCLfpBvkvXyhd3hGy8rulOHssMrfKI/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Rahul Jadhav</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Vivek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Methodology and Medical-statistics</t>
-  </si>
-  <si>
-    <t>2526ECD0459</t>
-  </si>
-  <si>
-    <t>1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CMXyvvEq9Sbfa8k9y7lqnQ-muNl13bGL/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPER ( Pharmacy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vivek Joshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Seena Sunil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Anatomy and Physiology</t>
-  </si>
-  <si>
-    <t>2526ECD0465</t>
-  </si>
-  <si>
-    <t>1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1pWmf1cpdF7igQj1i5dkCgVZ3A8GM_blK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:56 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ms. Devshree Parmar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Yash Janve</t>
-  </si>
-  <si>
-    <t>Pharmacology–Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0466</t>
-  </si>
-  <si>
-    <t>1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1sv5Q6Fp2PrE7KUrEBVhqBvtMxgJSGOUQ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Vrundaben Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ms. Jenish Bhagat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community Pharmacy &amp; Management – Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0467</t>
-  </si>
-  <si>
-    <t>177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/177LhNaMLSPHJMOa5I32Z2C8awywzrW3Y/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Rasana Yadav </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Soniya Yadav</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmacotherapeutics – Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0468</t>
-  </si>
-  <si>
-    <t>14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14vAAYceRHXsXE6HZIHI-KB-ntVunVT8b/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Srushti Shah </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Vishva Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospital &amp; Clinical Pharmacy – Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0469</t>
-  </si>
-  <si>
-    <t>1wcLOrmkHORoFVytxRv78yqDEh1-IRszk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wcLOrmkHORoFVytxRv78yqDEh1-IRszk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIA AYurveda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Narendra </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Tanjila</t>
-  </si>
-  <si>
-    <t>2526ECD0483</t>
-  </si>
-  <si>
-    <t>1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wJRTRCW1LoXt98bNM8UwDW11DnzhbzPO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:51 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Aswini Patil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Veena</t>
-  </si>
-  <si>
-    <t>12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/12hl2xwrwaoK7CiOJqdiJJcSSVfokBPuz/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:52 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Mahadevi B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Parth Akhani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dravyaguna Vigyan paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0486</t>
-  </si>
-  <si>
-    <t>1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rhVMIyKU6O-vQcCLqOX4wfcUkh-5JEP1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. POONAM BHOJAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. HARISANKAR K T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agad Tantra evam Vidhi Vaidyaka part B</t>
-  </si>
-  <si>
-    <t>2526ECD0488</t>
-  </si>
-  <si>
-    <t>12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/12pvl_0BQ5o35MlgWgNYJuVK8IbjAIjcf/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Mrunal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Akshatha K </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roga Nidan evam Vikriti Vigyan Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0489</t>
-  </si>
-  <si>
-    <t>1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VR-iHyImKnoS0BJM9Fk0O5fN1L1rXoAi/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:53 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Vasuprada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. MAULI VAISHNAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prasuti Tantra evam Stree Roga Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0494</t>
-  </si>
-  <si>
-    <t>1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1_krHK6SaGeCg5mvPyopXI775zDhKu0Tn/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>PIPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Tularam Barot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms Swathi G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biopharmaceutics &amp; Pharmacokinetics</t>
-  </si>
-  <si>
-    <t>1YVHFyliDEGRe-vNTVP0Wt8BC37xF1omL</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YVHFyliDEGRe-vNTVP0Wt8BC37xF1omL/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 5 2026 4:48 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Mohit Buddhadev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Priyal Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinical Research</t>
-  </si>
-  <si>
-    <t>1VDw44rE9HXpXw0KK2zzyKeE_swS-ShiU</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VDw44rE9HXpXw0KK2zzyKeE_swS-ShiU/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. S.P Nayak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. John Kirubakaran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinical Pharmacokinetics &amp; Pharmacotherapeutic Drug Monitoring</t>
-  </si>
-  <si>
-    <t>1ciSm0S55F2CP6xM9kGhMfiSNJU_GWvFO</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ciSm0S55F2CP6xM9kGhMfiSNJU_GWvFO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Bipin Shaji</t>
-  </si>
-  <si>
-    <t>1NuzxpEn3l_LZhSXU-gEkwOuY913Wf3qK</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1NuzxpEn3l_LZhSXU-gEkwOuY913Wf3qK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 5 2026 4:49 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name to be Printed on certificate 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Doc ID - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Doc URL - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link to merged Doc - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document Merge Status - 3 E - content Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialization - Cyber Security and Forensics - I</t>
-  </si>
-  <si>
-    <t>2526ECD0164</t>
-  </si>
-  <si>
-    <t>1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 3:44 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Renuka Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Gaurav Kumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Priya Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialization - Full Stack Web Development - I</t>
-  </si>
-  <si>
-    <t>2526ECD0165</t>
-  </si>
-  <si>
-    <t>1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Satish Chauhan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Meet Soni </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Shubhrajyoti Kundu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical and Electronics Engineering</t>
-  </si>
-  <si>
-    <t>2526ECD0166</t>
-  </si>
-  <si>
-    <t>1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 4:33 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Kartik Pandya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Mahit Jain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic Electrical Engineering</t>
-  </si>
-  <si>
-    <t>2526ECD0167</t>
-  </si>
-  <si>
-    <t>1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ankitsinh Zala</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ms. Divya Garg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Niti Shah</t>
-  </si>
-  <si>
-    <t>CVPDE</t>
-  </si>
-  <si>
-    <t>2526ECD0168</t>
-  </si>
-  <si>
-    <t>1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Purvesh Valanad</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr.  Mujahid Mirchiwala</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Gaurav Sahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC-1 (D.C Circuit)</t>
-  </si>
-  <si>
-    <t>2526ECD0205</t>
-  </si>
-  <si>
-    <t>1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:15 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Mayank Vyas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.  Ankit Patel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.  Nishant Hadiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduction to Electrical Safety &amp; Management</t>
-  </si>
-  <si>
-    <t>2526ECD0206</t>
-  </si>
-  <si>
-    <t>1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:16 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Hetal Prajapati</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Pavez Vasovala </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundamental of Electrical Engineering</t>
-  </si>
-  <si>
-    <t>2526ECD0207</t>
-  </si>
-  <si>
-    <t>1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Krunal Kayasth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.Jayesh Mahant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.Manthan Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Graphics </t>
-  </si>
-  <si>
-    <t>2526ECD0208</t>
-  </si>
-  <si>
-    <t>1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bhumi Bhoi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Piyush Mali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Shreen Gazala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Of Things</t>
-  </si>
-  <si>
-    <t>2526ECD0209</t>
-  </si>
-  <si>
-    <t>19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ashish Pandey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Prachi Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ravi Bhardwaj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Security</t>
-  </si>
-  <si>
-    <t>2526ECD0210</t>
-  </si>
-  <si>
-    <t>1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Kausal kalariya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bipasha Mandal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Hemali Nimavat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operating system </t>
-  </si>
-  <si>
-    <t>2526ECD0211</t>
-  </si>
-  <si>
-    <t>1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Mansi Rana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Kavita Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Bankim Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Object Oriented Programming with C++</t>
-  </si>
-  <si>
-    <t>2526ECD0212</t>
-  </si>
-  <si>
-    <t>1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 24 2026 5:17 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. DEVANSHI THAKKAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. AMITA TAILOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. SHILPA KHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web Design and Development</t>
-  </si>
-  <si>
-    <t>2526ECD0346</t>
-  </si>
-  <si>
-    <t>1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:47 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. VAIBHAVI PANDYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. RIYA DESAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr.HARDIK KUMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Structure </t>
-  </si>
-  <si>
-    <t>2526ECD0347</t>
-  </si>
-  <si>
-    <t>1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. BHAVYA GAJIWALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. KAVYA PRAJAPATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. POONAM FALDU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Network</t>
-  </si>
-  <si>
-    <t>2526ECD0348</t>
-  </si>
-  <si>
-    <t>1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 26 2026 11:48 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. KALPANA PRAJAPATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. DEVIKA KSHTRIYA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. VIJAY VASAIYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.Net Programming with C# </t>
-  </si>
-  <si>
-    <t>2526ECD0349</t>
-  </si>
-  <si>
-    <t>159BT_GO9SchY3qO-sK9fZg4H87gfmKd8</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/159BT_GO9SchY3qO-sK9fZg4H87gfmKd8/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Vrunda patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ankit Padariya, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Suraj singh</t>
-  </si>
-  <si>
-    <t>2526ECD0350</t>
-  </si>
-  <si>
-    <t>1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Radhika Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BK Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bhavya shah</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>2526ECD0351</t>
-  </si>
-  <si>
-    <t>1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Shivani Shelke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Shivani Gupta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Suraj Singh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Communication Network</t>
-  </si>
-  <si>
-    <t>2526ECD0352</t>
-  </si>
-  <si>
-    <t>1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Hiral Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Rachana S. Kumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Harshrajsinh Rana</t>
-  </si>
-  <si>
-    <t>Pharmaceutics</t>
-  </si>
-  <si>
-    <t>2526ECD0353</t>
-  </si>
-  <si>
-    <t>16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 3:20 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Tora Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Bhargavi Mistry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Krutika Agarwal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmaceutics –Theory</t>
-  </si>
-  <si>
-    <t>2526ECD0354</t>
-  </si>
-  <si>
-    <t>1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1/view?usp=drivesdk</t>
+    <t>1gVk0r3EMmebxgdRh0E25hgA5k5r07V_z</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gVk0r3EMmebxgdRh0E25hgA5k5r07V_z/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sambu Surendran-Dr. Sahil Patel-Dr. Dhriti Khandelwal-Shalya Tantra Paper 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 6 2026 1:26 AM</t>
+  </si>
+  <si>
+    <t>autocratn</t>
+  </si>
+  <si>
+    <t>autocratp</t>
+  </si>
+  <si>
+    <t>dataSheetName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Form Responses 1"</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>"5.1"</t>
+  </si>
+  <si>
+    <t>dataSheetId</t>
+  </si>
+  <si>
+    <t>"6.50628832E8"</t>
+  </si>
+  <si>
+    <t>updateTime</t>
+  </si>
+  <si>
+    <t>"1.777270430007E12"</t>
+  </si>
+  <si>
+    <t>vp</t>
+  </si>
+  <si>
+    <t>ssId</t>
+  </si>
+  <si>
+    <t>"1XAffx2osIAaU40eNPfh9ozyEJ0Jv8Cac9e2lgVmJ_5Y"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Sheet ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Data Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share As</t>
+  </si>
+  <si>
+    <t>Folders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic Folder Reference</t>
+  </si>
+  <si>
+    <t>Conditionals</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Append Breaks</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run On Time Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Trigger Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run On Form Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send Email And Share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email BCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Reply To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email No Reply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevent Resharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Trigger Timestamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form Trigger Timestamp</t>
+  </si>
+  <si>
+    <t>_1777010583975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) E content certificate</t>
+  </si>
+  <si>
+    <t>1hyfm2hOwN-su9PZzJQCcmUAJfsTj_Tuv6JRyBkz19SU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;&lt;Name to be Printed on Certificate&gt;&gt;-&lt;&lt;Subject&gt;&gt;</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>["1APY_TOVAsRdET2TZ1CeJ3l6lXbibUj-U"]</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>MULTIPLE_OUTPUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Sr No"},"tag":"Sr No"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Date"},"tag":"Date"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Subject"},"tag":"Subject"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Name to be Printed on Certificate"},"tag":"Name"}]</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name to be Printed on Certificate 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name to be Printed on Certificate 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc ID - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged Doc URL - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link to merged Doc - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document Merge Status - 2 Econtent Certificate</t>
+  </si>
+  <si>
+    <t>PHYSIOTHERAPHY</t>
+  </si>
+  <si>
+    <t>Dr.Rinkal</t>
+  </si>
+  <si>
+    <t>Dr.Asha</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr.Prachi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr.Dhaval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentals of ET-1</t>
+  </si>
+  <si>
+    <t>1gyUMYvdoAWp93yhR5yYZKB7kN6VS2SxE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gyUMYvdoAWp93yhR5yYZKB7kN6VS2SxE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:51 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.RUSHIKESH JOSHI, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.TANVI PATEL, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.POOJA SONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.NIDHI MANGROLIA</t>
+  </si>
+  <si>
+    <t>1RomXGXq4D02P0f3OIuBCfx5HuIEalA7w</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RomXGXq4D02P0f3OIuBCfx5HuIEalA7w/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Dr.Meghavi,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Heli, </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr.Sonal</t>
+  </si>
+  <si>
+    <t>Dr.Mansi</t>
+  </si>
+  <si>
+    <t>Electrotherapy-I</t>
+  </si>
+  <si>
+    <t>1kk-n50-lgKa2Efjs186_3l_ydH-m83HN</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kk-n50-lgKa2Efjs186_3l_ydH-m83HN/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:52 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Priyanka,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Simrah, </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Madhavi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Didhiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapeutics of Exercise Therapy-I</t>
+  </si>
+  <si>
+    <t>1H2hyQG6O2w0pM_3K6xpCqWfDUAdyVq2u</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1H2hyQG6O2w0pM_3K6xpCqWfDUAdyVq2u/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Jigisha, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Advita, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Joyal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Nilesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapeutics of Exercise Therapy-II</t>
+  </si>
+  <si>
+    <t>1nOYQgrmFO5MQqh5kDUnf05OxlJc20Y8P</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nOYQgrmFO5MQqh5kDUnf05OxlJc20Y8P/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Dhwani, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Dwija, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Chaitali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Dharmang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomechanics and Kinesiology-II</t>
+  </si>
+  <si>
+    <t>1PbxtA94A1_2lqEzrLOgMEK0CWlhdnE6C</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PbxtA94A1_2lqEzrLOgMEK0CWlhdnE6C/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.SANDIP PAREKH, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.PRAKRUTI PARIKH, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.GOPI PANCHMATIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.DARPAN VANAVI</t>
+  </si>
+  <si>
+    <t>1Rv1Qt1YcCGA4StmAj7SMbnIu_Twmdzpq</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Rv1Qt1YcCGA4StmAj7SMbnIu_Twmdzpq/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.MONALI SONI, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.PAYAL BHARDVA, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.HETA DOSHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR.PARTH PRAJAPATI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXERCISE THERAPY 2</t>
+  </si>
+  <si>
+    <t>1tRu8QJeYFsCjglalcbcD1UIuRU4EbLAt</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tRu8QJeYFsCjglalcbcD1UIuRU4EbLAt/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vikash Verma, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Vinay Yadav, </t>
   </si>
   <si>
     <t xml:space="preserve">Mr. Ashish Shah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vikash Verma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ishan Desai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power System - I </t>
-  </si>
-  <si>
-    <t>2526ECD0386</t>
-  </si>
-  <si>
-    <t>1wOuYeHtarx_tKiscCvISOnpheAA3LoXB</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wOuYeHtarx_tKiscCvISOnpheAA3LoXB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 27 2026 4:49 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mrs. Priyanka Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Priyank Makwana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Krishna Gohil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathematics - I</t>
-  </si>
-  <si>
-    <t>2526ECD405</t>
-  </si>
-  <si>
-    <t>1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 28 2026 5:51 AM</t>
-  </si>
-  <si>
-    <t>Physiotheraphy</t>
-  </si>
-  <si>
-    <t>Dr.Pooja</t>
-  </si>
-  <si>
-    <t>Dr.Vrunda</t>
-  </si>
-  <si>
-    <t>Dr.Siddharth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biomechanics and Kinesiology-I</t>
-  </si>
-  <si>
-    <t>2526ECD426</t>
-  </si>
-  <si>
-    <t>1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hk8ncDn6Tx-r6YVjbkYR7979omgRUSQy/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Pooja-Dr.Vrunda-Dr.Siddharth-Biomechanics and Kinesiology-I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:49 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Bhavik Thacker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Sonal Poojara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Vaishali Nathwani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied physics</t>
-  </si>
-  <si>
-    <t>1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1-eUfuFn2U8B6TGyG3J_oWOckIEK6CduO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Bhavik Thacker-Ms. Sonal Poojara-Ms. Vaishali Nathwani-Applied physics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 2:16 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Ravi Joshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Amarjeet Kaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Mital Kanani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachana Sharir (Human Anatomy) Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0460</t>
-  </si>
-  <si>
-    <t>1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gFXlB1tEIudrMbPxVQDFEG3rMXP-se82/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Ravi Joshi-Dr.Amarjeet Kaur-Dr.Mital Kanani-Rachana Sharir (Human Anatomy) Paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:09 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nikita P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Kruti P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Smita Rai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dravyaguna Vigyan paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0461</t>
-  </si>
-  <si>
-    <t>1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DEDWDlXu18IuPApo8jjYpqKeNz6eNpff/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nikita P-Dr. Kruti P-Dr.Smita Rai-Dravyaguna Vigyan paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Palak C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Jignesha P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Milind C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rasashastra evam Bhaishajyakalpana paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0462</t>
-  </si>
-  <si>
-    <t>1fZiljGMmRqmPperHUIzG1NAFD138oohm</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1fZiljGMmRqmPperHUIzG1NAFD138oohm/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Palak C-Dr. Jignesha P-Dr. Milind C-Rasashastra evam Bhaishajyakalpana paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Reshma Shaji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Vivek M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Archana Panchaksharimath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swasthavritta evam Yoga Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0463</t>
-  </si>
-  <si>
-    <t>1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1xMVFQp3Ot2sIpG7QO4G0Mf88iql6aSfH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Reshma Shaji-Dr. Vivek M-Dr. Archana Panchaksharimath-Swasthavritta evam Yoga Paper 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Sathish Mittapalli </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Rahul Barot </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Janavi Raut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmaceutical Organic Chemistry</t>
-  </si>
-  <si>
-    <t>2526ECD0464</t>
-  </si>
-  <si>
-    <t>15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/15uPXqjR6KUIUTm3I2O3ZPoZeynDnSknB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Sathish Mittapalli - Mr. Rahul Barot -Ms. Janavi Raut-Pharmaceutical Organic Chemistry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 4:54 AM</t>
-  </si>
-  <si>
-    <t>JNHMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Uma Sahoo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Upma Raval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Vinit Tapas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physiology and Biochemistry</t>
-  </si>
-  <si>
-    <t>2526ECD0476</t>
-  </si>
-  <si>
-    <t>1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1M6izG8C5-QEOoRkc_hnG5AaR83wD0P9U/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Uma Sahoo-Dr Upma Raval-Dr Vinit Tapas-Physiology and Biochemistry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:18 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Naresh Bhusara </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Nayana Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Neelima Sharan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homoeopathic Pharmacy</t>
-  </si>
-  <si>
-    <t>2526ECD0477</t>
-  </si>
-  <si>
-    <t>11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/11j89Qw09EJEeOZyvALs9Xv1ptkmkpUSA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Naresh Bhusara -Dr Nayana Patel-Dr Neelima Sharan-Homoeopathic Pharmacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Vani Oza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Archana Tegwal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Preeti Mulani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homoeopathic Materia Medica</t>
-  </si>
-  <si>
-    <t>2526ECD0478</t>
-  </si>
-  <si>
-    <t>1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wKQb5Q7TE4GdkRIHVtkcAAhShCemuchs/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Vani Oza-Dr Archana Tegwal-Dr Preeti Mulani-Homoeopathic Materia Medica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Pragya Srivastva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Preeti Pathak </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Amar Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pathology and Microbiology</t>
-  </si>
-  <si>
-    <t>2526ECD0479</t>
-  </si>
-  <si>
-    <t>1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1v9Hg3aWaaZOvBf9v56V2e6SmfQCqlmpy/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Pragya Srivastva-Dr Preeti Pathak -Dr Amar Thakkar-Pathology and Microbiology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Smit Dad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Astha Rawal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Dhwani Thakkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice of Medicine</t>
-  </si>
-  <si>
-    <t>2526ECD0480</t>
-  </si>
-  <si>
-    <t>1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Se1mSgc8xLPMTV2wTqoThUvoi3DTWzzc/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Smit Dad-Dr Astha Rawal-Dr Dhwani Thakkar-Practice of Medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Aparna Bagul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Rajalekshmi R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Hari Sankar M S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swasthavritta evam Yoga Paper 1</t>
-  </si>
-  <si>
-    <t>2526ECD0481</t>
-  </si>
-  <si>
-    <t>1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1eIaPd1DbD5cDdCcKcmHbHvfr3bQmpAgI/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Aparna Bagul-Dr Rajalekshmi R-Dr Hari Sankar M S-Swasthavritta evam Yoga Paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 12:58 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Jaiminikumari Mahendrasinh Rathod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nishant Nareshbhai Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
-  </si>
-  <si>
-    <t>2526ECD0482</t>
-  </si>
-  <si>
-    <t>1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FrexCoeeLyrHTJh5HaDFPQltH5fdrX1p/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. DIPEEKA SURESH SURWASE-Dr. Jaiminikumari Mahendrasinh Rathod-Dr. Nishant Nareshbhai Patel-Kayachikitsa including Manasa Roga, Rasayana and Vajikarana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. PARIKSHIT RAMAKANT SHIRODE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. PRAJAPATI HARSHADKUMAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shalya Tantra Paper 2</t>
-  </si>
-  <si>
-    <t>2526ECD0491</t>
-  </si>
-  <si>
-    <t>1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1tULN0D6xdeZ0BTirMYeZurSb-35ZpMWd/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Kushal Chhotu Chaudhari-Dr. PARIKSHIT RAMAKANT SHIRODE -Dr. PRAJAPATI HARSHADKUMAR-Shalya Tantra Paper 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 5:07 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Jalpa Zalawadia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Sumit Das Lala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krishnamraju Putta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop and Manufacturing Practice</t>
-  </si>
-  <si>
-    <t>1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1K3Kqc2E1p0OBawwtIPMCXZHZx6vYEPua/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Jalpa Zalawadia-Dr. Sumit Das Lala-Krishnamraju Putta-Workshop and Manufacturing Practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:24 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vishal Jain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Nishant Rajput</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Omprakash Bharti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elements of Thermal and Fluid Sciences</t>
-  </si>
-  <si>
-    <t>1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zWqsZU92kuhLz083PIBjXJWl6w9UGDTM/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vishal Jain-Mr. Nishant Rajput-Dr. Omprakash Bharti-Elements of Thermal and Fluid Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 30 2026 6:26 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Manan Shah </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Akash Shukla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Hitesh Dave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Graphics and Design</t>
-  </si>
-  <si>
-    <t>1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1RdybXkklFW3HbqMA8AKFGGnMRZsalI0x/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Manan Shah -Mr. Akash Shukla-Mr. Hitesh Dave-Engineering Graphics and Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Kalmesh Parmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms. Swati Prajapati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elements of Mechanical Engineering</t>
-  </si>
-  <si>
-    <t>1Qpkh7V28vWumf7dxUwEu-eF9NLCVIJ8E</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Qpkh7V28vWumf7dxUwEu-eF9NLCVIJ8E/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Kalmesh Parmar-Mr. Vishal Jain-Ms. Swati Prajapati-Elements of Mechanical Engineering</t>
-  </si>
-  <si>
-    <t>PIPTR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Rushikesh Joshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Pooja Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Tanvi Patel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biomedical Physics</t>
-  </si>
-  <si>
-    <t>1puGdke6h1uPM_P2PZDipi-LWpucG4B4D</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1puGdke6h1uPM_P2PZDipi-LWpucG4B4D/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Rushikesh Joshi-Dr.Pooja Soni-Dr.Tanvi Patel-Biomedical Physics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 4 2026 4:11 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Sandip Parekh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Gopi Panchmatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Darpan Vanavi</t>
-  </si>
-  <si>
-    <t>Electrotherapy-II</t>
-  </si>
-  <si>
-    <t>1DxtGtfqKb0TJxGXIFjJlPRpEAviIaSz3</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DxtGtfqKb0TJxGXIFjJlPRpEAviIaSz3/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Sandip Parekh-Dr.Gopi Panchmatia-Dr.Darpan Vanavi-Electrotherapy-II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Monali Soni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Payal Bhardva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Parth Prajapati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise Therapy II</t>
-  </si>
-  <si>
-    <t>1ra54wyU7EBWabC2HDdED01oTtce-nVXL</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ra54wyU7EBWabC2HDdED01oTtce-nVXL/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Monali Soni-Dr.Payal Bhardva-Dr.Parth Prajapati-Exercise Therapy II</t>
-  </si>
-  <si>
-    <t>PIAYR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Dhriti Khandelwal</t>
-  </si>
-  <si>
-    <t>1gVk0r3EMmebxgdRh0E25hgA5k5r07V_z</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gVk0r3EMmebxgdRh0E25hgA5k5r07V_z/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Sambu Surendran-Dr. Sahil Patel-Dr. Dhriti Khandelwal-Shalya Tantra Paper 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by kinnari.mishra12751@paruluniversity.ac.in; Timestamp: May 6 2026 1:26 AM</t>
-  </si>
-  <si>
-    <t>autocratn</t>
-  </si>
-  <si>
-    <t>autocratp</t>
-  </si>
-  <si>
-    <t>dataSheetName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Form Responses 1"</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>"5.1"</t>
-  </si>
-  <si>
-    <t>dataSheetId</t>
-  </si>
-  <si>
-    <t>"6.50628832E8"</t>
-  </si>
-  <si>
-    <t>updateTime</t>
-  </si>
-  <si>
-    <t>"1.777270430007E12"</t>
-  </si>
-  <si>
-    <t>vp</t>
-  </si>
-  <si>
-    <t>ssId</t>
-  </si>
-  <si>
-    <t>"1XAffx2osIAaU40eNPfh9ozyEJ0Jv8Cac9e2lgVmJ_5Y"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Sheet ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Data Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share As</t>
-  </si>
-  <si>
-    <t>Folders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Folder Reference</t>
-  </si>
-  <si>
-    <t>Conditionals</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Append Breaks</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run On Time Trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Trigger Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run On Form Trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Send Email And Share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email BCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Reply To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email No Reply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prevent Resharing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Trigger Timestamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form Trigger Timestamp</t>
-  </si>
-  <si>
-    <t>_1777010583975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) E content certificate</t>
-  </si>
-  <si>
-    <t>1hyfm2hOwN-su9PZzJQCcmUAJfsTj_Tuv6JRyBkz19SU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;&lt;Name to be Printed on Certificate&gt;&gt;-&lt;&lt;Subject&gt;&gt;</t>
-  </si>
-  <si>
-    <t>PDF</t>
-  </si>
-  <si>
-    <t>["1APY_TOVAsRdET2TZ1CeJ3l6lXbibUj-U"]</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>MULTIPLE_OUTPUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Sr No"},"tag":"Sr No"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Date"},"tag":"Date"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Subject"},"tag":"Subject"},{"type":"STANDARD","details":{"isUnmapped":false,"headerMap":"Name to be Printed on Certificate"},"tag":"Name"}]</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name to be Printed on Certificate 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name to be Printed on Certificate 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Doc ID - 2 Econtent Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Doc URL - 2 Econtent Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link to merged Doc - 2 Econtent Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document Merge Status - 2 Econtent Certificate</t>
-  </si>
-  <si>
-    <t>PHYSIOTHERAPHY</t>
-  </si>
-  <si>
-    <t>Dr.Rinkal</t>
-  </si>
-  <si>
-    <t>Dr.Asha</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr.Prachi</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr.Dhaval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundamentals of ET-1</t>
-  </si>
-  <si>
-    <t>1gyUMYvdoAWp93yhR5yYZKB7kN6VS2SxE</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gyUMYvdoAWp93yhR5yYZKB7kN6VS2SxE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:51 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.RUSHIKESH JOSHI, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.TANVI PATEL, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.POOJA SONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.NIDHI MANGROLIA</t>
-  </si>
-  <si>
-    <t>1RomXGXq4D02P0f3OIuBCfx5HuIEalA7w</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1RomXGXq4D02P0f3OIuBCfx5HuIEalA7w/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Dr.Meghavi,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Heli, </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr.Sonal</t>
-  </si>
-  <si>
-    <t>Dr.Mansi</t>
-  </si>
-  <si>
-    <t>Electrotherapy-I</t>
-  </si>
-  <si>
-    <t>1kk-n50-lgKa2Efjs186_3l_ydH-m83HN</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1kk-n50-lgKa2Efjs186_3l_ydH-m83HN/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document successfully created; Document successfully merged; PDF created; Manually run by nirmita.patel27183@paruluniversity.ac.in; Timestamp: Apr 29 2026 1:52 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Priyanka,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Simrah, </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dr. Madhavi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Didhiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapeutics of Exercise Therapy-I</t>
-  </si>
-  <si>
-    <t>1H2hyQG6O2w0pM_3K6xpCqWfDUAdyVq2u</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1H2hyQG6O2w0pM_3K6xpCqWfDUAdyVq2u/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr.Jigisha, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Advita, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Joyal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Nilesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapeutics of Exercise Therapy-II</t>
-  </si>
-  <si>
-    <t>1nOYQgrmFO5MQqh5kDUnf05OxlJc20Y8P</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nOYQgrmFO5MQqh5kDUnf05OxlJc20Y8P/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Dhwani, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Dwija, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Chaitali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Dharmang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biomechanics and Kinesiology-II</t>
-  </si>
-  <si>
-    <t>1PbxtA94A1_2lqEzrLOgMEK0CWlhdnE6C</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1PbxtA94A1_2lqEzrLOgMEK0CWlhdnE6C/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.SANDIP PAREKH, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.PRAKRUTI PARIKH, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.GOPI PANCHMATIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.DARPAN VANAVI</t>
-  </si>
-  <si>
-    <t>1Rv1Qt1YcCGA4StmAj7SMbnIu_Twmdzpq</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Rv1Qt1YcCGA4StmAj7SMbnIu_Twmdzpq/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.MONALI SONI, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.PAYAL BHARDVA, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.HETA DOSHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DR.PARTH PRAJAPATI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXERCISE THERAPY 2</t>
-  </si>
-  <si>
-    <t>1tRu8QJeYFsCjglalcbcD1UIuRU4EbLAt</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1tRu8QJeYFsCjglalcbcD1UIuRU4EbLAt/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vikash Verma, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Vinay Yadav, </t>
   </si>
   <si>
     <t xml:space="preserve">Ishan Desai</t>
@@ -10871,7 +10841,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="452">
+  <cellXfs count="450">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -11991,12 +11961,6 @@
     </xf>
     <xf fontId="51" fillId="8" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf fontId="16" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="6" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center"/>
@@ -26279,31 +26243,31 @@
       <c r="A83" s="369" t="s">
         <v>1619</v>
       </c>
-      <c r="B83" s="196" t="s">
+      <c r="B83" s="203" t="s">
         <v>2336</v>
       </c>
-      <c r="C83" s="196" t="s">
+      <c r="C83" s="203" t="s">
         <v>2337</v>
       </c>
-      <c r="D83" s="230" t="s">
+      <c r="D83" s="212" t="s">
         <v>2338</v>
       </c>
       <c r="E83" s="194" t="s">
         <v>2339</v>
       </c>
-      <c r="F83" s="195">
+      <c r="F83" s="202">
         <v>46139</v>
       </c>
-      <c r="G83" s="196" t="s">
+      <c r="G83" s="203" t="s">
         <v>2340</v>
       </c>
-      <c r="H83" s="197" t="s">
+      <c r="H83" s="204" t="s">
         <v>2341</v>
       </c>
-      <c r="I83" s="197" t="s">
+      <c r="I83" s="204" t="s">
         <v>2338</v>
       </c>
-      <c r="J83" s="198" t="s">
+      <c r="J83" s="205" t="s">
         <v>2342</v>
       </c>
       <c r="K83" s="190"/>
@@ -26313,243 +26277,243 @@
       <c r="A84" s="369" t="s">
         <v>1619</v>
       </c>
-      <c r="B84" s="203" t="s">
+      <c r="B84" s="196" t="s">
         <v>2343</v>
       </c>
-      <c r="C84" s="203" t="s">
+      <c r="C84" s="196" t="s">
         <v>2344</v>
       </c>
-      <c r="D84" s="212" t="s">
+      <c r="D84" s="230" t="s">
         <v>2345</v>
       </c>
       <c r="E84" s="194" t="s">
         <v>2346</v>
       </c>
-      <c r="F84" s="202">
+      <c r="F84" s="195">
         <v>46139</v>
       </c>
-      <c r="G84" s="203" t="s">
+      <c r="G84" s="196" t="s">
         <v>2347</v>
       </c>
-      <c r="H84" s="204" t="s">
+      <c r="H84" s="197" t="s">
         <v>2348</v>
       </c>
-      <c r="I84" s="204" t="s">
+      <c r="I84" s="197" t="s">
         <v>2345</v>
       </c>
-      <c r="J84" s="205" t="s">
+      <c r="J84" s="198" t="s">
         <v>2342</v>
       </c>
       <c r="K84" s="190"/>
       <c r="L84" s="190"/>
     </row>
     <row r="85" ht="25.5" customHeight="1">
-      <c r="A85" s="369" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B85" s="196" t="s">
+      <c r="A85" s="208" t="s">
         <v>2349</v>
       </c>
-      <c r="C85" s="196" t="s">
+      <c r="B85" s="203" t="s">
         <v>2350</v>
       </c>
-      <c r="D85" s="230" t="s">
+      <c r="C85" s="203" t="s">
         <v>2351</v>
       </c>
+      <c r="D85" s="212" t="s">
+        <v>2352</v>
+      </c>
       <c r="E85" s="194" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F85" s="202">
+        <v>46139</v>
+      </c>
+      <c r="G85" s="203" t="s">
+        <v>2354</v>
+      </c>
+      <c r="H85" s="204" t="s">
+        <v>2355</v>
+      </c>
+      <c r="I85" s="204" t="s">
         <v>2352</v>
       </c>
-      <c r="F85" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G85" s="196" t="s">
-        <v>2353</v>
-      </c>
-      <c r="H85" s="197" t="s">
-        <v>2354</v>
-      </c>
-      <c r="I85" s="197" t="s">
-        <v>2351</v>
-      </c>
-      <c r="J85" s="198" t="s">
-        <v>2342</v>
+      <c r="J85" s="205" t="s">
+        <v>2356</v>
       </c>
       <c r="K85" s="190"/>
       <c r="L85" s="190"/>
     </row>
     <row r="86" ht="25.5" customHeight="1">
-      <c r="A86" s="208" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B86" s="203" t="s">
+      <c r="A86" s="370" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B86" s="196" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C86" s="196" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D86" s="230" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E86" s="194" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F86" s="195">
+        <v>46139</v>
+      </c>
+      <c r="G86" s="196" t="s">
+        <v>2361</v>
+      </c>
+      <c r="H86" s="197" t="s">
+        <v>2362</v>
+      </c>
+      <c r="I86" s="197" t="s">
+        <v>2359</v>
+      </c>
+      <c r="J86" s="198" t="s">
         <v>2356</v>
-      </c>
-      <c r="C86" s="203" t="s">
-        <v>2357</v>
-      </c>
-      <c r="D86" s="212" t="s">
-        <v>2358</v>
-      </c>
-      <c r="E86" s="194" t="s">
-        <v>2359</v>
-      </c>
-      <c r="F86" s="202">
-        <v>46139</v>
-      </c>
-      <c r="G86" s="203" t="s">
-        <v>2360</v>
-      </c>
-      <c r="H86" s="204" t="s">
-        <v>2361</v>
-      </c>
-      <c r="I86" s="204" t="s">
-        <v>2358</v>
-      </c>
-      <c r="J86" s="205" t="s">
-        <v>2362</v>
       </c>
       <c r="K86" s="190"/>
       <c r="L86" s="190"/>
     </row>
     <row r="87" ht="25.5" customHeight="1">
       <c r="A87" s="370" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B87" s="196" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B87" s="203" t="s">
         <v>2363</v>
       </c>
-      <c r="C87" s="196" t="s">
+      <c r="C87" s="203" t="s">
         <v>2364</v>
       </c>
-      <c r="D87" s="230" t="s">
+      <c r="D87" s="212" t="s">
         <v>2365</v>
       </c>
       <c r="E87" s="194" t="s">
         <v>2366</v>
       </c>
-      <c r="F87" s="195">
+      <c r="F87" s="202">
         <v>46139</v>
       </c>
-      <c r="G87" s="196" t="s">
+      <c r="G87" s="203" t="s">
         <v>2367</v>
       </c>
-      <c r="H87" s="197" t="s">
+      <c r="H87" s="204" t="s">
         <v>2368</v>
       </c>
-      <c r="I87" s="197" t="s">
+      <c r="I87" s="204" t="s">
         <v>2365</v>
       </c>
-      <c r="J87" s="198" t="s">
-        <v>2362</v>
+      <c r="J87" s="205" t="s">
+        <v>2356</v>
       </c>
       <c r="K87" s="190"/>
       <c r="L87" s="190"/>
     </row>
     <row r="88" ht="25.5" customHeight="1">
       <c r="A88" s="370" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B88" s="203" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B88" s="196" t="s">
         <v>2369</v>
       </c>
-      <c r="C88" s="203" t="s">
+      <c r="C88" s="196" t="s">
         <v>2370</v>
       </c>
-      <c r="D88" s="212" t="s">
+      <c r="D88" s="230" t="s">
         <v>2371</v>
       </c>
       <c r="E88" s="194" t="s">
         <v>2372</v>
       </c>
-      <c r="F88" s="202">
+      <c r="F88" s="195">
         <v>46139</v>
       </c>
-      <c r="G88" s="203" t="s">
+      <c r="G88" s="196" t="s">
         <v>2373</v>
       </c>
-      <c r="H88" s="204" t="s">
+      <c r="H88" s="197" t="s">
         <v>2374</v>
       </c>
-      <c r="I88" s="204" t="s">
+      <c r="I88" s="197" t="s">
         <v>2371</v>
       </c>
-      <c r="J88" s="205" t="s">
-        <v>2362</v>
+      <c r="J88" s="198" t="s">
+        <v>2356</v>
       </c>
       <c r="K88" s="190"/>
       <c r="L88" s="190"/>
     </row>
     <row r="89" ht="25.5" customHeight="1">
       <c r="A89" s="370" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B89" s="196" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B89" s="203" t="s">
         <v>2375</v>
       </c>
-      <c r="C89" s="196" t="s">
+      <c r="C89" s="203" t="s">
         <v>2376</v>
       </c>
-      <c r="D89" s="230" t="s">
+      <c r="D89" s="212" t="s">
         <v>2377</v>
       </c>
       <c r="E89" s="194" t="s">
         <v>2378</v>
       </c>
-      <c r="F89" s="195">
+      <c r="F89" s="202">
         <v>46139</v>
       </c>
-      <c r="G89" s="196" t="s">
+      <c r="G89" s="203" t="s">
         <v>2379</v>
       </c>
-      <c r="H89" s="197" t="s">
+      <c r="H89" s="204" t="s">
         <v>2380</v>
       </c>
-      <c r="I89" s="197" t="s">
+      <c r="I89" s="204" t="s">
         <v>2377</v>
       </c>
-      <c r="J89" s="198" t="s">
-        <v>2362</v>
+      <c r="J89" s="205" t="s">
+        <v>2356</v>
       </c>
       <c r="K89" s="190"/>
       <c r="L89" s="190"/>
     </row>
     <row r="90" ht="25.5" customHeight="1">
-      <c r="A90" s="370" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B90" s="203" t="s">
+      <c r="A90" s="368" t="s">
         <v>2381</v>
       </c>
-      <c r="C90" s="203" t="s">
+      <c r="B90" s="196" t="s">
         <v>2382</v>
       </c>
-      <c r="D90" s="212" t="s">
+      <c r="C90" s="196" t="s">
         <v>2383</v>
+      </c>
+      <c r="D90" s="230" t="s">
+        <v>2382</v>
       </c>
       <c r="E90" s="194" t="s">
         <v>2384</v>
       </c>
-      <c r="F90" s="202">
+      <c r="F90" s="195">
         <v>46139</v>
       </c>
-      <c r="G90" s="203" t="s">
+      <c r="G90" s="196" t="s">
         <v>2385</v>
       </c>
-      <c r="H90" s="204" t="s">
+      <c r="H90" s="197" t="s">
         <v>2386</v>
       </c>
-      <c r="I90" s="204" t="s">
-        <v>2383</v>
-      </c>
-      <c r="J90" s="205" t="s">
-        <v>2362</v>
+      <c r="I90" s="197" t="s">
+        <v>2382</v>
+      </c>
+      <c r="J90" s="198" t="s">
+        <v>2387</v>
       </c>
       <c r="K90" s="190"/>
       <c r="L90" s="190"/>
     </row>
     <row r="91" ht="25.5" customHeight="1">
-      <c r="A91" s="368" t="s">
-        <v>2387</v>
+      <c r="A91" s="369" t="s">
+        <v>2381</v>
       </c>
       <c r="B91" s="196" t="s">
         <v>2388</v>
@@ -26558,66 +26522,66 @@
         <v>2389</v>
       </c>
       <c r="D91" s="230" t="s">
-        <v>2388</v>
+        <v>1628</v>
       </c>
       <c r="E91" s="194" t="s">
-        <v>2390</v>
+        <v>1662</v>
       </c>
       <c r="F91" s="195">
         <v>46139</v>
       </c>
       <c r="G91" s="196" t="s">
+        <v>2390</v>
+      </c>
+      <c r="H91" s="197" t="s">
         <v>2391</v>
       </c>
-      <c r="H91" s="197" t="s">
+      <c r="I91" s="197" t="s">
+        <v>1628</v>
+      </c>
+      <c r="J91" s="198" t="s">
         <v>2392</v>
-      </c>
-      <c r="I91" s="197" t="s">
-        <v>2388</v>
-      </c>
-      <c r="J91" s="198" t="s">
-        <v>2393</v>
       </c>
       <c r="K91" s="190"/>
       <c r="L91" s="190"/>
     </row>
     <row r="92" ht="25.5" customHeight="1">
       <c r="A92" s="369" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B92" s="196" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B92" s="203" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C92" s="203" t="s">
         <v>2394</v>
       </c>
-      <c r="C92" s="196" t="s">
+      <c r="D92" s="212" t="s">
         <v>2395</v>
       </c>
-      <c r="D92" s="230" t="s">
-        <v>1628</v>
-      </c>
       <c r="E92" s="194" t="s">
-        <v>1662</v>
-      </c>
-      <c r="F92" s="195">
+        <v>2396</v>
+      </c>
+      <c r="F92" s="202">
         <v>46139</v>
       </c>
-      <c r="G92" s="196" t="s">
-        <v>2396</v>
-      </c>
-      <c r="H92" s="197" t="s">
+      <c r="G92" s="203" t="s">
         <v>2397</v>
       </c>
-      <c r="I92" s="197" t="s">
-        <v>1628</v>
-      </c>
-      <c r="J92" s="198" t="s">
+      <c r="H92" s="204" t="s">
         <v>2398</v>
+      </c>
+      <c r="I92" s="204" t="s">
+        <v>2395</v>
+      </c>
+      <c r="J92" s="205" t="s">
+        <v>2392</v>
       </c>
       <c r="K92" s="190"/>
       <c r="L92" s="190"/>
     </row>
     <row r="93" ht="25.5" customHeight="1">
       <c r="A93" s="369" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
       <c r="B93" s="203" t="s">
         <v>2399</v>
@@ -26644,248 +26608,214 @@
         <v>2401</v>
       </c>
       <c r="J93" s="205" t="s">
-        <v>2398</v>
+        <v>2392</v>
       </c>
       <c r="K93" s="190"/>
       <c r="L93" s="190"/>
     </row>
     <row r="94" ht="25.5" customHeight="1">
       <c r="A94" s="369" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B94" s="203" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B94" s="196" t="s">
         <v>2405</v>
       </c>
-      <c r="C94" s="203" t="s">
+      <c r="C94" s="196" t="s">
         <v>2406</v>
       </c>
-      <c r="D94" s="212" t="s">
+      <c r="D94" s="230" t="s">
         <v>2407</v>
       </c>
       <c r="E94" s="194" t="s">
         <v>2408</v>
       </c>
-      <c r="F94" s="202">
+      <c r="F94" s="195">
         <v>46139</v>
       </c>
-      <c r="G94" s="203" t="s">
+      <c r="G94" s="196" t="s">
         <v>2409</v>
       </c>
-      <c r="H94" s="204" t="s">
+      <c r="H94" s="197" t="s">
         <v>2410</v>
       </c>
-      <c r="I94" s="204" t="s">
+      <c r="I94" s="197" t="s">
         <v>2407</v>
       </c>
-      <c r="J94" s="205" t="s">
-        <v>2398</v>
+      <c r="J94" s="198" t="s">
+        <v>2411</v>
       </c>
       <c r="K94" s="190"/>
       <c r="L94" s="190"/>
     </row>
     <row r="95" ht="25.5" customHeight="1">
       <c r="A95" s="369" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B95" s="196" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B95" s="289" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C95" s="289" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D95" s="229" t="s">
+        <v>2414</v>
+      </c>
+      <c r="E95" s="194" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F95" s="371">
+        <v>46139</v>
+      </c>
+      <c r="G95" s="289" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H95" s="290" t="s">
+        <v>2417</v>
+      </c>
+      <c r="I95" s="290" t="s">
+        <v>2414</v>
+      </c>
+      <c r="J95" s="291" t="s">
         <v>2411</v>
-      </c>
-      <c r="C95" s="196" t="s">
-        <v>2412</v>
-      </c>
-      <c r="D95" s="230" t="s">
-        <v>2413</v>
-      </c>
-      <c r="E95" s="194" t="s">
-        <v>2414</v>
-      </c>
-      <c r="F95" s="195">
-        <v>46139</v>
-      </c>
-      <c r="G95" s="196" t="s">
-        <v>2415</v>
-      </c>
-      <c r="H95" s="197" t="s">
-        <v>2416</v>
-      </c>
-      <c r="I95" s="197" t="s">
-        <v>2413</v>
-      </c>
-      <c r="J95" s="198" t="s">
-        <v>2417</v>
       </c>
       <c r="K95" s="190"/>
       <c r="L95" s="190"/>
     </row>
     <row r="96" ht="25.5" customHeight="1">
-      <c r="A96" s="369" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B96" s="289" t="s">
+      <c r="A96" s="272" t="s">
         <v>2418</v>
       </c>
-      <c r="C96" s="289" t="s">
+      <c r="B96" s="276" t="s">
         <v>2419</v>
       </c>
-      <c r="D96" s="229" t="s">
+      <c r="C96" s="276" t="s">
         <v>2420</v>
       </c>
-      <c r="E96" s="194" t="s">
+      <c r="D96" s="372" t="s">
         <v>2421</v>
       </c>
-      <c r="F96" s="371">
-        <v>46139</v>
-      </c>
-      <c r="G96" s="289" t="s">
+      <c r="E96" s="185" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F96" s="275">
+        <v>46146</v>
+      </c>
+      <c r="G96" s="276" t="s">
         <v>2422</v>
       </c>
-      <c r="H96" s="290" t="s">
+      <c r="H96" s="277" t="s">
         <v>2423</v>
       </c>
-      <c r="I96" s="290" t="s">
-        <v>2420</v>
-      </c>
-      <c r="J96" s="291" t="s">
-        <v>2417</v>
+      <c r="I96" s="277" t="s">
+        <v>2421</v>
+      </c>
+      <c r="J96" s="278" t="s">
+        <v>2424</v>
       </c>
       <c r="K96" s="190"/>
       <c r="L96" s="190"/>
     </row>
     <row r="97" ht="25.5" customHeight="1">
-      <c r="A97" s="272" t="s">
+      <c r="A97" s="373" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B97" s="203" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C97" s="203" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D97" s="212" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E97" s="194" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F97" s="281">
+        <v>46146</v>
+      </c>
+      <c r="G97" s="203" t="s">
+        <v>2428</v>
+      </c>
+      <c r="H97" s="204" t="s">
+        <v>2429</v>
+      </c>
+      <c r="I97" s="204" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J97" s="205" t="s">
         <v>2424</v>
-      </c>
-      <c r="B97" s="276" t="s">
-        <v>2425</v>
-      </c>
-      <c r="C97" s="276" t="s">
-        <v>2426</v>
-      </c>
-      <c r="D97" s="372" t="s">
-        <v>2427</v>
-      </c>
-      <c r="E97" s="185" t="s">
-        <v>1668</v>
-      </c>
-      <c r="F97" s="275">
-        <v>46146</v>
-      </c>
-      <c r="G97" s="276" t="s">
-        <v>2428</v>
-      </c>
-      <c r="H97" s="277" t="s">
-        <v>2429</v>
-      </c>
-      <c r="I97" s="277" t="s">
-        <v>2427</v>
-      </c>
-      <c r="J97" s="278" t="s">
-        <v>2430</v>
       </c>
       <c r="K97" s="190"/>
       <c r="L97" s="190"/>
     </row>
     <row r="98" ht="25.5" customHeight="1">
       <c r="A98" s="373" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B98" s="196" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C98" s="196" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D98" s="230" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E98" s="194" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F98" s="285">
+        <v>46146</v>
+      </c>
+      <c r="G98" s="196" t="s">
+        <v>2433</v>
+      </c>
+      <c r="H98" s="197" t="s">
+        <v>2434</v>
+      </c>
+      <c r="I98" s="197" t="s">
+        <v>2432</v>
+      </c>
+      <c r="J98" s="198" t="s">
         <v>2424</v>
-      </c>
-      <c r="B98" s="203" t="s">
-        <v>2431</v>
-      </c>
-      <c r="C98" s="203" t="s">
-        <v>2432</v>
-      </c>
-      <c r="D98" s="212" t="s">
-        <v>2433</v>
-      </c>
-      <c r="E98" s="194" t="s">
-        <v>1674</v>
-      </c>
-      <c r="F98" s="281">
-        <v>46146</v>
-      </c>
-      <c r="G98" s="203" t="s">
-        <v>2434</v>
-      </c>
-      <c r="H98" s="204" t="s">
-        <v>2435</v>
-      </c>
-      <c r="I98" s="204" t="s">
-        <v>2433</v>
-      </c>
-      <c r="J98" s="205" t="s">
-        <v>2430</v>
       </c>
       <c r="K98" s="190"/>
       <c r="L98" s="190"/>
     </row>
     <row r="99" ht="25.5" customHeight="1">
       <c r="A99" s="373" t="s">
-        <v>2424</v>
-      </c>
-      <c r="B99" s="196" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B99" s="289" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C99" s="289" t="s">
+        <v>2435</v>
+      </c>
+      <c r="D99" s="229" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E99" s="194" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F99" s="288">
+        <v>46146</v>
+      </c>
+      <c r="G99" s="289" t="s">
         <v>2436</v>
       </c>
-      <c r="C99" s="196" t="s">
+      <c r="H99" s="290" t="s">
         <v>2437</v>
       </c>
-      <c r="D99" s="230" t="s">
+      <c r="I99" s="290" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J99" s="291" t="s">
         <v>2438</v>
-      </c>
-      <c r="E99" s="194" t="s">
-        <v>1680</v>
-      </c>
-      <c r="F99" s="285">
-        <v>46146</v>
-      </c>
-      <c r="G99" s="196" t="s">
-        <v>2439</v>
-      </c>
-      <c r="H99" s="197" t="s">
-        <v>2440</v>
-      </c>
-      <c r="I99" s="197" t="s">
-        <v>2438</v>
-      </c>
-      <c r="J99" s="198" t="s">
-        <v>2430</v>
       </c>
       <c r="K99" s="190"/>
       <c r="L99" s="190"/>
-    </row>
-    <row r="100" ht="25.5" customHeight="1">
-      <c r="A100" s="373" t="s">
-        <v>2424</v>
-      </c>
-      <c r="B100" s="289" t="s">
-        <v>2431</v>
-      </c>
-      <c r="C100" s="289" t="s">
-        <v>2441</v>
-      </c>
-      <c r="D100" s="229" t="s">
-        <v>2433</v>
-      </c>
-      <c r="E100" s="194" t="s">
-        <v>1685</v>
-      </c>
-      <c r="F100" s="288">
-        <v>46146</v>
-      </c>
-      <c r="G100" s="289" t="s">
-        <v>2442</v>
-      </c>
-      <c r="H100" s="290" t="s">
-        <v>2443</v>
-      </c>
-      <c r="I100" s="290" t="s">
-        <v>2433</v>
-      </c>
-      <c r="J100" s="291" t="s">
-        <v>2444</v>
-      </c>
-      <c r="K100" s="190"/>
-      <c r="L100" s="190"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27006,8 +26936,6 @@
     <hyperlink r:id="rId97" ref="I98" tooltip=""/>
     <hyperlink r:id="rId98" ref="H99" tooltip=""/>
     <hyperlink r:id="rId98" ref="I99" tooltip=""/>
-    <hyperlink r:id="rId99" ref="H100" tooltip=""/>
-    <hyperlink r:id="rId99" ref="I100" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -27021,6 +26949,9 @@
   <sheetFormatPr defaultRowHeight="25.5" customHeight="1"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="16.140625"/>
+    <col bestFit="1" min="2" max="2" width="30.57421875"/>
+    <col bestFit="1" min="3" max="3" width="30.28125"/>
+    <col bestFit="1" min="4" max="4" width="29.8515625"/>
     <col bestFit="1" min="7" max="7" width="17.36328125"/>
   </cols>
   <sheetData>
@@ -27035,7 +26966,7 @@
         <v>1828</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2445</v>
+        <v>2439</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -27047,16 +26978,16 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2446</v>
+        <v>2440</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2447</v>
+        <v>2441</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2448</v>
+        <v>2442</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>2449</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1">
@@ -27073,26 +27004,26 @@
         <v>1939</v>
       </c>
       <c r="E2" s="375" t="s">
-        <v>2450</v>
+        <v>2444</v>
       </c>
       <c r="F2" s="376" t="s">
-        <v>2451</v>
+        <v>2445</v>
       </c>
       <c r="G2" s="377">
         <v>45986</v>
       </c>
       <c r="H2" s="374" t="s">
-        <v>2452</v>
+        <v>2446</v>
       </c>
       <c r="I2" s="378" t="s">
-        <v>2453</v>
+        <v>2447</v>
       </c>
       <c r="J2" s="379" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1a-uOa9x9yXzP0J7iuLZMYddyYrHmxRr_/view?usp=drivesdk","Mr. Abhishek Singh-Mr. Aniket Paul-Rafi -Specialization - Cyber Security and Forensics - I")</f>
         <v xml:space="preserve">Mr. Abhishek Singh-Mr. Aniket Paul-Rafi -Specialization - Cyber Security and Forensics - I</v>
       </c>
       <c r="K2" s="380" t="s">
-        <v>2454</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="3" ht="25.5" customHeight="1">
@@ -27100,35 +27031,35 @@
         <v>1847</v>
       </c>
       <c r="B3" s="374" t="s">
-        <v>2455</v>
+        <v>2449</v>
       </c>
       <c r="C3" s="374" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
       <c r="D3" s="374" t="s">
-        <v>2457</v>
+        <v>2451</v>
       </c>
       <c r="E3" s="375" t="s">
-        <v>2458</v>
+        <v>2452</v>
       </c>
       <c r="F3" s="376" t="s">
-        <v>2459</v>
+        <v>2453</v>
       </c>
       <c r="G3" s="381">
         <v>45986</v>
       </c>
       <c r="H3" s="374" t="s">
-        <v>2460</v>
+        <v>2454</v>
       </c>
       <c r="I3" s="378" t="s">
-        <v>2461</v>
+        <v>2455</v>
       </c>
       <c r="J3" s="379" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1rI8d6Poibl3WYDKH_BzLSCMMomf1ztqu/view?usp=drivesdk","Ms. Renuka Parmar-Mr. Gaurav Kumar-Ms. Priya Soni-Specialization - Full Stack Web Development - I")</f>
         <v xml:space="preserve">Ms. Renuka Parmar-Mr. Gaurav Kumar-Ms. Priya Soni-Specialization - Full Stack Web Development - I</v>
       </c>
       <c r="K3" s="380" t="s">
-        <v>2454</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
@@ -27136,35 +27067,35 @@
         <v>153</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>2462</v>
+        <v>2456</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>2463</v>
+        <v>2457</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>2464</v>
+        <v>2458</v>
       </c>
       <c r="E4" s="313" t="s">
-        <v>2465</v>
+        <v>2459</v>
       </c>
       <c r="F4" s="314" t="s">
-        <v>2466</v>
+        <v>2460</v>
       </c>
       <c r="G4" s="383">
         <v>46000</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2467</v>
+        <v>2461</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
       <c r="J4" s="29" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1n16mhGgL5hDAtQ6qFzxI9NFNfQykOU-X/view?usp=drivesdk","Mr. Satish Chauhan-Mr. Meet Soni -Dr. Shubhrajyoti Kundu-Electrical and Electronics Engineering")</f>
         <v xml:space="preserve">Mr. Satish Chauhan-Mr. Meet Soni -Dr. Shubhrajyoti Kundu-Electrical and Electronics Engineering</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>2469</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1">
@@ -27172,35 +27103,35 @@
         <v>153</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>2470</v>
+        <v>2464</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>2471</v>
+        <v>2465</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>1980</v>
       </c>
       <c r="E5" s="313" t="s">
-        <v>2472</v>
+        <v>2466</v>
       </c>
       <c r="F5" s="314" t="s">
-        <v>2473</v>
+        <v>2467</v>
       </c>
       <c r="G5" s="383">
         <v>46049</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>2474</v>
+        <v>2468</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>2475</v>
+        <v>2469</v>
       </c>
       <c r="J5" s="29" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1jPavbgFDMvDUXjvBkZi9V70kg1vXfd-Z/view?usp=drivesdk","Dr. Kartik Pandya-Mr. Mahit Jain-Mr. Nishith Shahu-Basic Electrical Engineering")</f>
         <v xml:space="preserve">Dr. Kartik Pandya-Mr. Mahit Jain-Mr. Nishith Shahu-Basic Electrical Engineering</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>2469</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="6" ht="25.5" customHeight="1">
@@ -27208,35 +27139,35 @@
         <v>153</v>
       </c>
       <c r="B6" s="313" t="s">
-        <v>2476</v>
+        <v>2470</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>2477</v>
+        <v>2471</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
       <c r="E6" s="313" t="s">
-        <v>2479</v>
+        <v>2473</v>
       </c>
       <c r="F6" s="314" t="s">
-        <v>2480</v>
+        <v>2474</v>
       </c>
       <c r="G6" s="383">
         <v>46112</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2481</v>
+        <v>2475</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>2482</v>
+        <v>2476</v>
       </c>
       <c r="J6" s="29" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1DeMyC0OPH72maWPEeiYaheKsHDVIaxVk/view?usp=drivesdk","Mr. Ankitsinh Zala- Ms. Divya Garg-Ms. Niti Shah-CVPDE")</f>
         <v xml:space="preserve">Mr. Ankitsinh Zala- Ms. Divya Garg-Ms. Niti Shah-CVPDE</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>2469</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1">
@@ -27244,35 +27175,35 @@
         <v>231</v>
       </c>
       <c r="B7" s="386" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>2484</v>
+        <v>2478</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>2485</v>
+        <v>2479</v>
       </c>
       <c r="E7" s="319" t="s">
-        <v>2486</v>
+        <v>2480</v>
       </c>
       <c r="F7" s="320" t="s">
-        <v>2487</v>
+        <v>2481</v>
       </c>
       <c r="G7" s="38">
         <v>46045</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>2488</v>
+        <v>2482</v>
       </c>
       <c r="I7" s="40" t="s">
-        <v>2489</v>
+        <v>2483</v>
       </c>
       <c r="J7" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1bR7N2h-ig_cWAOuLrsIQetSxxCKb-0lH/view?usp=drivesdk","Mr. Purvesh Valanad- Mr.  Mujahid Mirchiwala- Mr. Gaurav Sahu-PC-1 (D.C Circuit)")</f>
         <v xml:space="preserve">Mr. Purvesh Valanad- Mr.  Mujahid Mirchiwala- Mr. Gaurav Sahu-PC-1 (D.C Circuit)</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>2490</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="8" ht="25.5" customHeight="1">
@@ -27280,35 +27211,35 @@
         <v>231</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>2491</v>
+        <v>2485</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>2492</v>
+        <v>2486</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
       <c r="E8" s="319" t="s">
-        <v>2494</v>
+        <v>2488</v>
       </c>
       <c r="F8" s="320" t="s">
-        <v>2495</v>
+        <v>2489</v>
       </c>
       <c r="G8" s="38">
         <v>46045</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>2496</v>
+        <v>2490</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>2497</v>
+        <v>2491</v>
       </c>
       <c r="J8" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1CUCNL_PHH9-S4BWwksdXE3P4KVcHkKVb/view?usp=drivesdk","Mr. Mayank Vyas-Mr.  Ankit Patel -Mr.  Nishant Hadiya-Introduction to Electrical Safety &amp; Management")</f>
         <v xml:space="preserve">Mr. Mayank Vyas-Mr.  Ankit Patel -Mr.  Nishant Hadiya-Introduction to Electrical Safety &amp; Management</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1">
@@ -27316,35 +27247,35 @@
         <v>231</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>2499</v>
+        <v>2493</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>2500</v>
+        <v>2494</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>2043</v>
       </c>
       <c r="E9" s="319" t="s">
-        <v>2501</v>
+        <v>2495</v>
       </c>
       <c r="F9" s="320" t="s">
-        <v>2502</v>
+        <v>2496</v>
       </c>
       <c r="G9" s="38">
         <v>46045</v>
       </c>
       <c r="H9" s="39" t="s">
-        <v>2503</v>
+        <v>2497</v>
       </c>
       <c r="I9" s="40" t="s">
-        <v>2504</v>
+        <v>2498</v>
       </c>
       <c r="J9" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1G8gCyX6grkmKZemfv_RVm6TE-UgCgDkk/view?usp=drivesdk","Ms. Hetal Prajapati- Mr. Pavez Vasovala -Mr. Apoorv Prajapati-Fundamental of Electrical Engineering")</f>
         <v xml:space="preserve">Ms. Hetal Prajapati- Mr. Pavez Vasovala -Mr. Apoorv Prajapati-Fundamental of Electrical Engineering</v>
       </c>
       <c r="K9" s="42" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1">
@@ -27352,35 +27283,35 @@
         <v>231</v>
       </c>
       <c r="B10" s="386" t="s">
-        <v>2505</v>
+        <v>2499</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>2506</v>
+        <v>2500</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>2507</v>
+        <v>2501</v>
       </c>
       <c r="E10" s="319" t="s">
-        <v>2508</v>
+        <v>2502</v>
       </c>
       <c r="F10" s="320" t="s">
-        <v>2509</v>
+        <v>2503</v>
       </c>
       <c r="G10" s="38">
         <v>46045</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>2510</v>
+        <v>2504</v>
       </c>
       <c r="I10" s="40" t="s">
-        <v>2511</v>
+        <v>2505</v>
       </c>
       <c r="J10" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1VJv8AVyaWSRQT6z4W-aHMhL3PYvBc-oD/view?usp=drivesdk","Mr. Krunal Kayasth-Mr.Jayesh Mahant-Mr.Manthan Thakkar-Engineering Graphics ")</f>
         <v xml:space="preserve">Mr. Krunal Kayasth-Mr.Jayesh Mahant-Mr.Manthan Thakkar-Engineering Graphics </v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
@@ -27388,35 +27319,35 @@
         <v>231</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>2512</v>
+        <v>2506</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>2513</v>
+        <v>2507</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>2514</v>
+        <v>2508</v>
       </c>
       <c r="E11" s="319" t="s">
-        <v>2515</v>
+        <v>2509</v>
       </c>
       <c r="F11" s="320" t="s">
-        <v>2516</v>
+        <v>2510</v>
       </c>
       <c r="G11" s="38">
         <v>46045</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>2517</v>
+        <v>2511</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>2518</v>
+        <v>2512</v>
       </c>
       <c r="J11" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/19EbhFU4xeVhKDZuDss6HbY45LQp6cTKE/view?usp=drivesdk","Ms. Bhumi Bhoi-Mr. Piyush Mali-Ms. Shreen Gazala-Internet Of Things")</f>
         <v xml:space="preserve">Ms. Bhumi Bhoi-Mr. Piyush Mali-Ms. Shreen Gazala-Internet Of Things</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1">
@@ -27424,35 +27355,35 @@
         <v>231</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>2519</v>
+        <v>2513</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>2520</v>
+        <v>2514</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>2521</v>
+        <v>2515</v>
       </c>
       <c r="E12" s="319" t="s">
-        <v>2522</v>
+        <v>2516</v>
       </c>
       <c r="F12" s="320" t="s">
-        <v>2523</v>
+        <v>2517</v>
       </c>
       <c r="G12" s="38">
         <v>46045</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>2524</v>
+        <v>2518</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>2525</v>
+        <v>2519</v>
       </c>
       <c r="J12" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1KrDK0eUPAgRnA0dBA63dtPfOMqY7BgyZ/view?usp=drivesdk","Mr. Ashish Pandey-Ms. Prachi Patel-Mr. Ravi Bhardwaj-Information Security")</f>
         <v xml:space="preserve">Mr. Ashish Pandey-Ms. Prachi Patel-Mr. Ravi Bhardwaj-Information Security</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1">
@@ -27460,35 +27391,35 @@
         <v>231</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>2526</v>
+        <v>2520</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>2527</v>
+        <v>2521</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
       <c r="E13" s="319" t="s">
-        <v>2529</v>
+        <v>2523</v>
       </c>
       <c r="F13" s="320" t="s">
-        <v>2530</v>
+        <v>2524</v>
       </c>
       <c r="G13" s="38">
         <v>46045</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>2531</v>
+        <v>2525</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>2532</v>
+        <v>2526</v>
       </c>
       <c r="J13" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1FgqU60t75_ag7Z53dxLp2NnBG1_MwSqP/view?usp=drivesdk","Mr. Kausal kalariya-Ms. Bipasha Mandal-Ms. Hemali Nimavat-operating system ")</f>
         <v xml:space="preserve">Mr. Kausal kalariya-Ms. Bipasha Mandal-Ms. Hemali Nimavat-operating system </v>
       </c>
       <c r="K13" s="42" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
@@ -27496,35 +27427,35 @@
         <v>231</v>
       </c>
       <c r="B14" s="389" t="s">
-        <v>2533</v>
+        <v>2527</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
       <c r="D14" s="319" t="s">
-        <v>2535</v>
+        <v>2529</v>
       </c>
       <c r="E14" s="319" t="s">
-        <v>2536</v>
+        <v>2530</v>
       </c>
       <c r="F14" s="320" t="s">
-        <v>2537</v>
+        <v>2531</v>
       </c>
       <c r="G14" s="38">
         <v>46045</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>2538</v>
+        <v>2532</v>
       </c>
       <c r="I14" s="40" t="s">
-        <v>2539</v>
+        <v>2533</v>
       </c>
       <c r="J14" s="41" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1fbJEegb0HZbuGNXG7EDtpErMg_dIOHrx/view?usp=drivesdk","Ms. Mansi Rana-Ms. Kavita Parmar-Mr. Bankim Parmar-Object Oriented Programming with C++")</f>
         <v xml:space="preserve">Ms. Mansi Rana-Ms. Kavita Parmar-Mr. Bankim Parmar-Object Oriented Programming with C++</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>2540</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1">
@@ -27532,35 +27463,35 @@
         <v>2091</v>
       </c>
       <c r="B15" s="347" t="s">
-        <v>2541</v>
+        <v>2535</v>
       </c>
       <c r="C15" s="347" t="s">
-        <v>2542</v>
+        <v>2536</v>
       </c>
       <c r="D15" s="347" t="s">
-        <v>2543</v>
+        <v>2537</v>
       </c>
       <c r="E15" s="340" t="s">
-        <v>2544</v>
+        <v>2538</v>
       </c>
       <c r="F15" s="342" t="s">
-        <v>2545</v>
+        <v>2539</v>
       </c>
       <c r="G15" s="390">
         <v>45995</v>
       </c>
       <c r="H15" s="391" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
       <c r="I15" s="392" t="s">
-        <v>2547</v>
+        <v>2541</v>
       </c>
       <c r="J15" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1Ws3s5W7VEXtsUKLgVOWAuoc3GnLwF-zx/view?usp=drivesdk","Ms. DEVANSHI THAKKAR-Ms. AMITA TAILOR-Ms. SHILPA KHANT-Web Design and Development")</f>
         <v xml:space="preserve">Ms. DEVANSHI THAKKAR-Ms. AMITA TAILOR-Ms. SHILPA KHANT-Web Design and Development</v>
       </c>
       <c r="K15" s="394" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1">
@@ -27568,35 +27499,35 @@
         <v>2091</v>
       </c>
       <c r="B16" s="347" t="s">
-        <v>2549</v>
+        <v>2543</v>
       </c>
       <c r="C16" s="347" t="s">
-        <v>2550</v>
+        <v>2544</v>
       </c>
       <c r="D16" s="347" t="s">
-        <v>2551</v>
+        <v>2545</v>
       </c>
       <c r="E16" s="340" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="F16" s="342" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
       <c r="G16" s="390">
         <v>45995</v>
       </c>
       <c r="H16" s="391" t="s">
-        <v>2554</v>
+        <v>2548</v>
       </c>
       <c r="I16" s="392" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
       <c r="J16" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1EA3derEjWlT9vfMnCJzJX3Q-_hYUiaOY/view?usp=drivesdk","Ms. VAIBHAVI PANDYA-Ms. RIYA DESAI-Mr.HARDIK KUMAR-Data Structure ")</f>
         <v xml:space="preserve">Ms. VAIBHAVI PANDYA-Ms. RIYA DESAI-Mr.HARDIK KUMAR-Data Structure </v>
       </c>
       <c r="K16" s="394" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1">
@@ -27604,35 +27535,35 @@
         <v>2091</v>
       </c>
       <c r="B17" s="391" t="s">
-        <v>2556</v>
+        <v>2550</v>
       </c>
       <c r="C17" s="395" t="s">
-        <v>2557</v>
+        <v>2551</v>
       </c>
       <c r="D17" s="391" t="s">
-        <v>2558</v>
+        <v>2552</v>
       </c>
       <c r="E17" s="341" t="s">
-        <v>2559</v>
+        <v>2553</v>
       </c>
       <c r="F17" s="342" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
       <c r="G17" s="390">
         <v>45995</v>
       </c>
       <c r="H17" s="391" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
       <c r="I17" s="392" t="s">
-        <v>2562</v>
+        <v>2556</v>
       </c>
       <c r="J17" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1hgvuw2wIiUg6VnB9OKISg3DhBcw7OgI9/view?usp=drivesdk","Ms. BHAVYA GAJIWALA-Ms. KAVYA PRAJAPATI-Ms. POONAM FALDU-Computer Network")</f>
         <v xml:space="preserve">Ms. BHAVYA GAJIWALA-Ms. KAVYA PRAJAPATI-Ms. POONAM FALDU-Computer Network</v>
       </c>
       <c r="K17" s="394" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1">
@@ -27640,35 +27571,35 @@
         <v>2091</v>
       </c>
       <c r="B18" s="391" t="s">
-        <v>2564</v>
+        <v>2558</v>
       </c>
       <c r="C18" s="395" t="s">
-        <v>2565</v>
+        <v>2559</v>
       </c>
       <c r="D18" s="391" t="s">
-        <v>2566</v>
+        <v>2560</v>
       </c>
       <c r="E18" s="341" t="s">
-        <v>2567</v>
+        <v>2561</v>
       </c>
       <c r="F18" s="342" t="s">
-        <v>2568</v>
+        <v>2562</v>
       </c>
       <c r="G18" s="390">
         <v>45995</v>
       </c>
       <c r="H18" s="391" t="s">
-        <v>2569</v>
+        <v>2563</v>
       </c>
       <c r="I18" s="392" t="s">
-        <v>2570</v>
+        <v>2564</v>
       </c>
       <c r="J18" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/159BT_GO9SchY3qO-sK9fZg4H87gfmKd8/view?usp=drivesdk","Ms. KALPANA PRAJAPATI-Ms. DEVIKA KSHTRIYA -Mr. VIJAY VASAIYA-.Net Programming with C# ")</f>
         <v xml:space="preserve">Ms. KALPANA PRAJAPATI-Ms. DEVIKA KSHTRIYA -Mr. VIJAY VASAIYA-.Net Programming with C# </v>
       </c>
       <c r="K18" s="394" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1">
@@ -27676,35 +27607,35 @@
         <v>2091</v>
       </c>
       <c r="B19" s="391" t="s">
-        <v>2571</v>
+        <v>2565</v>
       </c>
       <c r="C19" s="395" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
       <c r="D19" s="391" t="s">
-        <v>2573</v>
+        <v>2567</v>
       </c>
       <c r="E19" s="341" t="s">
         <v>741</v>
       </c>
       <c r="F19" s="342" t="s">
-        <v>2574</v>
+        <v>2568</v>
       </c>
       <c r="G19" s="390">
         <v>45995</v>
       </c>
       <c r="H19" s="391" t="s">
-        <v>2575</v>
+        <v>2569</v>
       </c>
       <c r="I19" s="392" t="s">
-        <v>2576</v>
+        <v>2570</v>
       </c>
       <c r="J19" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1rXSdUT4GUYZNTp0vq7wUtTeIBlBSuTiH/view?usp=drivesdk","Ms. Vrunda patel-Mr. Ankit Padariya, -Mr. Suraj singh-Database Management System")</f>
         <v xml:space="preserve">Ms. Vrunda patel-Mr. Ankit Padariya, -Mr. Suraj singh-Database Management System</v>
       </c>
       <c r="K19" s="394" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="20" ht="25.5" customHeight="1">
@@ -27712,35 +27643,35 @@
         <v>2091</v>
       </c>
       <c r="B20" s="391" t="s">
-        <v>2577</v>
+        <v>2571</v>
       </c>
       <c r="C20" s="395" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
       <c r="D20" s="391" t="s">
-        <v>2579</v>
+        <v>2573</v>
       </c>
       <c r="E20" s="341" t="s">
-        <v>2580</v>
+        <v>2574</v>
       </c>
       <c r="F20" s="342" t="s">
-        <v>2581</v>
+        <v>2575</v>
       </c>
       <c r="G20" s="390">
         <v>45995</v>
       </c>
       <c r="H20" s="391" t="s">
-        <v>2582</v>
+        <v>2576</v>
       </c>
       <c r="I20" s="392" t="s">
-        <v>2583</v>
+        <v>2577</v>
       </c>
       <c r="J20" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1T8n7Xg44gpdLLBHQdBlAnBL9pCsC1hDr/view?usp=drivesdk","Ms. Radhika Thakkar-BK Soni-Ms. Bhavya shah-Java")</f>
         <v xml:space="preserve">Ms. Radhika Thakkar-BK Soni-Ms. Bhavya shah-Java</v>
       </c>
       <c r="K20" s="394" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1">
@@ -27748,35 +27679,35 @@
         <v>2091</v>
       </c>
       <c r="B21" s="391" t="s">
-        <v>2584</v>
+        <v>2578</v>
       </c>
       <c r="C21" s="396" t="s">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="D21" s="340" t="s">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="E21" s="341" t="s">
-        <v>2587</v>
+        <v>2581</v>
       </c>
       <c r="F21" s="342" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
       <c r="G21" s="390">
         <v>45995</v>
       </c>
       <c r="H21" s="391" t="s">
-        <v>2589</v>
+        <v>2583</v>
       </c>
       <c r="I21" s="392" t="s">
-        <v>2590</v>
+        <v>2584</v>
       </c>
       <c r="J21" s="393" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1LJepmKp35DQCv8_zMRng1cGA4WlpdqmY/view?usp=drivesdk","Ms. Shivani Shelke-Ms. Shivani Gupta-Mr. Suraj Singh-Data Communication Network")</f>
         <v xml:space="preserve">Ms. Shivani Shelke-Ms. Shivani Gupta-Mr. Suraj Singh-Data Communication Network</v>
       </c>
       <c r="K21" s="394" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1">
@@ -27784,35 +27715,35 @@
         <v>2215</v>
       </c>
       <c r="B22" s="352" t="s">
-        <v>2591</v>
+        <v>2585</v>
       </c>
       <c r="C22" s="397" t="s">
-        <v>2592</v>
+        <v>2586</v>
       </c>
       <c r="D22" s="397" t="s">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="E22" s="106" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
       <c r="F22" s="350" t="s">
-        <v>2595</v>
+        <v>2589</v>
       </c>
       <c r="G22" s="108">
         <v>46059</v>
       </c>
       <c r="H22" s="109" t="s">
-        <v>2596</v>
+        <v>2590</v>
       </c>
       <c r="I22" s="110" t="s">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="J22" s="111" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/16qEIbqt9k8SYeiMrJ2rl8AYbgfK3MaUe/view?usp=drivesdk","Dr. Hiral Shah-Ms. Rachana S. Kumar- Mr. Harshrajsinh Rana-Pharmaceutics")</f>
         <v xml:space="preserve">Dr. Hiral Shah-Ms. Rachana S. Kumar- Mr. Harshrajsinh Rana-Pharmaceutics</v>
       </c>
       <c r="K22" s="112" t="s">
-        <v>2598</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="23" ht="25.5" customHeight="1">
@@ -27820,959 +27751,923 @@
         <v>2215</v>
       </c>
       <c r="B23" s="109" t="s">
-        <v>2599</v>
+        <v>2593</v>
       </c>
       <c r="C23" s="398" t="s">
-        <v>2600</v>
+        <v>2594</v>
       </c>
       <c r="D23" s="398" t="s">
-        <v>2601</v>
+        <v>2595</v>
       </c>
       <c r="E23" s="106" t="s">
-        <v>2602</v>
+        <v>2596</v>
       </c>
       <c r="F23" s="350" t="s">
-        <v>2603</v>
+        <v>2597</v>
       </c>
       <c r="G23" s="108">
         <v>46059</v>
       </c>
       <c r="H23" s="109" t="s">
-        <v>2604</v>
+        <v>2598</v>
       </c>
       <c r="I23" s="110" t="s">
-        <v>2605</v>
+        <v>2599</v>
       </c>
       <c r="J23" s="111" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1ob18LxgMFgPdVwBxS5ujusyRVFmq-7L1/view?usp=drivesdk","Ms. Tora Shah-Ms. Bhargavi Mistry-Ms. Krutika Agarwal-Pharmaceutics –Theory")</f>
         <v xml:space="preserve">Ms. Tora Shah-Ms. Bhargavi Mistry-Ms. Krutika Agarwal-Pharmaceutics –Theory</v>
       </c>
       <c r="K23" s="112" t="s">
-        <v>2598</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" s="399" t="s">
         <v>2091</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="400" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C24" s="401" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D24" s="401" t="s">
+        <v>2602</v>
+      </c>
+      <c r="E24" s="402" t="s">
+        <v>2603</v>
+      </c>
+      <c r="F24" s="350" t="s">
+        <v>2604</v>
+      </c>
+      <c r="G24" s="179">
+        <v>46049</v>
+      </c>
+      <c r="H24" s="364" t="s">
+        <v>2605</v>
+      </c>
+      <c r="I24" s="365" t="s">
         <v>2606</v>
       </c>
-      <c r="C24" s="400" t="s">
-        <v>2607</v>
-      </c>
-      <c r="D24" s="400" t="s">
-        <v>2608</v>
-      </c>
-      <c r="E24" s="401" t="s">
-        <v>2609</v>
-      </c>
-      <c r="F24" s="350" t="s">
-        <v>2610</v>
-      </c>
-      <c r="G24" s="108">
-        <v>46049</v>
-      </c>
-      <c r="H24" s="109" t="s">
-        <v>2611</v>
-      </c>
-      <c r="I24" s="110" t="s">
-        <v>2612</v>
-      </c>
-      <c r="J24" s="111" t="str">
-        <f>HYPERLINK("https://drive.google.com/file/d/1wOuYeHtarx_tKiscCvISOnpheAA3LoXB/view?usp=drivesdk","Mr. Ashish Shah-Mr. Vikash Verma-Mr. Ishan Desai-Power System - I ")</f>
-        <v xml:space="preserve">Mr. Ashish Shah-Mr. Vikash Verma-Mr. Ishan Desai-Power System - I </v>
-      </c>
-      <c r="K24" s="112" t="s">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="399" t="s">
-        <v>2091</v>
-      </c>
-      <c r="B25" s="402" t="s">
-        <v>2614</v>
-      </c>
-      <c r="C25" s="403" t="s">
-        <v>2615</v>
-      </c>
-      <c r="D25" s="403" t="s">
-        <v>2616</v>
-      </c>
-      <c r="E25" s="404" t="s">
-        <v>2617</v>
-      </c>
-      <c r="F25" s="350" t="s">
-        <v>2618</v>
-      </c>
-      <c r="G25" s="179">
-        <v>46049</v>
-      </c>
-      <c r="H25" s="364" t="s">
-        <v>2619</v>
-      </c>
-      <c r="I25" s="365" t="s">
-        <v>2620</v>
-      </c>
-      <c r="J25" s="366" t="str">
+      <c r="J24" s="366" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1lbETzF1tFEs_w8DSgGToTodeBlqUBv7e/view?usp=drivesdk","Mrs. Priyanka Patel-Mr. Priyank Makwana-Ms. Krishna Gohil-Mathematics - I")</f>
         <v xml:space="preserve">Mrs. Priyanka Patel-Mr. Priyank Makwana-Ms. Krishna Gohil-Mathematics - I</v>
       </c>
-      <c r="K25" s="367" t="s">
+      <c r="K24" s="367" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25" s="403" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B25" s="404" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C25" s="404" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D25" s="405" t="s">
+        <v>2611</v>
+      </c>
+      <c r="E25" s="372" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F25" s="406" t="s">
+        <v>2613</v>
+      </c>
+      <c r="G25" s="407">
+        <v>46139</v>
+      </c>
+      <c r="H25" s="276" t="s">
+        <v>2614</v>
+      </c>
+      <c r="I25" s="277" t="s">
+        <v>2615</v>
+      </c>
+      <c r="J25" s="277" t="s">
+        <v>2616</v>
+      </c>
+      <c r="K25" s="278" t="s">
+        <v>2617</v>
+      </c>
+      <c r="L25" s="190"/>
+      <c r="M25" s="190"/>
+    </row>
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26" s="227" t="s">
+        <v>231</v>
+      </c>
+      <c r="B26" s="203" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C26" s="203" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D26" s="408" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E26" s="212" t="s">
         <v>2621</v>
       </c>
-    </row>
-    <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="405" t="s">
+      <c r="F26" s="194" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G26" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H26" s="203" t="s">
         <v>2622</v>
       </c>
-      <c r="B26" s="406" t="s">
+      <c r="I26" s="204" t="s">
         <v>2623</v>
       </c>
-      <c r="C26" s="406" t="s">
+      <c r="J26" s="204" t="s">
         <v>2624</v>
       </c>
-      <c r="D26" s="407" t="s">
+      <c r="K26" s="205" t="s">
         <v>2625</v>
-      </c>
-      <c r="E26" s="372" t="s">
-        <v>2626</v>
-      </c>
-      <c r="F26" s="408" t="s">
-        <v>2627</v>
-      </c>
-      <c r="G26" s="409">
-        <v>46139</v>
-      </c>
-      <c r="H26" s="276" t="s">
-        <v>2628</v>
-      </c>
-      <c r="I26" s="277" t="s">
-        <v>2629</v>
-      </c>
-      <c r="J26" s="277" t="s">
-        <v>2630</v>
-      </c>
-      <c r="K26" s="278" t="s">
-        <v>2631</v>
       </c>
       <c r="L26" s="190"/>
       <c r="M26" s="190"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="227" t="s">
-        <v>231</v>
-      </c>
-      <c r="B27" s="203" t="s">
+      <c r="A27" s="191" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B27" s="196" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C27" s="196" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D27" s="409" t="s">
+        <v>2628</v>
+      </c>
+      <c r="E27" s="230" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F27" s="194" t="s">
+        <v>2630</v>
+      </c>
+      <c r="G27" s="195">
+        <v>46139</v>
+      </c>
+      <c r="H27" s="196" t="s">
+        <v>2631</v>
+      </c>
+      <c r="I27" s="197" t="s">
         <v>2632</v>
       </c>
-      <c r="C27" s="203" t="s">
+      <c r="J27" s="197" t="s">
         <v>2633</v>
       </c>
-      <c r="D27" s="410" t="s">
+      <c r="K27" s="198" t="s">
         <v>2634</v>
-      </c>
-      <c r="E27" s="212" t="s">
-        <v>2635</v>
-      </c>
-      <c r="F27" s="194" t="s">
-        <v>1595</v>
-      </c>
-      <c r="G27" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H27" s="203" t="s">
-        <v>2636</v>
-      </c>
-      <c r="I27" s="204" t="s">
-        <v>2637</v>
-      </c>
-      <c r="J27" s="204" t="s">
-        <v>2638</v>
-      </c>
-      <c r="K27" s="205" t="s">
-        <v>2639</v>
       </c>
       <c r="L27" s="190"/>
       <c r="M27" s="190"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
-      <c r="A28" s="191" t="s">
+      <c r="A28" s="410" t="s">
         <v>1619</v>
       </c>
-      <c r="B28" s="196" t="s">
+      <c r="B28" s="203" t="s">
+        <v>2635</v>
+      </c>
+      <c r="C28" s="203" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D28" s="408" t="s">
+        <v>2637</v>
+      </c>
+      <c r="E28" s="212" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F28" s="194" t="s">
+        <v>2639</v>
+      </c>
+      <c r="G28" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H28" s="203" t="s">
         <v>2640</v>
       </c>
-      <c r="C28" s="196" t="s">
+      <c r="I28" s="204" t="s">
         <v>2641</v>
       </c>
-      <c r="D28" s="411" t="s">
+      <c r="J28" s="204" t="s">
         <v>2642</v>
       </c>
-      <c r="E28" s="230" t="s">
-        <v>2643</v>
-      </c>
-      <c r="F28" s="194" t="s">
-        <v>2644</v>
-      </c>
-      <c r="G28" s="195">
-        <v>46139</v>
-      </c>
-      <c r="H28" s="196" t="s">
-        <v>2645</v>
-      </c>
-      <c r="I28" s="197" t="s">
-        <v>2646</v>
-      </c>
-      <c r="J28" s="197" t="s">
-        <v>2647</v>
-      </c>
-      <c r="K28" s="198" t="s">
-        <v>2648</v>
+      <c r="K28" s="205" t="s">
+        <v>2634</v>
       </c>
       <c r="L28" s="190"/>
       <c r="M28" s="190"/>
     </row>
     <row r="29" ht="25.5" customHeight="1">
-      <c r="A29" s="412" t="s">
+      <c r="A29" s="410" t="s">
         <v>1619</v>
       </c>
-      <c r="B29" s="203" t="s">
+      <c r="B29" s="196" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C29" s="196" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D29" s="409" t="s">
+        <v>2645</v>
+      </c>
+      <c r="E29" s="230" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F29" s="194" t="s">
+        <v>2647</v>
+      </c>
+      <c r="G29" s="195">
+        <v>46139</v>
+      </c>
+      <c r="H29" s="196" t="s">
+        <v>2648</v>
+      </c>
+      <c r="I29" s="197" t="s">
         <v>2649</v>
       </c>
-      <c r="C29" s="203" t="s">
+      <c r="J29" s="197" t="s">
         <v>2650</v>
       </c>
-      <c r="D29" s="410" t="s">
-        <v>2651</v>
-      </c>
-      <c r="E29" s="212" t="s">
-        <v>2652</v>
-      </c>
-      <c r="F29" s="194" t="s">
-        <v>2653</v>
-      </c>
-      <c r="G29" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H29" s="203" t="s">
-        <v>2654</v>
-      </c>
-      <c r="I29" s="204" t="s">
-        <v>2655</v>
-      </c>
-      <c r="J29" s="204" t="s">
-        <v>2656</v>
-      </c>
-      <c r="K29" s="205" t="s">
-        <v>2648</v>
+      <c r="K29" s="198" t="s">
+        <v>2634</v>
       </c>
       <c r="L29" s="190"/>
       <c r="M29" s="190"/>
     </row>
     <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="412" t="s">
+      <c r="A30" s="410" t="s">
         <v>1619</v>
       </c>
-      <c r="B30" s="196" t="s">
+      <c r="B30" s="203" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C30" s="203" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D30" s="408" t="s">
+        <v>2653</v>
+      </c>
+      <c r="E30" s="212" t="s">
+        <v>2654</v>
+      </c>
+      <c r="F30" s="194" t="s">
+        <v>2655</v>
+      </c>
+      <c r="G30" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H30" s="203" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I30" s="204" t="s">
         <v>2657</v>
       </c>
-      <c r="C30" s="196" t="s">
+      <c r="J30" s="204" t="s">
         <v>2658</v>
       </c>
-      <c r="D30" s="411" t="s">
-        <v>2659</v>
-      </c>
-      <c r="E30" s="230" t="s">
-        <v>2660</v>
-      </c>
-      <c r="F30" s="194" t="s">
-        <v>2661</v>
-      </c>
-      <c r="G30" s="195">
-        <v>46139</v>
-      </c>
-      <c r="H30" s="196" t="s">
-        <v>2662</v>
-      </c>
-      <c r="I30" s="197" t="s">
-        <v>2663</v>
-      </c>
-      <c r="J30" s="197" t="s">
-        <v>2664</v>
-      </c>
-      <c r="K30" s="198" t="s">
-        <v>2648</v>
+      <c r="K30" s="205" t="s">
+        <v>2328</v>
       </c>
       <c r="L30" s="190"/>
       <c r="M30" s="190"/>
     </row>
     <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="412" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B31" s="203" t="s">
+      <c r="A31" s="191" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B31" s="196" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C31" s="196" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D31" s="409" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E31" s="230" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F31" s="194" t="s">
+        <v>2663</v>
+      </c>
+      <c r="G31" s="195">
+        <v>46139</v>
+      </c>
+      <c r="H31" s="196" t="s">
+        <v>2664</v>
+      </c>
+      <c r="I31" s="197" t="s">
         <v>2665</v>
       </c>
-      <c r="C31" s="203" t="s">
+      <c r="J31" s="197" t="s">
         <v>2666</v>
       </c>
-      <c r="D31" s="410" t="s">
+      <c r="K31" s="198" t="s">
         <v>2667</v>
-      </c>
-      <c r="E31" s="212" t="s">
-        <v>2668</v>
-      </c>
-      <c r="F31" s="194" t="s">
-        <v>2669</v>
-      </c>
-      <c r="G31" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H31" s="203" t="s">
-        <v>2670</v>
-      </c>
-      <c r="I31" s="204" t="s">
-        <v>2671</v>
-      </c>
-      <c r="J31" s="204" t="s">
-        <v>2672</v>
-      </c>
-      <c r="K31" s="205" t="s">
-        <v>2328</v>
       </c>
       <c r="L31" s="190"/>
       <c r="M31" s="190"/>
     </row>
     <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="191" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B32" s="196" t="s">
+      <c r="A32" s="227" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B32" s="203" t="s">
+        <v>2669</v>
+      </c>
+      <c r="C32" s="203" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D32" s="408" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E32" s="212" t="s">
+        <v>2672</v>
+      </c>
+      <c r="F32" s="194" t="s">
         <v>2673</v>
       </c>
-      <c r="C32" s="196" t="s">
+      <c r="G32" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H32" s="203" t="s">
         <v>2674</v>
       </c>
-      <c r="D32" s="411" t="s">
+      <c r="I32" s="204" t="s">
         <v>2675</v>
       </c>
-      <c r="E32" s="230" t="s">
+      <c r="J32" s="204" t="s">
         <v>2676</v>
       </c>
-      <c r="F32" s="194" t="s">
+      <c r="K32" s="205" t="s">
         <v>2677</v>
-      </c>
-      <c r="G32" s="195">
-        <v>46139</v>
-      </c>
-      <c r="H32" s="196" t="s">
-        <v>2678</v>
-      </c>
-      <c r="I32" s="197" t="s">
-        <v>2679</v>
-      </c>
-      <c r="J32" s="197" t="s">
-        <v>2680</v>
-      </c>
-      <c r="K32" s="198" t="s">
-        <v>2681</v>
       </c>
       <c r="L32" s="190"/>
       <c r="M32" s="190"/>
     </row>
     <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="227" t="s">
+      <c r="A33" s="411" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B33" s="196" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C33" s="196" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D33" s="409" t="s">
+        <v>2680</v>
+      </c>
+      <c r="E33" s="230" t="s">
+        <v>2681</v>
+      </c>
+      <c r="F33" s="194" t="s">
         <v>2682</v>
       </c>
-      <c r="B33" s="203" t="s">
+      <c r="G33" s="195">
+        <v>46139</v>
+      </c>
+      <c r="H33" s="196" t="s">
         <v>2683</v>
       </c>
-      <c r="C33" s="203" t="s">
+      <c r="I33" s="197" t="s">
         <v>2684</v>
       </c>
-      <c r="D33" s="410" t="s">
+      <c r="J33" s="197" t="s">
         <v>2685</v>
       </c>
-      <c r="E33" s="212" t="s">
-        <v>2686</v>
-      </c>
-      <c r="F33" s="194" t="s">
-        <v>2687</v>
-      </c>
-      <c r="G33" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H33" s="203" t="s">
-        <v>2688</v>
-      </c>
-      <c r="I33" s="204" t="s">
-        <v>2689</v>
-      </c>
-      <c r="J33" s="204" t="s">
-        <v>2690</v>
-      </c>
-      <c r="K33" s="205" t="s">
-        <v>2691</v>
+      <c r="K33" s="198" t="s">
+        <v>2677</v>
       </c>
       <c r="L33" s="190"/>
       <c r="M33" s="190"/>
     </row>
     <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="413" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B34" s="196" t="s">
+      <c r="A34" s="411" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B34" s="203" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C34" s="203" t="s">
+        <v>2687</v>
+      </c>
+      <c r="D34" s="408" t="s">
+        <v>2688</v>
+      </c>
+      <c r="E34" s="212" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F34" s="194" t="s">
+        <v>2690</v>
+      </c>
+      <c r="G34" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H34" s="203" t="s">
+        <v>2691</v>
+      </c>
+      <c r="I34" s="204" t="s">
         <v>2692</v>
       </c>
-      <c r="C34" s="196" t="s">
+      <c r="J34" s="204" t="s">
         <v>2693</v>
       </c>
-      <c r="D34" s="411" t="s">
-        <v>2694</v>
-      </c>
-      <c r="E34" s="230" t="s">
-        <v>2695</v>
-      </c>
-      <c r="F34" s="194" t="s">
-        <v>2696</v>
-      </c>
-      <c r="G34" s="195">
-        <v>46139</v>
-      </c>
-      <c r="H34" s="196" t="s">
-        <v>2697</v>
-      </c>
-      <c r="I34" s="197" t="s">
-        <v>2698</v>
-      </c>
-      <c r="J34" s="197" t="s">
-        <v>2699</v>
-      </c>
-      <c r="K34" s="198" t="s">
-        <v>2691</v>
+      <c r="K34" s="205" t="s">
+        <v>2677</v>
       </c>
       <c r="L34" s="190"/>
       <c r="M34" s="190"/>
     </row>
     <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="413" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B35" s="203" t="s">
+      <c r="A35" s="411" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B35" s="196" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C35" s="196" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D35" s="409" t="s">
+        <v>2696</v>
+      </c>
+      <c r="E35" s="230" t="s">
+        <v>2697</v>
+      </c>
+      <c r="F35" s="194" t="s">
+        <v>2698</v>
+      </c>
+      <c r="G35" s="195">
+        <v>46139</v>
+      </c>
+      <c r="H35" s="196" t="s">
+        <v>2699</v>
+      </c>
+      <c r="I35" s="197" t="s">
         <v>2700</v>
       </c>
-      <c r="C35" s="203" t="s">
+      <c r="J35" s="197" t="s">
         <v>2701</v>
       </c>
-      <c r="D35" s="410" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E35" s="212" t="s">
-        <v>2703</v>
-      </c>
-      <c r="F35" s="194" t="s">
-        <v>2704</v>
-      </c>
-      <c r="G35" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H35" s="203" t="s">
-        <v>2705</v>
-      </c>
-      <c r="I35" s="204" t="s">
-        <v>2706</v>
-      </c>
-      <c r="J35" s="204" t="s">
-        <v>2707</v>
-      </c>
-      <c r="K35" s="205" t="s">
-        <v>2691</v>
+      <c r="K35" s="198" t="s">
+        <v>2677</v>
       </c>
       <c r="L35" s="190"/>
       <c r="M35" s="190"/>
     </row>
     <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="413" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B36" s="196" t="s">
+      <c r="A36" s="411" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B36" s="203" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C36" s="203" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D36" s="408" t="s">
+        <v>2704</v>
+      </c>
+      <c r="E36" s="212" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F36" s="194" t="s">
+        <v>2706</v>
+      </c>
+      <c r="G36" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H36" s="203" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I36" s="204" t="s">
         <v>2708</v>
       </c>
-      <c r="C36" s="196" t="s">
+      <c r="J36" s="204" t="s">
         <v>2709</v>
       </c>
-      <c r="D36" s="411" t="s">
-        <v>2710</v>
-      </c>
-      <c r="E36" s="230" t="s">
-        <v>2711</v>
-      </c>
-      <c r="F36" s="194" t="s">
-        <v>2712</v>
-      </c>
-      <c r="G36" s="195">
-        <v>46139</v>
-      </c>
-      <c r="H36" s="196" t="s">
-        <v>2713</v>
-      </c>
-      <c r="I36" s="197" t="s">
-        <v>2714</v>
-      </c>
-      <c r="J36" s="197" t="s">
-        <v>2715</v>
-      </c>
-      <c r="K36" s="198" t="s">
-        <v>2691</v>
+      <c r="K36" s="205" t="s">
+        <v>2677</v>
       </c>
       <c r="L36" s="190"/>
       <c r="M36" s="190"/>
     </row>
     <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="413" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B37" s="203" t="s">
+      <c r="A37" s="191" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B37" s="196" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C37" s="196" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D37" s="409" t="s">
+        <v>2712</v>
+      </c>
+      <c r="E37" s="230" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F37" s="194" t="s">
+        <v>2714</v>
+      </c>
+      <c r="G37" s="195">
+        <v>46139</v>
+      </c>
+      <c r="H37" s="196" t="s">
+        <v>2715</v>
+      </c>
+      <c r="I37" s="197" t="s">
         <v>2716</v>
       </c>
-      <c r="C37" s="203" t="s">
+      <c r="J37" s="197" t="s">
         <v>2717</v>
       </c>
-      <c r="D37" s="410" t="s">
+      <c r="K37" s="198" t="s">
         <v>2718</v>
-      </c>
-      <c r="E37" s="212" t="s">
-        <v>2719</v>
-      </c>
-      <c r="F37" s="194" t="s">
-        <v>2720</v>
-      </c>
-      <c r="G37" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H37" s="203" t="s">
-        <v>2721</v>
-      </c>
-      <c r="I37" s="204" t="s">
-        <v>2722</v>
-      </c>
-      <c r="J37" s="204" t="s">
-        <v>2723</v>
-      </c>
-      <c r="K37" s="205" t="s">
-        <v>2691</v>
       </c>
       <c r="L37" s="190"/>
       <c r="M37" s="190"/>
     </row>
     <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="191" t="s">
+      <c r="A38" s="410" t="s">
         <v>1652</v>
       </c>
-      <c r="B38" s="196" t="s">
+      <c r="B38" s="203" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C38" s="203" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D38" s="408" t="s">
+        <v>2721</v>
+      </c>
+      <c r="E38" s="212" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F38" s="194" t="s">
+        <v>2723</v>
+      </c>
+      <c r="G38" s="202">
+        <v>46139</v>
+      </c>
+      <c r="H38" s="203" t="s">
         <v>2724</v>
       </c>
-      <c r="C38" s="196" t="s">
+      <c r="I38" s="204" t="s">
         <v>2725</v>
       </c>
-      <c r="D38" s="411" t="s">
+      <c r="J38" s="204" t="s">
         <v>2726</v>
       </c>
-      <c r="E38" s="230" t="s">
-        <v>2727</v>
-      </c>
-      <c r="F38" s="194" t="s">
-        <v>2728</v>
-      </c>
-      <c r="G38" s="195">
-        <v>46139</v>
-      </c>
-      <c r="H38" s="196" t="s">
-        <v>2729</v>
-      </c>
-      <c r="I38" s="197" t="s">
-        <v>2730</v>
-      </c>
-      <c r="J38" s="197" t="s">
-        <v>2731</v>
-      </c>
-      <c r="K38" s="198" t="s">
-        <v>2732</v>
+      <c r="K38" s="205" t="s">
+        <v>2718</v>
       </c>
       <c r="L38" s="190"/>
       <c r="M38" s="190"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="412" t="s">
+      <c r="A39" s="410" t="s">
         <v>1652</v>
       </c>
-      <c r="B39" s="203" t="s">
+      <c r="B39" s="196" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C39" s="196" t="s">
+        <v>2728</v>
+      </c>
+      <c r="D39" s="196" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E39" s="230" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F39" s="412" t="s">
+        <v>2731</v>
+      </c>
+      <c r="G39" s="413">
+        <v>46139</v>
+      </c>
+      <c r="H39" s="196" t="s">
+        <v>2732</v>
+      </c>
+      <c r="I39" s="197" t="s">
         <v>2733</v>
       </c>
-      <c r="C39" s="203" t="s">
+      <c r="J39" s="197" t="s">
         <v>2734</v>
       </c>
-      <c r="D39" s="410" t="s">
+      <c r="K39" s="198" t="s">
         <v>2735</v>
-      </c>
-      <c r="E39" s="212" t="s">
-        <v>2736</v>
-      </c>
-      <c r="F39" s="194" t="s">
-        <v>2737</v>
-      </c>
-      <c r="G39" s="202">
-        <v>46139</v>
-      </c>
-      <c r="H39" s="203" t="s">
-        <v>2738</v>
-      </c>
-      <c r="I39" s="204" t="s">
-        <v>2739</v>
-      </c>
-      <c r="J39" s="204" t="s">
-        <v>2740</v>
-      </c>
-      <c r="K39" s="205" t="s">
-        <v>2732</v>
       </c>
       <c r="L39" s="190"/>
       <c r="M39" s="190"/>
     </row>
     <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="412" t="s">
-        <v>1652</v>
-      </c>
-      <c r="B40" s="196" t="s">
+      <c r="A40" s="227" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="203" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C40" s="203" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D40" s="203" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E40" s="212" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F40" s="194" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G40" s="414">
+        <v>46139</v>
+      </c>
+      <c r="H40" s="203" t="s">
+        <v>2740</v>
+      </c>
+      <c r="I40" s="204" t="s">
         <v>2741</v>
       </c>
-      <c r="C40" s="196" t="s">
+      <c r="J40" s="204" t="s">
         <v>2742</v>
       </c>
-      <c r="D40" s="196" t="s">
+      <c r="K40" s="205" t="s">
         <v>2743</v>
-      </c>
-      <c r="E40" s="230" t="s">
-        <v>2744</v>
-      </c>
-      <c r="F40" s="414" t="s">
-        <v>2745</v>
-      </c>
-      <c r="G40" s="415">
-        <v>46139</v>
-      </c>
-      <c r="H40" s="196" t="s">
-        <v>2746</v>
-      </c>
-      <c r="I40" s="197" t="s">
-        <v>2747</v>
-      </c>
-      <c r="J40" s="197" t="s">
-        <v>2748</v>
-      </c>
-      <c r="K40" s="198" t="s">
-        <v>2749</v>
       </c>
       <c r="L40" s="190"/>
       <c r="M40" s="190"/>
     </row>
     <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="227" t="s">
+      <c r="A41" s="411" t="s">
         <v>153</v>
       </c>
-      <c r="B41" s="203" t="s">
+      <c r="B41" s="196" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C41" s="196" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D41" s="196" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E41" s="230" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F41" s="194" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G41" s="413">
+        <v>46139</v>
+      </c>
+      <c r="H41" s="196" t="s">
+        <v>2748</v>
+      </c>
+      <c r="I41" s="197" t="s">
+        <v>2749</v>
+      </c>
+      <c r="J41" s="197" t="s">
         <v>2750</v>
       </c>
-      <c r="C41" s="203" t="s">
+      <c r="K41" s="198" t="s">
         <v>2751</v>
-      </c>
-      <c r="D41" s="203" t="s">
-        <v>2752</v>
-      </c>
-      <c r="E41" s="212" t="s">
-        <v>2753</v>
-      </c>
-      <c r="F41" s="194" t="s">
-        <v>1668</v>
-      </c>
-      <c r="G41" s="416">
-        <v>46139</v>
-      </c>
-      <c r="H41" s="203" t="s">
-        <v>2754</v>
-      </c>
-      <c r="I41" s="204" t="s">
-        <v>2755</v>
-      </c>
-      <c r="J41" s="204" t="s">
-        <v>2756</v>
-      </c>
-      <c r="K41" s="205" t="s">
-        <v>2757</v>
       </c>
       <c r="L41" s="190"/>
       <c r="M41" s="190"/>
     </row>
     <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="413" t="s">
+      <c r="A42" s="415" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="196" t="s">
+      <c r="B42" s="203" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C42" s="203" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D42" s="203" t="s">
+        <v>2754</v>
+      </c>
+      <c r="E42" s="212" t="s">
+        <v>2755</v>
+      </c>
+      <c r="F42" s="194" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G42" s="414">
+        <v>46139</v>
+      </c>
+      <c r="H42" s="203" t="s">
+        <v>2756</v>
+      </c>
+      <c r="I42" s="204" t="s">
+        <v>2757</v>
+      </c>
+      <c r="J42" s="204" t="s">
         <v>2758</v>
       </c>
-      <c r="C42" s="196" t="s">
-        <v>2759</v>
-      </c>
-      <c r="D42" s="196" t="s">
-        <v>2760</v>
-      </c>
-      <c r="E42" s="230" t="s">
-        <v>2761</v>
-      </c>
-      <c r="F42" s="194" t="s">
-        <v>1674</v>
-      </c>
-      <c r="G42" s="415">
-        <v>46139</v>
-      </c>
-      <c r="H42" s="196" t="s">
-        <v>2762</v>
-      </c>
-      <c r="I42" s="197" t="s">
-        <v>2763</v>
-      </c>
-      <c r="J42" s="197" t="s">
-        <v>2764</v>
-      </c>
-      <c r="K42" s="198" t="s">
-        <v>2765</v>
+      <c r="K42" s="205" t="s">
+        <v>2751</v>
       </c>
       <c r="L42" s="190"/>
       <c r="M42" s="190"/>
     </row>
     <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="417" t="s">
+      <c r="A43" s="227" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="203" t="s">
-        <v>2766</v>
-      </c>
-      <c r="C43" s="203" t="s">
-        <v>2767</v>
-      </c>
-      <c r="D43" s="203" t="s">
-        <v>2768</v>
-      </c>
-      <c r="E43" s="212" t="s">
-        <v>2769</v>
-      </c>
-      <c r="F43" s="194" t="s">
-        <v>1680</v>
-      </c>
-      <c r="G43" s="416">
+      <c r="B43" s="416" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C43" s="276" t="s">
+        <v>2744</v>
+      </c>
+      <c r="D43" s="276" t="s">
+        <v>2760</v>
+      </c>
+      <c r="E43" s="372" t="s">
+        <v>2761</v>
+      </c>
+      <c r="F43" s="185" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G43" s="417">
         <v>46139</v>
       </c>
-      <c r="H43" s="203" t="s">
-        <v>2770</v>
-      </c>
-      <c r="I43" s="204" t="s">
-        <v>2771</v>
-      </c>
-      <c r="J43" s="204" t="s">
-        <v>2772</v>
-      </c>
-      <c r="K43" s="205" t="s">
-        <v>2765</v>
+      <c r="H43" s="276" t="s">
+        <v>2762</v>
+      </c>
+      <c r="I43" s="277" t="s">
+        <v>2763</v>
+      </c>
+      <c r="J43" s="277" t="s">
+        <v>2764</v>
+      </c>
+      <c r="K43" s="278" t="s">
+        <v>2751</v>
       </c>
       <c r="L43" s="190"/>
       <c r="M43" s="190"/>
     </row>
     <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="227" t="s">
-        <v>153</v>
-      </c>
-      <c r="B44" s="418" t="s">
-        <v>2773</v>
-      </c>
-      <c r="C44" s="276" t="s">
-        <v>2758</v>
-      </c>
-      <c r="D44" s="276" t="s">
-        <v>2774</v>
-      </c>
-      <c r="E44" s="372" t="s">
-        <v>2775</v>
-      </c>
-      <c r="F44" s="185" t="s">
-        <v>1685</v>
+      <c r="A44" s="418" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B44" s="203" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C44" s="203" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D44" s="203" t="s">
+        <v>2768</v>
+      </c>
+      <c r="E44" s="212" t="s">
+        <v>2769</v>
+      </c>
+      <c r="F44" s="194" t="s">
+        <v>1691</v>
       </c>
       <c r="G44" s="419">
         <v>46139</v>
       </c>
-      <c r="H44" s="276" t="s">
-        <v>2776</v>
-      </c>
-      <c r="I44" s="277" t="s">
-        <v>2777</v>
-      </c>
-      <c r="J44" s="277" t="s">
-        <v>2778</v>
-      </c>
-      <c r="K44" s="278" t="s">
-        <v>2765</v>
+      <c r="H44" s="203" t="s">
+        <v>2770</v>
+      </c>
+      <c r="I44" s="204" t="s">
+        <v>2771</v>
+      </c>
+      <c r="J44" s="204" t="s">
+        <v>2772</v>
+      </c>
+      <c r="K44" s="205" t="s">
+        <v>2773</v>
       </c>
       <c r="L44" s="190"/>
       <c r="M44" s="190"/>
     </row>
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" s="420" t="s">
-        <v>2779</v>
-      </c>
-      <c r="B45" s="203" t="s">
-        <v>2780</v>
-      </c>
-      <c r="C45" s="203" t="s">
-        <v>2781</v>
-      </c>
-      <c r="D45" s="203" t="s">
-        <v>2782</v>
-      </c>
-      <c r="E45" s="212" t="s">
-        <v>2783</v>
+        <v>2765</v>
+      </c>
+      <c r="B45" s="196" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C45" s="196" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D45" s="196" t="s">
+        <v>2776</v>
+      </c>
+      <c r="E45" s="230" t="s">
+        <v>2777</v>
       </c>
       <c r="F45" s="194" t="s">
-        <v>1691</v>
+        <v>1697</v>
       </c>
       <c r="G45" s="421">
         <v>46139</v>
       </c>
-      <c r="H45" s="203" t="s">
-        <v>2784</v>
-      </c>
-      <c r="I45" s="204" t="s">
-        <v>2785</v>
-      </c>
-      <c r="J45" s="204" t="s">
-        <v>2786</v>
-      </c>
-      <c r="K45" s="205" t="s">
-        <v>2787</v>
+      <c r="H45" s="196" t="s">
+        <v>2778</v>
+      </c>
+      <c r="I45" s="197" t="s">
+        <v>2779</v>
+      </c>
+      <c r="J45" s="197" t="s">
+        <v>2780</v>
+      </c>
+      <c r="K45" s="198" t="s">
+        <v>2773</v>
       </c>
       <c r="L45" s="190"/>
       <c r="M45" s="190"/>
     </row>
     <row r="46" ht="25.5" customHeight="1">
-      <c r="A46" s="422" t="s">
-        <v>2779</v>
-      </c>
-      <c r="B46" s="196" t="s">
-        <v>2788</v>
-      </c>
-      <c r="C46" s="196" t="s">
-        <v>2789</v>
-      </c>
-      <c r="D46" s="196" t="s">
-        <v>2790</v>
-      </c>
-      <c r="E46" s="230" t="s">
-        <v>2791</v>
+      <c r="A46" s="420" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B46" s="203" t="s">
+        <v>2781</v>
+      </c>
+      <c r="C46" s="203" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D46" s="203" t="s">
+        <v>2783</v>
+      </c>
+      <c r="E46" s="212" t="s">
+        <v>2784</v>
       </c>
       <c r="F46" s="194" t="s">
-        <v>1697</v>
-      </c>
-      <c r="G46" s="423">
+        <v>1702</v>
+      </c>
+      <c r="G46" s="419">
         <v>46139</v>
       </c>
-      <c r="H46" s="196" t="s">
-        <v>2792</v>
-      </c>
-      <c r="I46" s="197" t="s">
-        <v>2793</v>
-      </c>
-      <c r="J46" s="197" t="s">
-        <v>2794</v>
-      </c>
-      <c r="K46" s="198" t="s">
+      <c r="H46" s="203" t="s">
+        <v>2785</v>
+      </c>
+      <c r="I46" s="204" t="s">
+        <v>2786</v>
+      </c>
+      <c r="J46" s="204" t="s">
         <v>2787</v>
+      </c>
+      <c r="K46" s="205" t="s">
+        <v>2773</v>
       </c>
       <c r="L46" s="190"/>
       <c r="M46" s="190"/>
     </row>
     <row r="47" ht="25.5" customHeight="1">
       <c r="A47" s="422" t="s">
-        <v>2779</v>
-      </c>
-      <c r="B47" s="203" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B47" s="423" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C47" s="423" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D47" s="244" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E47" s="424" t="s">
+        <v>2792</v>
+      </c>
+      <c r="F47" s="194" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G47" s="425">
+        <v>46148</v>
+      </c>
+      <c r="H47" s="244" t="s">
+        <v>2793</v>
+      </c>
+      <c r="I47" s="245" t="s">
+        <v>2794</v>
+      </c>
+      <c r="J47" s="245" t="s">
         <v>2795</v>
       </c>
-      <c r="C47" s="203" t="s">
+      <c r="K47" s="246" t="s">
         <v>2796</v>
-      </c>
-      <c r="D47" s="203" t="s">
-        <v>2797</v>
-      </c>
-      <c r="E47" s="212" t="s">
-        <v>2798</v>
-      </c>
-      <c r="F47" s="194" t="s">
-        <v>1702</v>
-      </c>
-      <c r="G47" s="421">
-        <v>46139</v>
-      </c>
-      <c r="H47" s="203" t="s">
-        <v>2799</v>
-      </c>
-      <c r="I47" s="204" t="s">
-        <v>2800</v>
-      </c>
-      <c r="J47" s="204" t="s">
-        <v>2801</v>
-      </c>
-      <c r="K47" s="205" t="s">
-        <v>2787</v>
       </c>
       <c r="L47" s="190"/>
       <c r="M47" s="190"/>
-    </row>
-    <row r="48" ht="25.5" customHeight="1">
-      <c r="A48" s="424" t="s">
-        <v>2802</v>
-      </c>
-      <c r="B48" s="425" t="s">
-        <v>2336</v>
-      </c>
-      <c r="C48" s="425" t="s">
-        <v>2337</v>
-      </c>
-      <c r="D48" s="244" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E48" s="426" t="s">
-        <v>2338</v>
-      </c>
-      <c r="F48" s="194" t="s">
-        <v>1708</v>
-      </c>
-      <c r="G48" s="427">
-        <v>46148</v>
-      </c>
-      <c r="H48" s="244" t="s">
-        <v>2804</v>
-      </c>
-      <c r="I48" s="245" t="s">
-        <v>2805</v>
-      </c>
-      <c r="J48" s="245" t="s">
-        <v>2806</v>
-      </c>
-      <c r="K48" s="246" t="s">
-        <v>2807</v>
-      </c>
-      <c r="L48" s="190"/>
-      <c r="M48" s="190"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28799,7 +28694,8 @@
     <hyperlink r:id="rId21" ref="I22"/>
     <hyperlink r:id="rId22" ref="I23"/>
     <hyperlink r:id="rId23" ref="I24"/>
-    <hyperlink r:id="rId24" ref="I25"/>
+    <hyperlink r:id="rId24" ref="I25" tooltip=""/>
+    <hyperlink r:id="rId24" ref="J25" tooltip=""/>
     <hyperlink r:id="rId25" ref="I26" tooltip=""/>
     <hyperlink r:id="rId25" ref="J26" tooltip=""/>
     <hyperlink r:id="rId26" ref="I27" tooltip=""/>
@@ -28844,8 +28740,6 @@
     <hyperlink r:id="rId45" ref="J46" tooltip=""/>
     <hyperlink r:id="rId46" ref="I47" tooltip=""/>
     <hyperlink r:id="rId46" ref="J47" tooltip=""/>
-    <hyperlink r:id="rId47" ref="I48" tooltip=""/>
-    <hyperlink r:id="rId47" ref="J48" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -28863,59 +28757,59 @@
   <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="428" t="s">
+      <c r="A1" s="426" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B1" s="426" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="427" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B2" s="427" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="427" t="s">
+        <v>2801</v>
+      </c>
+      <c r="B3" s="427" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="427" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B4" s="427" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="427" t="s">
+        <v>2805</v>
+      </c>
+      <c r="B5" s="427" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="427" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B6" s="427" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="427" t="s">
         <v>2808</v>
       </c>
-      <c r="B1" s="428" t="s">
+      <c r="B7" s="427" t="s">
         <v>2809</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="429" t="s">
-        <v>2810</v>
-      </c>
-      <c r="B2" s="429" t="s">
-        <v>2811</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="429" t="s">
-        <v>2812</v>
-      </c>
-      <c r="B3" s="429" t="s">
-        <v>2813</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="429" t="s">
-        <v>2814</v>
-      </c>
-      <c r="B4" s="429" t="s">
-        <v>2815</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="429" t="s">
-        <v>2816</v>
-      </c>
-      <c r="B5" s="429" t="s">
-        <v>2817</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="429" t="s">
-        <v>2818</v>
-      </c>
-      <c r="B6" s="429" t="s">
-        <v>2813</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="429" t="s">
-        <v>2819</v>
-      </c>
-      <c r="B7" s="429" t="s">
-        <v>2820</v>
       </c>
     </row>
   </sheetData>
@@ -28935,153 +28829,153 @@
   <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="429" t="s">
+      <c r="A1" s="427" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1" s="427" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C1" s="427" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1" s="427" t="s">
+        <v>2813</v>
+      </c>
+      <c r="E1" s="427" t="s">
+        <v>2814</v>
+      </c>
+      <c r="F1" s="427" t="s">
+        <v>2815</v>
+      </c>
+      <c r="G1" s="427" t="s">
+        <v>2816</v>
+      </c>
+      <c r="H1" s="427" t="s">
+        <v>2817</v>
+      </c>
+      <c r="I1" s="427" t="s">
+        <v>2818</v>
+      </c>
+      <c r="J1" s="427" t="s">
+        <v>2819</v>
+      </c>
+      <c r="K1" s="427" t="s">
+        <v>2820</v>
+      </c>
+      <c r="L1" s="427" t="s">
         <v>2821</v>
       </c>
-      <c r="B1" s="429" t="s">
+      <c r="M1" s="427" t="s">
         <v>2822</v>
       </c>
-      <c r="C1" s="429" t="s">
+      <c r="N1" s="427" t="s">
         <v>2823</v>
       </c>
-      <c r="D1" s="429" t="s">
+      <c r="O1" s="427" t="s">
         <v>2824</v>
       </c>
-      <c r="E1" s="429" t="s">
+      <c r="P1" s="427" t="s">
         <v>2825</v>
       </c>
-      <c r="F1" s="429" t="s">
+      <c r="Q1" s="427" t="s">
         <v>2826</v>
       </c>
-      <c r="G1" s="429" t="s">
+      <c r="R1" s="427" t="s">
         <v>2827</v>
       </c>
-      <c r="H1" s="429" t="s">
+      <c r="S1" s="427" t="s">
         <v>2828</v>
       </c>
-      <c r="I1" s="429" t="s">
+      <c r="T1" s="427" t="s">
         <v>2829</v>
       </c>
-      <c r="J1" s="429" t="s">
+      <c r="U1" s="427" t="s">
         <v>2830</v>
       </c>
-      <c r="K1" s="429" t="s">
+      <c r="V1" s="427" t="s">
         <v>2831</v>
       </c>
-      <c r="L1" s="429" t="s">
+      <c r="W1" s="427" t="s">
         <v>2832</v>
       </c>
-      <c r="M1" s="429" t="s">
+      <c r="X1" s="427" t="s">
         <v>2833</v>
       </c>
-      <c r="N1" s="429" t="s">
+      <c r="Y1" s="427" t="s">
         <v>2834</v>
       </c>
-      <c r="O1" s="429" t="s">
+      <c r="Z1" s="427" t="s">
         <v>2835</v>
       </c>
-      <c r="P1" s="429" t="s">
+      <c r="AA1" s="427" t="s">
         <v>2836</v>
       </c>
-      <c r="Q1" s="429" t="s">
+      <c r="AB1" s="427" t="s">
         <v>2837</v>
       </c>
-      <c r="R1" s="429" t="s">
+      <c r="AC1" s="427" t="s">
         <v>2838</v>
       </c>
-      <c r="S1" s="429" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="427" t="s">
         <v>2839</v>
       </c>
-      <c r="T1" s="429" t="s">
+      <c r="B2" s="427" t="s">
         <v>2840</v>
       </c>
-      <c r="U1" s="429" t="s">
+      <c r="C2" s="427" t="s">
         <v>2841</v>
       </c>
-      <c r="V1" s="429" t="s">
+      <c r="D2" s="427">
+        <v>650628832</v>
+      </c>
+      <c r="E2" s="427">
+        <v>1</v>
+      </c>
+      <c r="F2" s="427">
+        <v>2</v>
+      </c>
+      <c r="G2" s="427" t="s">
         <v>2842</v>
       </c>
-      <c r="W1" s="429" t="s">
+      <c r="H2" s="427" t="s">
         <v>2843</v>
       </c>
-      <c r="X1" s="429" t="s">
+      <c r="I2" s="427" t="s">
+        <v>2843</v>
+      </c>
+      <c r="J2" s="427" t="s">
         <v>2844</v>
       </c>
-      <c r="Y1" s="429" t="s">
+      <c r="K2" s="427" t="s">
         <v>2845</v>
       </c>
-      <c r="Z1" s="429" t="s">
+      <c r="L2" s="427" t="s">
+        <v>2845</v>
+      </c>
+      <c r="M2" s="427" t="s">
         <v>2846</v>
       </c>
-      <c r="AA1" s="429" t="s">
+      <c r="N2" s="427" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="427" t="s">
         <v>2847</v>
       </c>
-      <c r="AB1" s="429" t="s">
-        <v>2848</v>
-      </c>
-      <c r="AC1" s="429" t="s">
-        <v>2849</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="429" t="s">
-        <v>2850</v>
-      </c>
-      <c r="B2" s="429" t="s">
-        <v>2851</v>
-      </c>
-      <c r="C2" s="429" t="s">
-        <v>2852</v>
-      </c>
-      <c r="D2" s="429">
-        <v>650628832</v>
-      </c>
-      <c r="E2" s="429">
+      <c r="P2" s="427" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="427" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="429">
-        <v>2</v>
-      </c>
-      <c r="G2" s="429" t="s">
-        <v>2853</v>
-      </c>
-      <c r="H2" s="429" t="s">
-        <v>2854</v>
-      </c>
-      <c r="I2" s="429" t="s">
-        <v>2854</v>
-      </c>
-      <c r="J2" s="429" t="s">
-        <v>2855</v>
-      </c>
-      <c r="K2" s="429" t="s">
-        <v>2856</v>
-      </c>
-      <c r="L2" s="429" t="s">
-        <v>2856</v>
-      </c>
-      <c r="M2" s="429" t="s">
-        <v>2857</v>
-      </c>
-      <c r="N2" s="429" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="429" t="s">
-        <v>2858</v>
-      </c>
-      <c r="P2" s="429" t="b">
+      <c r="S2" s="427" t="b">
         <v>0</v>
       </c>
-      <c r="R2" s="429" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="429" t="b">
+      <c r="X2" s="427" t="b">
         <v>0</v>
       </c>
-      <c r="X2" s="429" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="429" t="b">
+      <c r="AA2" s="427" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29103,438 +28997,438 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="430" t="s">
-        <v>2859</v>
-      </c>
-      <c r="B1" s="431" t="s">
+      <c r="A1" s="428" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B1" s="429" t="s">
         <v>1827</v>
       </c>
-      <c r="C1" s="431" t="s">
+      <c r="C1" s="429" t="s">
         <v>1828</v>
       </c>
-      <c r="D1" s="431" t="s">
-        <v>2860</v>
-      </c>
-      <c r="E1" s="431" t="s">
-        <v>2861</v>
-      </c>
-      <c r="F1" s="431" t="s">
+      <c r="D1" s="429" t="s">
+        <v>2849</v>
+      </c>
+      <c r="E1" s="429" t="s">
+        <v>2850</v>
+      </c>
+      <c r="F1" s="429" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="431" t="s">
+      <c r="G1" s="429" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="431" t="s">
+      <c r="H1" s="429" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="432" t="s">
-        <v>2862</v>
-      </c>
-      <c r="J1" s="432" t="s">
-        <v>2863</v>
-      </c>
-      <c r="K1" s="432" t="s">
-        <v>2864</v>
-      </c>
-      <c r="L1" s="433" t="s">
-        <v>2865</v>
-      </c>
-      <c r="M1" s="434"/>
-      <c r="N1" s="434"/>
+      <c r="I1" s="430" t="s">
+        <v>2851</v>
+      </c>
+      <c r="J1" s="430" t="s">
+        <v>2852</v>
+      </c>
+      <c r="K1" s="430" t="s">
+        <v>2853</v>
+      </c>
+      <c r="L1" s="431" t="s">
+        <v>2854</v>
+      </c>
+      <c r="M1" s="432"/>
+      <c r="N1" s="432"/>
     </row>
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="247" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B2" s="435" t="s">
-        <v>2867</v>
-      </c>
-      <c r="C2" s="436" t="s">
-        <v>2868</v>
-      </c>
-      <c r="D2" s="436" t="s">
-        <v>2869</v>
-      </c>
-      <c r="E2" s="436" t="s">
-        <v>2870</v>
+        <v>2855</v>
+      </c>
+      <c r="B2" s="433" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C2" s="434" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D2" s="434" t="s">
+        <v>2858</v>
+      </c>
+      <c r="E2" s="434" t="s">
+        <v>2859</v>
       </c>
       <c r="F2" s="187" t="s">
-        <v>2871</v>
-      </c>
-      <c r="G2" s="437" t="s">
+        <v>2860</v>
+      </c>
+      <c r="G2" s="435" t="s">
         <v>1507</v>
       </c>
       <c r="H2" s="186">
         <v>46139</v>
       </c>
       <c r="I2" s="187" t="s">
-        <v>2872</v>
+        <v>2861</v>
       </c>
       <c r="J2" s="188" t="s">
-        <v>2873</v>
+        <v>2862</v>
       </c>
       <c r="K2" s="188" t="s">
-        <v>2871</v>
+        <v>2860</v>
       </c>
       <c r="L2" s="189" t="s">
-        <v>2874</v>
+        <v>2863</v>
       </c>
       <c r="M2" s="190"/>
       <c r="N2" s="190"/>
     </row>
     <row r="3" ht="25.5" customHeight="1">
-      <c r="A3" s="438" t="s">
+      <c r="A3" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B3" s="437" t="s">
+        <v>2864</v>
+      </c>
+      <c r="C3" s="437" t="s">
+        <v>2865</v>
+      </c>
+      <c r="D3" s="437" t="s">
         <v>2866</v>
       </c>
-      <c r="B3" s="439" t="s">
-        <v>2875</v>
-      </c>
-      <c r="C3" s="439" t="s">
-        <v>2876</v>
-      </c>
-      <c r="D3" s="439" t="s">
-        <v>2877</v>
-      </c>
-      <c r="E3" s="439" t="s">
-        <v>2878</v>
+      <c r="E3" s="437" t="s">
+        <v>2867</v>
       </c>
       <c r="F3" s="196" t="s">
-        <v>2783</v>
-      </c>
-      <c r="G3" s="440" t="s">
+        <v>2769</v>
+      </c>
+      <c r="G3" s="438" t="s">
         <v>1514</v>
       </c>
       <c r="H3" s="195">
         <v>46139</v>
       </c>
       <c r="I3" s="196" t="s">
-        <v>2879</v>
+        <v>2868</v>
       </c>
       <c r="J3" s="197" t="s">
-        <v>2880</v>
+        <v>2869</v>
       </c>
       <c r="K3" s="197" t="s">
-        <v>2783</v>
+        <v>2769</v>
       </c>
       <c r="L3" s="198" t="s">
-        <v>2874</v>
+        <v>2863</v>
       </c>
       <c r="M3" s="190"/>
       <c r="N3" s="190"/>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="A4" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B4" s="441" t="s">
-        <v>2881</v>
-      </c>
-      <c r="C4" s="441" t="s">
-        <v>2882</v>
-      </c>
-      <c r="D4" s="441" t="s">
-        <v>2883</v>
-      </c>
-      <c r="E4" s="441" t="s">
-        <v>2884</v>
+      <c r="A4" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B4" s="439" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C4" s="439" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D4" s="439" t="s">
+        <v>2872</v>
+      </c>
+      <c r="E4" s="439" t="s">
+        <v>2873</v>
       </c>
       <c r="F4" s="203" t="s">
-        <v>2885</v>
-      </c>
-      <c r="G4" s="442" t="s">
+        <v>2874</v>
+      </c>
+      <c r="G4" s="440" t="s">
         <v>1520</v>
       </c>
       <c r="H4" s="202">
         <v>46139</v>
       </c>
       <c r="I4" s="203" t="s">
-        <v>2886</v>
+        <v>2875</v>
       </c>
       <c r="J4" s="204" t="s">
-        <v>2887</v>
+        <v>2876</v>
       </c>
       <c r="K4" s="204" t="s">
-        <v>2885</v>
+        <v>2874</v>
       </c>
       <c r="L4" s="205" t="s">
-        <v>2888</v>
+        <v>2877</v>
       </c>
       <c r="M4" s="190"/>
       <c r="N4" s="190"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B5" s="439" t="s">
-        <v>2889</v>
-      </c>
-      <c r="C5" s="439" t="s">
-        <v>2890</v>
-      </c>
-      <c r="D5" s="439" t="s">
-        <v>2891</v>
-      </c>
-      <c r="E5" s="439" t="s">
-        <v>2892</v>
+      <c r="A5" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B5" s="437" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C5" s="437" t="s">
+        <v>2879</v>
+      </c>
+      <c r="D5" s="437" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E5" s="437" t="s">
+        <v>2881</v>
       </c>
       <c r="F5" s="196" t="s">
-        <v>2893</v>
-      </c>
-      <c r="G5" s="440" t="s">
+        <v>2882</v>
+      </c>
+      <c r="G5" s="438" t="s">
         <v>1526</v>
       </c>
       <c r="H5" s="195">
         <v>46139</v>
       </c>
       <c r="I5" s="196" t="s">
-        <v>2894</v>
+        <v>2883</v>
       </c>
       <c r="J5" s="197" t="s">
-        <v>2895</v>
+        <v>2884</v>
       </c>
       <c r="K5" s="197" t="s">
-        <v>2893</v>
+        <v>2882</v>
       </c>
       <c r="L5" s="198" t="s">
-        <v>2888</v>
+        <v>2877</v>
       </c>
       <c r="M5" s="190"/>
       <c r="N5" s="190"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B6" s="441" t="s">
-        <v>2896</v>
-      </c>
-      <c r="C6" s="441" t="s">
-        <v>2897</v>
-      </c>
-      <c r="D6" s="441" t="s">
-        <v>2898</v>
-      </c>
-      <c r="E6" s="441" t="s">
-        <v>2899</v>
+      <c r="A6" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B6" s="439" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C6" s="439" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D6" s="439" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E6" s="439" t="s">
+        <v>2888</v>
       </c>
       <c r="F6" s="203" t="s">
-        <v>2900</v>
-      </c>
-      <c r="G6" s="442" t="s">
+        <v>2889</v>
+      </c>
+      <c r="G6" s="440" t="s">
         <v>1532</v>
       </c>
       <c r="H6" s="202">
         <v>46139</v>
       </c>
       <c r="I6" s="203" t="s">
-        <v>2901</v>
+        <v>2890</v>
       </c>
       <c r="J6" s="204" t="s">
-        <v>2902</v>
+        <v>2891</v>
       </c>
       <c r="K6" s="204" t="s">
-        <v>2900</v>
+        <v>2889</v>
       </c>
       <c r="L6" s="205" t="s">
-        <v>2888</v>
+        <v>2877</v>
       </c>
       <c r="M6" s="190"/>
       <c r="N6" s="190"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B7" s="439" t="s">
-        <v>2903</v>
-      </c>
-      <c r="C7" s="439" t="s">
-        <v>2904</v>
-      </c>
-      <c r="D7" s="439" t="s">
-        <v>2905</v>
-      </c>
-      <c r="E7" s="439" t="s">
-        <v>2906</v>
+      <c r="A7" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B7" s="437" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C7" s="437" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D7" s="437" t="s">
+        <v>2894</v>
+      </c>
+      <c r="E7" s="437" t="s">
+        <v>2895</v>
       </c>
       <c r="F7" s="196" t="s">
-        <v>2907</v>
-      </c>
-      <c r="G7" s="440" t="s">
+        <v>2896</v>
+      </c>
+      <c r="G7" s="438" t="s">
         <v>1538</v>
       </c>
       <c r="H7" s="195">
         <v>46139</v>
       </c>
       <c r="I7" s="196" t="s">
-        <v>2908</v>
+        <v>2897</v>
       </c>
       <c r="J7" s="197" t="s">
-        <v>2909</v>
+        <v>2898</v>
       </c>
       <c r="K7" s="197" t="s">
-        <v>2907</v>
+        <v>2896</v>
       </c>
       <c r="L7" s="198" t="s">
-        <v>2888</v>
+        <v>2877</v>
       </c>
       <c r="M7" s="190"/>
       <c r="N7" s="190"/>
     </row>
     <row r="8" ht="25.5" customHeight="1">
-      <c r="A8" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B8" s="441" t="s">
-        <v>2910</v>
-      </c>
-      <c r="C8" s="441" t="s">
-        <v>2911</v>
-      </c>
-      <c r="D8" s="441" t="s">
-        <v>2912</v>
-      </c>
-      <c r="E8" s="441" t="s">
-        <v>2913</v>
+      <c r="A8" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B8" s="439" t="s">
+        <v>2899</v>
+      </c>
+      <c r="C8" s="439" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D8" s="439" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E8" s="439" t="s">
+        <v>2902</v>
       </c>
       <c r="F8" s="203" t="s">
-        <v>2791</v>
-      </c>
-      <c r="G8" s="442" t="s">
+        <v>2777</v>
+      </c>
+      <c r="G8" s="440" t="s">
         <v>1544</v>
       </c>
       <c r="H8" s="202">
         <v>46139</v>
       </c>
       <c r="I8" s="203" t="s">
-        <v>2914</v>
+        <v>2903</v>
       </c>
       <c r="J8" s="204" t="s">
-        <v>2915</v>
+        <v>2904</v>
       </c>
       <c r="K8" s="204" t="s">
-        <v>2791</v>
+        <v>2777</v>
       </c>
       <c r="L8" s="205" t="s">
-        <v>2888</v>
+        <v>2877</v>
       </c>
       <c r="M8" s="190"/>
       <c r="N8" s="190"/>
     </row>
     <row r="9" ht="25.5" customHeight="1">
-      <c r="A9" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B9" s="439" t="s">
-        <v>2916</v>
-      </c>
-      <c r="C9" s="439" t="s">
-        <v>2917</v>
-      </c>
-      <c r="D9" s="439" t="s">
-        <v>2918</v>
-      </c>
-      <c r="E9" s="439" t="s">
-        <v>2919</v>
+      <c r="A9" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B9" s="437" t="s">
+        <v>2905</v>
+      </c>
+      <c r="C9" s="437" t="s">
+        <v>2906</v>
+      </c>
+      <c r="D9" s="437" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E9" s="437" t="s">
+        <v>2908</v>
       </c>
       <c r="F9" s="196" t="s">
-        <v>2920</v>
-      </c>
-      <c r="G9" s="440" t="s">
+        <v>2909</v>
+      </c>
+      <c r="G9" s="438" t="s">
         <v>1551</v>
       </c>
       <c r="H9" s="195">
         <v>46139</v>
       </c>
       <c r="I9" s="196" t="s">
-        <v>2921</v>
+        <v>2910</v>
       </c>
       <c r="J9" s="197" t="s">
-        <v>2922</v>
+        <v>2911</v>
       </c>
       <c r="K9" s="197" t="s">
-        <v>2920</v>
+        <v>2909</v>
       </c>
       <c r="L9" s="198" t="s">
-        <v>2888</v>
+        <v>2877</v>
       </c>
       <c r="M9" s="190"/>
       <c r="N9" s="190"/>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="438" t="s">
-        <v>2866</v>
-      </c>
-      <c r="B10" s="441" t="s">
-        <v>2923</v>
-      </c>
-      <c r="C10" s="441" t="s">
-        <v>2924</v>
-      </c>
-      <c r="D10" s="441" t="s">
-        <v>2606</v>
-      </c>
-      <c r="E10" s="441" t="s">
-        <v>2925</v>
+      <c r="A10" s="436" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B10" s="439" t="s">
+        <v>2912</v>
+      </c>
+      <c r="C10" s="439" t="s">
+        <v>2913</v>
+      </c>
+      <c r="D10" s="439" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E10" s="439" t="s">
+        <v>2915</v>
       </c>
       <c r="F10" s="203" t="s">
-        <v>2926</v>
-      </c>
-      <c r="G10" s="443" t="s">
+        <v>2916</v>
+      </c>
+      <c r="G10" s="441" t="s">
         <v>1557</v>
       </c>
       <c r="H10" s="202">
         <v>46139</v>
       </c>
       <c r="I10" s="203" t="s">
-        <v>2927</v>
+        <v>2917</v>
       </c>
       <c r="J10" s="204" t="s">
-        <v>2928</v>
+        <v>2918</v>
       </c>
       <c r="K10" s="204" t="s">
-        <v>2926</v>
+        <v>2916</v>
       </c>
       <c r="L10" s="205" t="s">
-        <v>2929</v>
+        <v>2919</v>
       </c>
       <c r="M10" s="190"/>
       <c r="N10" s="190"/>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="444" t="s">
+      <c r="A11" s="442" t="s">
         <v>1619</v>
       </c>
-      <c r="B11" s="439" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C11" s="439" t="s">
-        <v>2931</v>
-      </c>
-      <c r="D11" s="445" t="s">
-        <v>2932</v>
-      </c>
-      <c r="E11" s="445" t="s">
-        <v>2933</v>
+      <c r="B11" s="437" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C11" s="437" t="s">
+        <v>2921</v>
+      </c>
+      <c r="D11" s="443" t="s">
+        <v>2922</v>
+      </c>
+      <c r="E11" s="443" t="s">
+        <v>2923</v>
       </c>
       <c r="F11" s="230" t="s">
-        <v>2934</v>
+        <v>2924</v>
       </c>
       <c r="G11" s="194" t="s">
-        <v>2935</v>
+        <v>2925</v>
       </c>
       <c r="H11" s="195">
         <v>46139</v>
       </c>
       <c r="I11" s="196" t="s">
-        <v>2936</v>
+        <v>2926</v>
       </c>
       <c r="J11" s="197" t="s">
-        <v>2937</v>
+        <v>2927</v>
       </c>
       <c r="K11" s="197" t="s">
-        <v>2934</v>
+        <v>2924</v>
       </c>
       <c r="L11" s="198" t="s">
         <v>2335</v>
@@ -29543,38 +29437,38 @@
       <c r="N11" s="190"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="446" t="s">
+      <c r="A12" s="444" t="s">
         <v>1619</v>
       </c>
-      <c r="B12" s="441" t="s">
-        <v>2938</v>
-      </c>
-      <c r="C12" s="441" t="s">
-        <v>2939</v>
-      </c>
-      <c r="D12" s="447" t="s">
-        <v>2940</v>
-      </c>
-      <c r="E12" s="447" t="s">
-        <v>2941</v>
+      <c r="B12" s="439" t="s">
+        <v>2928</v>
+      </c>
+      <c r="C12" s="439" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D12" s="445" t="s">
+        <v>2930</v>
+      </c>
+      <c r="E12" s="445" t="s">
+        <v>2931</v>
       </c>
       <c r="F12" s="212" t="s">
-        <v>2942</v>
+        <v>2932</v>
       </c>
       <c r="G12" s="194" t="s">
-        <v>2943</v>
+        <v>2933</v>
       </c>
       <c r="H12" s="202">
         <v>46139</v>
       </c>
       <c r="I12" s="203" t="s">
-        <v>2944</v>
+        <v>2934</v>
       </c>
       <c r="J12" s="204" t="s">
-        <v>2945</v>
+        <v>2935</v>
       </c>
       <c r="K12" s="204" t="s">
-        <v>2942</v>
+        <v>2932</v>
       </c>
       <c r="L12" s="205" t="s">
         <v>2335</v>
@@ -29583,38 +29477,38 @@
       <c r="N12" s="190"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="446" t="s">
+      <c r="A13" s="444" t="s">
         <v>1619</v>
       </c>
-      <c r="B13" s="439" t="s">
-        <v>2946</v>
-      </c>
-      <c r="C13" s="439" t="s">
-        <v>2947</v>
-      </c>
-      <c r="D13" s="445" t="s">
-        <v>2948</v>
-      </c>
-      <c r="E13" s="445" t="s">
+      <c r="B13" s="437" t="s">
+        <v>2936</v>
+      </c>
+      <c r="C13" s="437" t="s">
+        <v>2937</v>
+      </c>
+      <c r="D13" s="443" t="s">
+        <v>2938</v>
+      </c>
+      <c r="E13" s="443" t="s">
+        <v>2930</v>
+      </c>
+      <c r="F13" s="230" t="s">
+        <v>2939</v>
+      </c>
+      <c r="G13" s="194" t="s">
         <v>2940</v>
-      </c>
-      <c r="F13" s="230" t="s">
-        <v>2949</v>
-      </c>
-      <c r="G13" s="194" t="s">
-        <v>2950</v>
       </c>
       <c r="H13" s="195">
         <v>46139</v>
       </c>
       <c r="I13" s="196" t="s">
-        <v>2951</v>
+        <v>2941</v>
       </c>
       <c r="J13" s="197" t="s">
-        <v>2952</v>
+        <v>2942</v>
       </c>
       <c r="K13" s="197" t="s">
-        <v>2949</v>
+        <v>2939</v>
       </c>
       <c r="L13" s="198" t="s">
         <v>2335</v>
@@ -29623,38 +29517,38 @@
       <c r="N13" s="190"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="446" t="s">
+      <c r="A14" s="444" t="s">
         <v>1619</v>
       </c>
-      <c r="B14" s="441" t="s">
-        <v>2953</v>
-      </c>
-      <c r="C14" s="441" t="s">
-        <v>2954</v>
-      </c>
-      <c r="D14" s="447" t="s">
-        <v>2955</v>
-      </c>
-      <c r="E14" s="447" t="s">
-        <v>2956</v>
+      <c r="B14" s="439" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C14" s="439" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D14" s="445" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E14" s="445" t="s">
+        <v>2946</v>
       </c>
       <c r="F14" s="212" t="s">
-        <v>2957</v>
+        <v>2947</v>
       </c>
       <c r="G14" s="194" t="s">
-        <v>2958</v>
+        <v>2948</v>
       </c>
       <c r="H14" s="202">
         <v>46139</v>
       </c>
       <c r="I14" s="203" t="s">
-        <v>2959</v>
+        <v>2949</v>
       </c>
       <c r="J14" s="204" t="s">
-        <v>2960</v>
+        <v>2950</v>
       </c>
       <c r="K14" s="204" t="s">
-        <v>2957</v>
+        <v>2947</v>
       </c>
       <c r="L14" s="205" t="s">
         <v>2335</v>
@@ -29663,38 +29557,38 @@
       <c r="N14" s="190"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="446" t="s">
+      <c r="A15" s="444" t="s">
         <v>1619</v>
       </c>
-      <c r="B15" s="441" t="s">
-        <v>2961</v>
-      </c>
-      <c r="C15" s="441" t="s">
-        <v>2962</v>
-      </c>
-      <c r="D15" s="447" t="s">
-        <v>2963</v>
-      </c>
-      <c r="E15" s="447" t="s">
-        <v>2964</v>
+      <c r="B15" s="439" t="s">
+        <v>2951</v>
+      </c>
+      <c r="C15" s="439" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D15" s="445" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E15" s="445" t="s">
+        <v>2954</v>
       </c>
       <c r="F15" s="212" t="s">
-        <v>2965</v>
+        <v>2955</v>
       </c>
       <c r="G15" s="194" t="s">
-        <v>2966</v>
+        <v>2956</v>
       </c>
       <c r="H15" s="202">
         <v>46139</v>
       </c>
       <c r="I15" s="203" t="s">
-        <v>2967</v>
+        <v>2957</v>
       </c>
       <c r="J15" s="204" t="s">
-        <v>2968</v>
+        <v>2958</v>
       </c>
       <c r="K15" s="204" t="s">
-        <v>2965</v>
+        <v>2955</v>
       </c>
       <c r="L15" s="205" t="s">
         <v>2342</v>
@@ -29703,38 +29597,38 @@
       <c r="N15" s="190"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="446" t="s">
+      <c r="A16" s="444" t="s">
         <v>1619</v>
       </c>
-      <c r="B16" s="439" t="s">
-        <v>2969</v>
-      </c>
-      <c r="C16" s="439" t="s">
-        <v>2970</v>
-      </c>
-      <c r="D16" s="445" t="s">
-        <v>2971</v>
-      </c>
-      <c r="E16" s="445" t="s">
-        <v>2972</v>
+      <c r="B16" s="437" t="s">
+        <v>2959</v>
+      </c>
+      <c r="C16" s="437" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D16" s="443" t="s">
+        <v>2961</v>
+      </c>
+      <c r="E16" s="443" t="s">
+        <v>2962</v>
       </c>
       <c r="F16" s="230" t="s">
-        <v>2973</v>
+        <v>2963</v>
       </c>
       <c r="G16" s="194" t="s">
-        <v>2974</v>
+        <v>2964</v>
       </c>
       <c r="H16" s="195">
         <v>46139</v>
       </c>
       <c r="I16" s="196" t="s">
-        <v>2975</v>
+        <v>2965</v>
       </c>
       <c r="J16" s="197" t="s">
-        <v>2976</v>
+        <v>2966</v>
       </c>
       <c r="K16" s="197" t="s">
-        <v>2973</v>
+        <v>2963</v>
       </c>
       <c r="L16" s="198" t="s">
         <v>2342</v>
@@ -29744,262 +29638,262 @@
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" s="368" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B17" s="439" t="s">
-        <v>2977</v>
-      </c>
-      <c r="C17" s="439" t="s">
-        <v>2978</v>
-      </c>
-      <c r="D17" s="445" t="s">
-        <v>2979</v>
-      </c>
-      <c r="E17" s="445" t="s">
-        <v>2980</v>
+        <v>2668</v>
+      </c>
+      <c r="B17" s="437" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C17" s="437" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D17" s="443" t="s">
+        <v>2969</v>
+      </c>
+      <c r="E17" s="443" t="s">
+        <v>2970</v>
       </c>
       <c r="F17" s="230" t="s">
-        <v>2981</v>
+        <v>2971</v>
       </c>
       <c r="G17" s="194" t="s">
-        <v>2982</v>
+        <v>2972</v>
       </c>
       <c r="H17" s="195">
         <v>46139</v>
       </c>
       <c r="I17" s="196" t="s">
-        <v>2983</v>
+        <v>2973</v>
       </c>
       <c r="J17" s="197" t="s">
-        <v>2984</v>
+        <v>2974</v>
       </c>
       <c r="K17" s="197" t="s">
-        <v>2981</v>
+        <v>2971</v>
       </c>
       <c r="L17" s="198" t="s">
-        <v>2985</v>
+        <v>2975</v>
       </c>
       <c r="M17" s="190"/>
       <c r="N17" s="190"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
       <c r="A18" s="369" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B18" s="441" t="s">
-        <v>2986</v>
-      </c>
-      <c r="C18" s="441" t="s">
-        <v>2987</v>
-      </c>
-      <c r="D18" s="447" t="s">
-        <v>2988</v>
-      </c>
-      <c r="E18" s="447" t="s">
-        <v>2989</v>
+        <v>2668</v>
+      </c>
+      <c r="B18" s="439" t="s">
+        <v>2976</v>
+      </c>
+      <c r="C18" s="439" t="s">
+        <v>2977</v>
+      </c>
+      <c r="D18" s="445" t="s">
+        <v>2978</v>
+      </c>
+      <c r="E18" s="445" t="s">
+        <v>2979</v>
       </c>
       <c r="F18" s="212" t="s">
-        <v>2990</v>
+        <v>2980</v>
       </c>
       <c r="G18" s="194" t="s">
-        <v>2991</v>
+        <v>2981</v>
       </c>
       <c r="H18" s="202">
         <v>46139</v>
       </c>
       <c r="I18" s="203" t="s">
-        <v>2992</v>
+        <v>2982</v>
       </c>
       <c r="J18" s="204" t="s">
-        <v>2993</v>
+        <v>2983</v>
       </c>
       <c r="K18" s="204" t="s">
-        <v>2990</v>
+        <v>2980</v>
       </c>
       <c r="L18" s="205" t="s">
-        <v>2985</v>
+        <v>2975</v>
       </c>
       <c r="M18" s="190"/>
       <c r="N18" s="190"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19" s="369" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B19" s="439" t="s">
-        <v>2994</v>
-      </c>
-      <c r="C19" s="439" t="s">
-        <v>2995</v>
-      </c>
-      <c r="D19" s="445" t="s">
-        <v>2996</v>
-      </c>
-      <c r="E19" s="445" t="s">
-        <v>2997</v>
+        <v>2668</v>
+      </c>
+      <c r="B19" s="437" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C19" s="437" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D19" s="443" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E19" s="443" t="s">
+        <v>2987</v>
       </c>
       <c r="F19" s="230" t="s">
-        <v>2998</v>
+        <v>2988</v>
       </c>
       <c r="G19" s="194" t="s">
-        <v>2999</v>
+        <v>2989</v>
       </c>
       <c r="H19" s="195">
         <v>46139</v>
       </c>
       <c r="I19" s="196" t="s">
-        <v>3000</v>
+        <v>2990</v>
       </c>
       <c r="J19" s="197" t="s">
-        <v>3001</v>
+        <v>2991</v>
       </c>
       <c r="K19" s="197" t="s">
-        <v>2998</v>
+        <v>2988</v>
       </c>
       <c r="L19" s="198" t="s">
-        <v>2985</v>
+        <v>2975</v>
       </c>
       <c r="M19" s="190"/>
       <c r="N19" s="190"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
       <c r="A20" s="369" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B20" s="441" t="s">
-        <v>3002</v>
-      </c>
-      <c r="C20" s="441" t="s">
-        <v>3003</v>
-      </c>
-      <c r="D20" s="447" t="s">
-        <v>3004</v>
-      </c>
-      <c r="E20" s="447" t="s">
-        <v>3005</v>
+        <v>2668</v>
+      </c>
+      <c r="B20" s="439" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C20" s="439" t="s">
+        <v>2993</v>
+      </c>
+      <c r="D20" s="445" t="s">
+        <v>2994</v>
+      </c>
+      <c r="E20" s="445" t="s">
+        <v>2995</v>
       </c>
       <c r="F20" s="212" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="G20" s="194" t="s">
-        <v>3007</v>
+        <v>2997</v>
       </c>
       <c r="H20" s="202">
         <v>46139</v>
       </c>
       <c r="I20" s="203" t="s">
-        <v>3008</v>
+        <v>2998</v>
       </c>
       <c r="J20" s="204" t="s">
-        <v>3009</v>
+        <v>2999</v>
       </c>
       <c r="K20" s="204" t="s">
-        <v>3006</v>
+        <v>2996</v>
       </c>
       <c r="L20" s="205" t="s">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="M20" s="190"/>
       <c r="N20" s="190"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="369" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B21" s="439" t="s">
-        <v>3011</v>
-      </c>
-      <c r="C21" s="439" t="s">
-        <v>3012</v>
-      </c>
-      <c r="D21" s="445" t="s">
-        <v>3013</v>
-      </c>
-      <c r="E21" s="445" t="s">
-        <v>3014</v>
+        <v>2668</v>
+      </c>
+      <c r="B21" s="437" t="s">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="437" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D21" s="443" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E21" s="443" t="s">
+        <v>3004</v>
       </c>
       <c r="F21" s="230" t="s">
-        <v>3015</v>
+        <v>3005</v>
       </c>
       <c r="G21" s="194" t="s">
-        <v>3016</v>
+        <v>3006</v>
       </c>
       <c r="H21" s="195">
         <v>46139</v>
       </c>
       <c r="I21" s="196" t="s">
-        <v>3017</v>
+        <v>3007</v>
       </c>
       <c r="J21" s="197" t="s">
-        <v>3018</v>
+        <v>3008</v>
       </c>
       <c r="K21" s="197" t="s">
-        <v>3015</v>
+        <v>3005</v>
       </c>
       <c r="L21" s="198" t="s">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="M21" s="190"/>
       <c r="N21" s="190"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="369" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B22" s="441" t="s">
-        <v>3019</v>
-      </c>
-      <c r="C22" s="441" t="s">
-        <v>3020</v>
-      </c>
-      <c r="D22" s="447" t="s">
-        <v>3021</v>
-      </c>
-      <c r="E22" s="447" t="s">
-        <v>3022</v>
+        <v>2668</v>
+      </c>
+      <c r="B22" s="439" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C22" s="439" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D22" s="445" t="s">
+        <v>3011</v>
+      </c>
+      <c r="E22" s="445" t="s">
+        <v>3012</v>
       </c>
       <c r="F22" s="212" t="s">
-        <v>3023</v>
+        <v>3013</v>
       </c>
       <c r="G22" s="194" t="s">
-        <v>3024</v>
+        <v>3014</v>
       </c>
       <c r="H22" s="202">
         <v>46139</v>
       </c>
       <c r="I22" s="203" t="s">
-        <v>3025</v>
+        <v>3015</v>
       </c>
       <c r="J22" s="204" t="s">
-        <v>3026</v>
+        <v>3016</v>
       </c>
       <c r="K22" s="204" t="s">
-        <v>3023</v>
+        <v>3013</v>
       </c>
       <c r="L22" s="205" t="s">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="M22" s="190"/>
       <c r="N22" s="190"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="448" t="s">
-        <v>3027</v>
-      </c>
-      <c r="B23" s="441" t="s">
-        <v>3028</v>
-      </c>
-      <c r="C23" s="441" t="s">
-        <v>3029</v>
-      </c>
-      <c r="D23" s="447" t="s">
-        <v>3030</v>
-      </c>
-      <c r="E23" s="447" t="s">
-        <v>3031</v>
+      <c r="A23" s="446" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B23" s="439" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C23" s="439" t="s">
+        <v>3019</v>
+      </c>
+      <c r="D23" s="445" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E23" s="445" t="s">
+        <v>3021</v>
       </c>
       <c r="F23" s="212" t="s">
-        <v>3032</v>
+        <v>3022</v>
       </c>
       <c r="G23" s="194" t="s">
         <v>1655</v>
@@ -30008,176 +29902,176 @@
         <v>46139</v>
       </c>
       <c r="I23" s="203" t="s">
-        <v>3033</v>
+        <v>3023</v>
       </c>
       <c r="J23" s="204" t="s">
-        <v>3034</v>
+        <v>3024</v>
       </c>
       <c r="K23" s="204" t="s">
-        <v>3032</v>
+        <v>3022</v>
       </c>
       <c r="L23" s="205" t="s">
-        <v>2398</v>
+        <v>2392</v>
       </c>
       <c r="M23" s="190"/>
       <c r="N23" s="190"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="449" t="s">
+      <c r="A24" s="447" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B24" s="437" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C24" s="437" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D24" s="443" t="s">
         <v>3027</v>
       </c>
-      <c r="B24" s="439" t="s">
-        <v>3035</v>
-      </c>
-      <c r="C24" s="439" t="s">
-        <v>3036</v>
-      </c>
-      <c r="D24" s="445" t="s">
-        <v>3037</v>
-      </c>
-      <c r="E24" s="445" t="s">
-        <v>3038</v>
+      <c r="E24" s="443" t="s">
+        <v>3028</v>
       </c>
       <c r="F24" s="230" t="s">
-        <v>3039</v>
+        <v>3029</v>
       </c>
       <c r="G24" s="194" t="s">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="H24" s="195">
         <v>46139</v>
       </c>
       <c r="I24" s="196" t="s">
-        <v>3041</v>
+        <v>3031</v>
       </c>
       <c r="J24" s="197" t="s">
-        <v>3042</v>
+        <v>3032</v>
       </c>
       <c r="K24" s="197" t="s">
-        <v>3039</v>
+        <v>3029</v>
       </c>
       <c r="L24" s="198" t="s">
-        <v>2398</v>
+        <v>2392</v>
       </c>
       <c r="M24" s="190"/>
       <c r="N24" s="190"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="449" t="s">
-        <v>3027</v>
-      </c>
-      <c r="B25" s="450" t="s">
-        <v>3043</v>
-      </c>
-      <c r="C25" s="450" t="s">
-        <v>3044</v>
-      </c>
-      <c r="D25" s="451" t="s">
-        <v>3045</v>
-      </c>
-      <c r="E25" s="451" t="s">
-        <v>3046</v>
+      <c r="A25" s="447" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B25" s="448" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C25" s="448" t="s">
+        <v>3034</v>
+      </c>
+      <c r="D25" s="449" t="s">
+        <v>3035</v>
+      </c>
+      <c r="E25" s="449" t="s">
+        <v>3036</v>
       </c>
       <c r="F25" s="233" t="s">
-        <v>3047</v>
+        <v>3037</v>
       </c>
       <c r="G25" s="194" t="s">
-        <v>3048</v>
+        <v>3038</v>
       </c>
       <c r="H25" s="234">
         <v>46139</v>
       </c>
       <c r="I25" s="235" t="s">
-        <v>3049</v>
+        <v>3039</v>
       </c>
       <c r="J25" s="236" t="s">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="K25" s="236" t="s">
-        <v>3047</v>
+        <v>3037</v>
       </c>
       <c r="L25" s="237" t="s">
-        <v>3051</v>
+        <v>3041</v>
       </c>
       <c r="M25" s="190"/>
       <c r="N25" s="190"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="449" t="s">
-        <v>3027</v>
-      </c>
-      <c r="B26" s="441" t="s">
-        <v>3052</v>
-      </c>
-      <c r="C26" s="441" t="s">
-        <v>3053</v>
-      </c>
-      <c r="D26" s="447" t="s">
-        <v>3054</v>
-      </c>
-      <c r="E26" s="447" t="s">
-        <v>3055</v>
+      <c r="A26" s="447" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B26" s="439" t="s">
+        <v>3042</v>
+      </c>
+      <c r="C26" s="439" t="s">
+        <v>3043</v>
+      </c>
+      <c r="D26" s="445" t="s">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="445" t="s">
+        <v>3045</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>3056</v>
+        <v>3046</v>
       </c>
       <c r="G26" s="194" t="s">
-        <v>3057</v>
+        <v>3047</v>
       </c>
       <c r="H26" s="202">
         <v>46139</v>
       </c>
       <c r="I26" s="203" t="s">
-        <v>3058</v>
+        <v>3048</v>
       </c>
       <c r="J26" s="204" t="s">
-        <v>3059</v>
+        <v>3049</v>
       </c>
       <c r="K26" s="204" t="s">
-        <v>3056</v>
+        <v>3046</v>
       </c>
       <c r="L26" s="205" t="s">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="M26" s="190"/>
       <c r="N26" s="190"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
-      <c r="A27" s="449" t="s">
-        <v>3027</v>
-      </c>
-      <c r="B27" s="439" t="s">
-        <v>3061</v>
-      </c>
-      <c r="C27" s="439" t="s">
-        <v>3062</v>
-      </c>
-      <c r="D27" s="445" t="s">
-        <v>3063</v>
-      </c>
-      <c r="E27" s="445" t="s">
-        <v>3064</v>
+      <c r="A27" s="447" t="s">
+        <v>3017</v>
+      </c>
+      <c r="B27" s="437" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C27" s="437" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D27" s="443" t="s">
+        <v>3053</v>
+      </c>
+      <c r="E27" s="443" t="s">
+        <v>3054</v>
       </c>
       <c r="F27" s="230" t="s">
-        <v>3065</v>
+        <v>3055</v>
       </c>
       <c r="G27" s="194" t="s">
-        <v>3066</v>
+        <v>3056</v>
       </c>
       <c r="H27" s="195">
         <v>46139</v>
       </c>
       <c r="I27" s="196" t="s">
-        <v>3067</v>
+        <v>3057</v>
       </c>
       <c r="J27" s="197" t="s">
-        <v>3068</v>
+        <v>3058</v>
       </c>
       <c r="K27" s="197" t="s">
-        <v>3065</v>
+        <v>3055</v>
       </c>
       <c r="L27" s="198" t="s">
-        <v>3069</v>
+        <v>3059</v>
       </c>
       <c r="M27" s="190"/>
       <c r="N27" s="190"/>
